--- a/review-results/河北实时运行及市场出清数据-20260829.xlsx
+++ b/review-results/河北实时运行及市场出清数据-20260829.xlsx
@@ -1389,7 +1389,9 @@
       <s:c r="D2" s="12" t="n">
         <s:v>27988.4</s:v>
       </s:c>
-      <s:c r="E2" s="13"/>
+      <s:c r="E2" s="13" t="n">
+        <s:v>9011.05</s:v>
+      </s:c>
       <s:c r="F2" s="14" t="n">
         <s:v>749.2</s:v>
       </s:c>
@@ -1415,7 +1417,9 @@
       <s:c r="D3" s="12" t="n">
         <s:v>27916.3</s:v>
       </s:c>
-      <s:c r="E3" s="13"/>
+      <s:c r="E3" s="13" t="n">
+        <s:v>9007.17</s:v>
+      </s:c>
       <s:c r="F3" s="14" t="n">
         <s:v>702.9</s:v>
       </s:c>
@@ -1441,7 +1445,9 @@
       <s:c r="D4" s="12" t="n">
         <s:v>27569.5</s:v>
       </s:c>
-      <s:c r="E4" s="13"/>
+      <s:c r="E4" s="13" t="n">
+        <s:v>9003.5</s:v>
+      </s:c>
       <s:c r="F4" s="14" t="n">
         <s:v>615.9</s:v>
       </s:c>
@@ -1467,7 +1473,9 @@
       <s:c r="D5" s="12" t="n">
         <s:v>27777.9</s:v>
       </s:c>
-      <s:c r="E5" s="13"/>
+      <s:c r="E5" s="13" t="n">
+        <s:v>9151.72</s:v>
+      </s:c>
       <s:c r="F5" s="14" t="n">
         <s:v>576.1</s:v>
       </s:c>
@@ -1493,7 +1501,9 @@
       <s:c r="D6" s="12" t="n">
         <s:v>30651.1</s:v>
       </s:c>
-      <s:c r="E6" s="13"/>
+      <s:c r="E6" s="13" t="n">
+        <s:v>9396.93</s:v>
+      </s:c>
       <s:c r="F6" s="14" t="n">
         <s:v>567.6</s:v>
       </s:c>
@@ -1519,7 +1529,9 @@
       <s:c r="D7" s="12" t="n">
         <s:v>30479.2</s:v>
       </s:c>
-      <s:c r="E7" s="13"/>
+      <s:c r="E7" s="13" t="n">
+        <s:v>9492.71</s:v>
+      </s:c>
       <s:c r="F7" s="14" t="n">
         <s:v>561.3</s:v>
       </s:c>
@@ -1545,7 +1557,9 @@
       <s:c r="D8" s="12" t="n">
         <s:v>29780.5</s:v>
       </s:c>
-      <s:c r="E8" s="13"/>
+      <s:c r="E8" s="13" t="n">
+        <s:v>9489.67</s:v>
+      </s:c>
       <s:c r="F8" s="14" t="n">
         <s:v>521.8</s:v>
       </s:c>
@@ -1571,7 +1585,9 @@
       <s:c r="D9" s="12" t="n">
         <s:v>29290.8</s:v>
       </s:c>
-      <s:c r="E9" s="13"/>
+      <s:c r="E9" s="13" t="n">
+        <s:v>9389.35</s:v>
+      </s:c>
       <s:c r="F9" s="14" t="n">
         <s:v>478</s:v>
       </s:c>
@@ -1597,7 +1613,9 @@
       <s:c r="D10" s="12" t="n">
         <s:v>28426.3</s:v>
       </s:c>
-      <s:c r="E10" s="13"/>
+      <s:c r="E10" s="13" t="n">
+        <s:v>9135.04</s:v>
+      </s:c>
       <s:c r="F10" s="14" t="n">
         <s:v>426.2</s:v>
       </s:c>
@@ -1623,7 +1641,9 @@
       <s:c r="D11" s="12" t="n">
         <s:v>28193.1</s:v>
       </s:c>
-      <s:c r="E11" s="13"/>
+      <s:c r="E11" s="13" t="n">
+        <s:v>8985.42</s:v>
+      </s:c>
       <s:c r="F11" s="14" t="n">
         <s:v>436.5</s:v>
       </s:c>
@@ -1649,7 +1669,9 @@
       <s:c r="D12" s="12" t="n">
         <s:v>27746</s:v>
       </s:c>
-      <s:c r="E12" s="13"/>
+      <s:c r="E12" s="13" t="n">
+        <s:v>8984.96</s:v>
+      </s:c>
       <s:c r="F12" s="14" t="n">
         <s:v>431.1</s:v>
       </s:c>
@@ -1675,7 +1697,9 @@
       <s:c r="D13" s="12" t="n">
         <s:v>27537.2</s:v>
       </s:c>
-      <s:c r="E13" s="13"/>
+      <s:c r="E13" s="13" t="n">
+        <s:v>8984.46</s:v>
+      </s:c>
       <s:c r="F13" s="14" t="n">
         <s:v>424.4</s:v>
       </s:c>
@@ -1701,7 +1725,9 @@
       <s:c r="D14" s="12" t="n">
         <s:v>27090.8</s:v>
       </s:c>
-      <s:c r="E14" s="13"/>
+      <s:c r="E14" s="13" t="n">
+        <s:v>8981.76</s:v>
+      </s:c>
       <s:c r="F14" s="14" t="n">
         <s:v>381.7</s:v>
       </s:c>
@@ -1727,7 +1753,9 @@
       <s:c r="D15" s="12" t="n">
         <s:v>27088.4</s:v>
       </s:c>
-      <s:c r="E15" s="13"/>
+      <s:c r="E15" s="13" t="n">
+        <s:v>8981.39</s:v>
+      </s:c>
       <s:c r="F15" s="14" t="n">
         <s:v>390.6</s:v>
       </s:c>
@@ -1753,7 +1781,9 @@
       <s:c r="D16" s="12" t="n">
         <s:v>26784.1</s:v>
       </s:c>
-      <s:c r="E16" s="13"/>
+      <s:c r="E16" s="13" t="n">
+        <s:v>8978.21</s:v>
+      </s:c>
       <s:c r="F16" s="14" t="n">
         <s:v>381.6</s:v>
       </s:c>
@@ -1779,7 +1809,9 @@
       <s:c r="D17" s="12" t="n">
         <s:v>26696.8</s:v>
       </s:c>
-      <s:c r="E17" s="13"/>
+      <s:c r="E17" s="13" t="n">
+        <s:v>8977.58</s:v>
+      </s:c>
       <s:c r="F17" s="14" t="n">
         <s:v>416.5</s:v>
       </s:c>
@@ -1805,7 +1837,9 @@
       <s:c r="D18" s="12" t="n">
         <s:v>26720</s:v>
       </s:c>
-      <s:c r="E18" s="13"/>
+      <s:c r="E18" s="13" t="n">
+        <s:v>8987.37</s:v>
+      </s:c>
       <s:c r="F18" s="14" t="n">
         <s:v>456.4</s:v>
       </s:c>
@@ -1831,7 +1865,9 @@
       <s:c r="D19" s="12" t="n">
         <s:v>26555.6</s:v>
       </s:c>
-      <s:c r="E19" s="13"/>
+      <s:c r="E19" s="13" t="n">
+        <s:v>8985.47</s:v>
+      </s:c>
       <s:c r="F19" s="14" t="n">
         <s:v>469.3</s:v>
       </s:c>
@@ -1857,7 +1893,9 @@
       <s:c r="D20" s="12" t="n">
         <s:v>26678.3</s:v>
       </s:c>
-      <s:c r="E20" s="13"/>
+      <s:c r="E20" s="13" t="n">
+        <s:v>8981.87</s:v>
+      </s:c>
       <s:c r="F20" s="14" t="n">
         <s:v>454.8</s:v>
       </s:c>
@@ -1883,7 +1921,9 @@
       <s:c r="D21" s="12" t="n">
         <s:v>26531.2</s:v>
       </s:c>
-      <s:c r="E21" s="13"/>
+      <s:c r="E21" s="13" t="n">
+        <s:v>8981.91</s:v>
+      </s:c>
       <s:c r="F21" s="14" t="n">
         <s:v>452</s:v>
       </s:c>
@@ -1909,7 +1949,9 @@
       <s:c r="D22" s="12" t="n">
         <s:v>26731.3</s:v>
       </s:c>
-      <s:c r="E22" s="13"/>
+      <s:c r="E22" s="13" t="n">
+        <s:v>8977.53</s:v>
+      </s:c>
       <s:c r="F22" s="14" t="n">
         <s:v>434.6</s:v>
       </s:c>
@@ -1935,7 +1977,9 @@
       <s:c r="D23" s="12" t="n">
         <s:v>26927.4</s:v>
       </s:c>
-      <s:c r="E23" s="13"/>
+      <s:c r="E23" s="13" t="n">
+        <s:v>8979.24</s:v>
+      </s:c>
       <s:c r="F23" s="14" t="n">
         <s:v>423.7</s:v>
       </s:c>
@@ -1961,7 +2005,9 @@
       <s:c r="D24" s="12" t="n">
         <s:v>27454.8</s:v>
       </s:c>
-      <s:c r="E24" s="13"/>
+      <s:c r="E24" s="13" t="n">
+        <s:v>8982.5</s:v>
+      </s:c>
       <s:c r="F24" s="14" t="n">
         <s:v>425.1</s:v>
       </s:c>
@@ -1987,7 +2033,9 @@
       <s:c r="D25" s="12" t="n">
         <s:v>27979.2</s:v>
       </s:c>
-      <s:c r="E25" s="13"/>
+      <s:c r="E25" s="13" t="n">
+        <s:v>8988.14</s:v>
+      </s:c>
       <s:c r="F25" s="14" t="n">
         <s:v>516.7</s:v>
       </s:c>
@@ -2013,7 +2061,9 @@
       <s:c r="D26" s="12" t="n">
         <s:v>28966.8</s:v>
       </s:c>
-      <s:c r="E26" s="13"/>
+      <s:c r="E26" s="13" t="n">
+        <s:v>8876.36</s:v>
+      </s:c>
       <s:c r="F26" s="14" t="n">
         <s:v>630.6</s:v>
       </s:c>
@@ -2039,7 +2089,9 @@
       <s:c r="D27" s="12" t="n">
         <s:v>28692.7</s:v>
       </s:c>
-      <s:c r="E27" s="13"/>
+      <s:c r="E27" s="13" t="n">
+        <s:v>8441.55</s:v>
+      </s:c>
       <s:c r="F27" s="14" t="n">
         <s:v>809.7</s:v>
       </s:c>
@@ -2065,7 +2117,9 @@
       <s:c r="D28" s="12" t="n">
         <s:v>28615.2</s:v>
       </s:c>
-      <s:c r="E28" s="13"/>
+      <s:c r="E28" s="13" t="n">
+        <s:v>7828.34</s:v>
+      </s:c>
       <s:c r="F28" s="14" t="n">
         <s:v>1139.9</s:v>
       </s:c>
@@ -2091,7 +2145,9 @@
       <s:c r="D29" s="12" t="n">
         <s:v>28241.1</s:v>
       </s:c>
-      <s:c r="E29" s="13"/>
+      <s:c r="E29" s="13" t="n">
+        <s:v>7225.5</s:v>
+      </s:c>
       <s:c r="F29" s="14" t="n">
         <s:v>1420.5</s:v>
       </s:c>
@@ -2117,7 +2173,9 @@
       <s:c r="D30" s="12" t="n">
         <s:v>28299.3</s:v>
       </s:c>
-      <s:c r="E30" s="13"/>
+      <s:c r="E30" s="13" t="n">
+        <s:v>6620.85</s:v>
+      </s:c>
       <s:c r="F30" s="14" t="n">
         <s:v>1758.9</s:v>
       </s:c>
@@ -2143,7 +2201,9 @@
       <s:c r="D31" s="12" t="n">
         <s:v>28105.7</s:v>
       </s:c>
-      <s:c r="E31" s="13"/>
+      <s:c r="E31" s="13" t="n">
+        <s:v>6107.59</s:v>
+      </s:c>
       <s:c r="F31" s="14" t="n">
         <s:v>2043.3</s:v>
       </s:c>
@@ -2169,7 +2229,9 @@
       <s:c r="D32" s="12" t="n">
         <s:v>28267.4</s:v>
       </s:c>
-      <s:c r="E32" s="13"/>
+      <s:c r="E32" s="13" t="n">
+        <s:v>5608.12</s:v>
+      </s:c>
       <s:c r="F32" s="14" t="n">
         <s:v>2296.3</s:v>
       </s:c>
@@ -2195,7 +2257,9 @@
       <s:c r="D33" s="12" t="n">
         <s:v>28802.3</s:v>
       </s:c>
-      <s:c r="E33" s="13"/>
+      <s:c r="E33" s="13" t="n">
+        <s:v>4775.68</s:v>
+      </s:c>
       <s:c r="F33" s="14" t="n">
         <s:v>2643.8</s:v>
       </s:c>
@@ -2221,7 +2285,9 @@
       <s:c r="D34" s="12" t="n">
         <s:v>29240.9</s:v>
       </s:c>
-      <s:c r="E34" s="13"/>
+      <s:c r="E34" s="13" t="n">
+        <s:v>4581.85</s:v>
+      </s:c>
       <s:c r="F34" s="14" t="n">
         <s:v>3355.7</s:v>
       </s:c>
@@ -2247,7 +2313,9 @@
       <s:c r="D35" s="12" t="n">
         <s:v>29328.4</s:v>
       </s:c>
-      <s:c r="E35" s="13"/>
+      <s:c r="E35" s="13" t="n">
+        <s:v>4622.1</s:v>
+      </s:c>
       <s:c r="F35" s="14" t="n">
         <s:v>4020.4</s:v>
       </s:c>
@@ -2273,7 +2341,9 @@
       <s:c r="D36" s="12" t="n">
         <s:v>28885.1</s:v>
       </s:c>
-      <s:c r="E36" s="13"/>
+      <s:c r="E36" s="13" t="n">
+        <s:v>4654.35</s:v>
+      </s:c>
       <s:c r="F36" s="14" t="n">
         <s:v>4733.9</s:v>
       </s:c>
@@ -2299,7 +2369,9 @@
       <s:c r="D37" s="12" t="n">
         <s:v>28557.5</s:v>
       </s:c>
-      <s:c r="E37" s="13"/>
+      <s:c r="E37" s="13" t="n">
+        <s:v>4683.82</s:v>
+      </s:c>
       <s:c r="F37" s="14" t="n">
         <s:v>5073.8</s:v>
       </s:c>
@@ -2325,7 +2397,9 @@
       <s:c r="D38" s="12" t="n">
         <s:v>28532.7</s:v>
       </s:c>
-      <s:c r="E38" s="13"/>
+      <s:c r="E38" s="13" t="n">
+        <s:v>4707.93</s:v>
+      </s:c>
       <s:c r="F38" s="14" t="n">
         <s:v>5878.9</s:v>
       </s:c>
@@ -2351,7 +2425,9 @@
       <s:c r="D39" s="12" t="n">
         <s:v>27415</s:v>
       </s:c>
-      <s:c r="E39" s="13"/>
+      <s:c r="E39" s="13" t="n">
+        <s:v>4746.84</s:v>
+      </s:c>
       <s:c r="F39" s="14" t="n">
         <s:v>6676.7</s:v>
       </s:c>
@@ -2377,7 +2453,9 @@
       <s:c r="D40" s="12" t="n">
         <s:v>27244.4</s:v>
       </s:c>
-      <s:c r="E40" s="13"/>
+      <s:c r="E40" s="13" t="n">
+        <s:v>4778.85</s:v>
+      </s:c>
       <s:c r="F40" s="14" t="n">
         <s:v>7182.1</s:v>
       </s:c>
@@ -2403,7 +2481,9 @@
       <s:c r="D41" s="12" t="n">
         <s:v>27072.8</s:v>
       </s:c>
-      <s:c r="E41" s="13"/>
+      <s:c r="E41" s="13" t="n">
+        <s:v>4796.25</s:v>
+      </s:c>
       <s:c r="F41" s="14" t="n">
         <s:v>7382.1</s:v>
       </s:c>
@@ -2429,7 +2509,9 @@
       <s:c r="D42" s="12" t="n">
         <s:v>26415.9</s:v>
       </s:c>
-      <s:c r="E42" s="13"/>
+      <s:c r="E42" s="13" t="n">
+        <s:v>4821.69</s:v>
+      </s:c>
       <s:c r="F42" s="14" t="n">
         <s:v>7884.7</s:v>
       </s:c>
@@ -2455,7 +2537,9 @@
       <s:c r="D43" s="12" t="n">
         <s:v>26228.2</s:v>
       </s:c>
-      <s:c r="E43" s="13"/>
+      <s:c r="E43" s="13" t="n">
+        <s:v>4838.07</s:v>
+      </s:c>
       <s:c r="F43" s="14" t="n">
         <s:v>8243.5</s:v>
       </s:c>
@@ -2481,7 +2565,9 @@
       <s:c r="D44" s="12" t="n">
         <s:v>26207.1</s:v>
       </s:c>
-      <s:c r="E44" s="13"/>
+      <s:c r="E44" s="13" t="n">
+        <s:v>4859.67</s:v>
+      </s:c>
       <s:c r="F44" s="14" t="n">
         <s:v>8357.2</s:v>
       </s:c>
@@ -2507,7 +2593,9 @@
       <s:c r="D45" s="12" t="n">
         <s:v>26748.1</s:v>
       </s:c>
-      <s:c r="E45" s="13"/>
+      <s:c r="E45" s="13" t="n">
+        <s:v>4876.35</s:v>
+      </s:c>
       <s:c r="F45" s="14" t="n">
         <s:v>8446.2</s:v>
       </s:c>
@@ -2533,7 +2621,9 @@
       <s:c r="D46" s="12" t="n">
         <s:v>26888.2</s:v>
       </s:c>
-      <s:c r="E46" s="13"/>
+      <s:c r="E46" s="13" t="n">
+        <s:v>4882.67</s:v>
+      </s:c>
       <s:c r="F46" s="14" t="n">
         <s:v>8642.1</s:v>
       </s:c>
@@ -2559,7 +2649,9 @@
       <s:c r="D47" s="12" t="n">
         <s:v>26325.9</s:v>
       </s:c>
-      <s:c r="E47" s="13"/>
+      <s:c r="E47" s="13" t="n">
+        <s:v>4906.37</s:v>
+      </s:c>
       <s:c r="F47" s="14" t="n">
         <s:v>8645.7</s:v>
       </s:c>
@@ -2585,7 +2677,9 @@
       <s:c r="D48" s="12" t="n">
         <s:v>25682.5</s:v>
       </s:c>
-      <s:c r="E48" s="13"/>
+      <s:c r="E48" s="13" t="n">
+        <s:v>4904.87</s:v>
+      </s:c>
       <s:c r="F48" s="14" t="n">
         <s:v>8777.9</s:v>
       </s:c>
@@ -2611,7 +2705,9 @@
       <s:c r="D49" s="12" t="n">
         <s:v>24785.9</s:v>
       </s:c>
-      <s:c r="E49" s="13"/>
+      <s:c r="E49" s="13" t="n">
+        <s:v>4902.02</s:v>
+      </s:c>
       <s:c r="F49" s="14" t="n">
         <s:v>8612.3</s:v>
       </s:c>
@@ -2637,7 +2733,9 @@
       <s:c r="D50" s="12" t="n">
         <s:v>27023</s:v>
       </s:c>
-      <s:c r="E50" s="13"/>
+      <s:c r="E50" s="13" t="n">
+        <s:v>4911.1</s:v>
+      </s:c>
       <s:c r="F50" s="14" t="n">
         <s:v>8772.9</s:v>
       </s:c>
@@ -2663,7 +2761,9 @@
       <s:c r="D51" s="12" t="n">
         <s:v>26792.1</s:v>
       </s:c>
-      <s:c r="E51" s="13"/>
+      <s:c r="E51" s="13" t="n">
+        <s:v>4902.27</s:v>
+      </s:c>
       <s:c r="F51" s="14" t="n">
         <s:v>8947.1</s:v>
       </s:c>
@@ -2689,7 +2789,9 @@
       <s:c r="D52" s="12" t="n">
         <s:v>26083.3</s:v>
       </s:c>
-      <s:c r="E52" s="13"/>
+      <s:c r="E52" s="13" t="n">
+        <s:v>4914.27</s:v>
+      </s:c>
       <s:c r="F52" s="14" t="n">
         <s:v>8675</s:v>
       </s:c>
@@ -2715,7 +2817,9 @@
       <s:c r="D53" s="12" t="n">
         <s:v>26138.9</s:v>
       </s:c>
-      <s:c r="E53" s="13"/>
+      <s:c r="E53" s="13" t="n">
+        <s:v>4907.39</s:v>
+      </s:c>
       <s:c r="F53" s="14" t="n">
         <s:v>8850.3</s:v>
       </s:c>
@@ -2741,7 +2845,9 @@
       <s:c r="D54" s="12" t="n">
         <s:v>26527.2</s:v>
       </s:c>
-      <s:c r="E54" s="13"/>
+      <s:c r="E54" s="13" t="n">
+        <s:v>4900.48</s:v>
+      </s:c>
       <s:c r="F54" s="14" t="n">
         <s:v>8986.7</s:v>
       </s:c>
@@ -2767,7 +2873,9 @@
       <s:c r="D55" s="12" t="n">
         <s:v>26820</s:v>
       </s:c>
-      <s:c r="E55" s="13"/>
+      <s:c r="E55" s="13" t="n">
+        <s:v>4891.88</s:v>
+      </s:c>
       <s:c r="F55" s="14" t="n">
         <s:v>8852.2</s:v>
       </s:c>
@@ -2793,7 +2901,9 @@
       <s:c r="D56" s="12" t="n">
         <s:v>27560.7</s:v>
       </s:c>
-      <s:c r="E56" s="13"/>
+      <s:c r="E56" s="13" t="n">
+        <s:v>4880.62</s:v>
+      </s:c>
       <s:c r="F56" s="14" t="n">
         <s:v>8165.3</s:v>
       </s:c>
@@ -2819,7 +2929,9 @@
       <s:c r="D57" s="12" t="n">
         <s:v>27265.2</s:v>
       </s:c>
-      <s:c r="E57" s="13"/>
+      <s:c r="E57" s="13" t="n">
+        <s:v>4874.53</s:v>
+      </s:c>
       <s:c r="F57" s="14" t="n">
         <s:v>8037.5</s:v>
       </s:c>
@@ -2845,7 +2957,9 @@
       <s:c r="D58" s="12" t="n">
         <s:v>27517</s:v>
       </s:c>
-      <s:c r="E58" s="13"/>
+      <s:c r="E58" s="13" t="n">
+        <s:v>5077.09</s:v>
+      </s:c>
       <s:c r="F58" s="14" t="n">
         <s:v>7561</s:v>
       </s:c>
@@ -2871,7 +2985,9 @@
       <s:c r="D59" s="12" t="n">
         <s:v>28435</s:v>
       </s:c>
-      <s:c r="E59" s="13"/>
+      <s:c r="E59" s="13" t="n">
+        <s:v>5338.38</s:v>
+      </s:c>
       <s:c r="F59" s="14" t="n">
         <s:v>6980.8</s:v>
       </s:c>
@@ -2897,7 +3013,9 @@
       <s:c r="D60" s="12" t="n">
         <s:v>29114.9</s:v>
       </s:c>
-      <s:c r="E60" s="13"/>
+      <s:c r="E60" s="13" t="n">
+        <s:v>5339.27</s:v>
+      </s:c>
       <s:c r="F60" s="14" t="n">
         <s:v>6547.5</s:v>
       </s:c>
@@ -2923,7 +3041,9 @@
       <s:c r="D61" s="12" t="n">
         <s:v>29432.8</s:v>
       </s:c>
-      <s:c r="E61" s="13"/>
+      <s:c r="E61" s="13" t="n">
+        <s:v>5318.48</s:v>
+      </s:c>
       <s:c r="F61" s="14" t="n">
         <s:v>6010.7</s:v>
       </s:c>
@@ -2949,7 +3069,9 @@
       <s:c r="D62" s="12" t="n">
         <s:v>30062.1</s:v>
       </s:c>
-      <s:c r="E62" s="13"/>
+      <s:c r="E62" s="13" t="n">
+        <s:v>5286.04</s:v>
+      </s:c>
       <s:c r="F62" s="14" t="n">
         <s:v>5410.8</s:v>
       </s:c>
@@ -2975,7 +3097,9 @@
       <s:c r="D63" s="12" t="n">
         <s:v>30552.1</s:v>
       </s:c>
-      <s:c r="E63" s="13"/>
+      <s:c r="E63" s="13" t="n">
+        <s:v>5464.74</s:v>
+      </s:c>
       <s:c r="F63" s="14" t="n">
         <s:v>5059.8</s:v>
       </s:c>
@@ -3001,7 +3125,9 @@
       <s:c r="D64" s="12" t="n">
         <s:v>31129.6</s:v>
       </s:c>
-      <s:c r="E64" s="13"/>
+      <s:c r="E64" s="13" t="n">
+        <s:v>5637.73</s:v>
+      </s:c>
       <s:c r="F64" s="14" t="n">
         <s:v>5051.3</s:v>
       </s:c>
@@ -3027,7 +3153,9 @@
       <s:c r="D65" s="12" t="n">
         <s:v>31212.2</s:v>
       </s:c>
-      <s:c r="E65" s="13"/>
+      <s:c r="E65" s="13" t="n">
+        <s:v>5772.16</s:v>
+      </s:c>
       <s:c r="F65" s="14" t="n">
         <s:v>4499.4</s:v>
       </s:c>
@@ -3053,7 +3181,9 @@
       <s:c r="D66" s="12" t="n">
         <s:v>31586.6</s:v>
       </s:c>
-      <s:c r="E66" s="13"/>
+      <s:c r="E66" s="13" t="n">
+        <s:v>6022.23</s:v>
+      </s:c>
       <s:c r="F66" s="14" t="n">
         <s:v>4350.2</s:v>
       </s:c>
@@ -3079,7 +3209,9 @@
       <s:c r="D67" s="12" t="n">
         <s:v>32184.1</s:v>
       </s:c>
-      <s:c r="E67" s="13"/>
+      <s:c r="E67" s="13" t="n">
+        <s:v>6117.26</s:v>
+      </s:c>
       <s:c r="F67" s="14" t="n">
         <s:v>3673.6</s:v>
       </s:c>
@@ -3105,7 +3237,9 @@
       <s:c r="D68" s="12" t="n">
         <s:v>32541.9</s:v>
       </s:c>
-      <s:c r="E68" s="13"/>
+      <s:c r="E68" s="13" t="n">
+        <s:v>6711.77</s:v>
+      </s:c>
       <s:c r="F68" s="14" t="n">
         <s:v>3257.6</s:v>
       </s:c>
@@ -3131,7 +3265,9 @@
       <s:c r="D69" s="12" t="n">
         <s:v>33563.4</s:v>
       </s:c>
-      <s:c r="E69" s="13"/>
+      <s:c r="E69" s="13" t="n">
+        <s:v>7297.05</s:v>
+      </s:c>
       <s:c r="F69" s="14" t="n">
         <s:v>2852.3</s:v>
       </s:c>
@@ -3157,7 +3293,9 @@
       <s:c r="D70" s="12" t="n">
         <s:v>33889.8</s:v>
       </s:c>
-      <s:c r="E70" s="13"/>
+      <s:c r="E70" s="13" t="n">
+        <s:v>7889.85</s:v>
+      </s:c>
       <s:c r="F70" s="14" t="n">
         <s:v>2477.8</s:v>
       </s:c>
@@ -3183,7 +3321,9 @@
       <s:c r="D71" s="12" t="n">
         <s:v>34305</s:v>
       </s:c>
-      <s:c r="E71" s="13"/>
+      <s:c r="E71" s="13" t="n">
+        <s:v>8481.67</s:v>
+      </s:c>
       <s:c r="F71" s="14" t="n">
         <s:v>2112.5</s:v>
       </s:c>
@@ -3209,7 +3349,9 @@
       <s:c r="D72" s="12" t="n">
         <s:v>34891.1</s:v>
       </s:c>
-      <s:c r="E72" s="13"/>
+      <s:c r="E72" s="13" t="n">
+        <s:v>9070.59</s:v>
+      </s:c>
       <s:c r="F72" s="14" t="n">
         <s:v>1578.5</s:v>
       </s:c>
@@ -3235,7 +3377,9 @@
       <s:c r="D73" s="12" t="n">
         <s:v>35049.4</s:v>
       </s:c>
-      <s:c r="E73" s="13"/>
+      <s:c r="E73" s="13" t="n">
+        <s:v>9635.5</s:v>
+      </s:c>
       <s:c r="F73" s="14" t="n">
         <s:v>1178.5</s:v>
       </s:c>
@@ -3261,7 +3405,9 @@
       <s:c r="D74" s="12" t="n">
         <s:v>35238.5</s:v>
       </s:c>
-      <s:c r="E74" s="13"/>
+      <s:c r="E74" s="13" t="n">
+        <s:v>9980.66</s:v>
+      </s:c>
       <s:c r="F74" s="14" t="n">
         <s:v>827.9</s:v>
       </s:c>
@@ -3287,7 +3433,9 @@
       <s:c r="D75" s="12" t="n">
         <s:v>35413</s:v>
       </s:c>
-      <s:c r="E75" s="13"/>
+      <s:c r="E75" s="13" t="n">
+        <s:v>9958.31</s:v>
+      </s:c>
       <s:c r="F75" s="14" t="n">
         <s:v>514.7</s:v>
       </s:c>
@@ -3313,7 +3461,9 @@
       <s:c r="D76" s="12" t="n">
         <s:v>35118.6</s:v>
       </s:c>
-      <s:c r="E76" s="13"/>
+      <s:c r="E76" s="13" t="n">
+        <s:v>9941.3</s:v>
+      </s:c>
       <s:c r="F76" s="14" t="n">
         <s:v>319.6</s:v>
       </s:c>
@@ -3339,7 +3489,9 @@
       <s:c r="D77" s="12" t="n">
         <s:v>34993.9</s:v>
       </s:c>
-      <s:c r="E77" s="13"/>
+      <s:c r="E77" s="13" t="n">
+        <s:v>9931.43</s:v>
+      </s:c>
       <s:c r="F77" s="14" t="n">
         <s:v>265</s:v>
       </s:c>
@@ -3365,7 +3517,9 @@
       <s:c r="D78" s="12" t="n">
         <s:v>34853.9</s:v>
       </s:c>
-      <s:c r="E78" s="13"/>
+      <s:c r="E78" s="13" t="n">
+        <s:v>9921.49</s:v>
+      </s:c>
       <s:c r="F78" s="14" t="n">
         <s:v>292.1</s:v>
       </s:c>
@@ -3391,7 +3545,9 @@
       <s:c r="D79" s="12" t="n">
         <s:v>34995.4</s:v>
       </s:c>
-      <s:c r="E79" s="13"/>
+      <s:c r="E79" s="13" t="n">
+        <s:v>9919.72</s:v>
+      </s:c>
       <s:c r="F79" s="14" t="n">
         <s:v>343.9</s:v>
       </s:c>
@@ -3417,7 +3573,9 @@
       <s:c r="D80" s="12" t="n">
         <s:v>34418.9</s:v>
       </s:c>
-      <s:c r="E80" s="13"/>
+      <s:c r="E80" s="13" t="n">
+        <s:v>9920.36</s:v>
+      </s:c>
       <s:c r="F80" s="14" t="n">
         <s:v>363.7</s:v>
       </s:c>
@@ -3443,7 +3601,9 @@
       <s:c r="D81" s="12" t="n">
         <s:v>33826.1</s:v>
       </s:c>
-      <s:c r="E81" s="13"/>
+      <s:c r="E81" s="13" t="n">
+        <s:v>9822.14</s:v>
+      </s:c>
       <s:c r="F81" s="14" t="n">
         <s:v>359.1</s:v>
       </s:c>
@@ -3469,7 +3629,9 @@
       <s:c r="D82" s="12" t="n">
         <s:v>33916.4</s:v>
       </s:c>
-      <s:c r="E82" s="13"/>
+      <s:c r="E82" s="13" t="n">
+        <s:v>9567.94</s:v>
+      </s:c>
       <s:c r="F82" s="14" t="n">
         <s:v>331.4</s:v>
       </s:c>
@@ -3495,7 +3657,9 @@
       <s:c r="D83" s="12" t="n">
         <s:v>33357.3</s:v>
       </s:c>
-      <s:c r="E83" s="13"/>
+      <s:c r="E83" s="13" t="n">
+        <s:v>9417.11</s:v>
+      </s:c>
       <s:c r="F83" s="14" t="n">
         <s:v>329.7</s:v>
       </s:c>
@@ -3521,7 +3685,9 @@
       <s:c r="D84" s="12" t="n">
         <s:v>33518.2</s:v>
       </s:c>
-      <s:c r="E84" s="13"/>
+      <s:c r="E84" s="13" t="n">
+        <s:v>9417.26</s:v>
+      </s:c>
       <s:c r="F84" s="14" t="n">
         <s:v>372.8</s:v>
       </s:c>
@@ -3547,7 +3713,9 @@
       <s:c r="D85" s="12" t="n">
         <s:v>33300.1</s:v>
       </s:c>
-      <s:c r="E85" s="13"/>
+      <s:c r="E85" s="13" t="n">
+        <s:v>9416.86</s:v>
+      </s:c>
       <s:c r="F85" s="14" t="n">
         <s:v>409.1</s:v>
       </s:c>
@@ -3573,7 +3741,9 @@
       <s:c r="D86" s="12" t="n">
         <s:v>32939.3</s:v>
       </s:c>
-      <s:c r="E86" s="13"/>
+      <s:c r="E86" s="13" t="n">
+        <s:v>9408.44</s:v>
+      </s:c>
       <s:c r="F86" s="14" t="n">
         <s:v>459.4</s:v>
       </s:c>
@@ -3599,7 +3769,9 @@
       <s:c r="D87" s="12" t="n">
         <s:v>32399.6</s:v>
       </s:c>
-      <s:c r="E87" s="13"/>
+      <s:c r="E87" s="13" t="n">
+        <s:v>9413.19</s:v>
+      </s:c>
       <s:c r="F87" s="14" t="n">
         <s:v>497.7</s:v>
       </s:c>
@@ -3625,7 +3797,9 @@
       <s:c r="D88" s="12" t="n">
         <s:v>32052.5</s:v>
       </s:c>
-      <s:c r="E88" s="13"/>
+      <s:c r="E88" s="13" t="n">
+        <s:v>9418.36</s:v>
+      </s:c>
       <s:c r="F88" s="14" t="n">
         <s:v>532.5</s:v>
       </s:c>
@@ -3651,7 +3825,9 @@
       <s:c r="D89" s="12" t="n">
         <s:v>31683.4</s:v>
       </s:c>
-      <s:c r="E89" s="13"/>
+      <s:c r="E89" s="13" t="n">
+        <s:v>9423.49</s:v>
+      </s:c>
       <s:c r="F89" s="14" t="n">
         <s:v>556.3</s:v>
       </s:c>
@@ -3677,7 +3853,9 @@
       <s:c r="D90" s="12" t="n">
         <s:v>31413.7</s:v>
       </s:c>
-      <s:c r="E90" s="13"/>
+      <s:c r="E90" s="13" t="n">
+        <s:v>9378.42</s:v>
+      </s:c>
       <s:c r="F90" s="14" t="n">
         <s:v>558</s:v>
       </s:c>
@@ -3703,7 +3881,9 @@
       <s:c r="D91" s="12" t="n">
         <s:v>30987.5</s:v>
       </s:c>
-      <s:c r="E91" s="13"/>
+      <s:c r="E91" s="13" t="n">
+        <s:v>9384.97</s:v>
+      </s:c>
       <s:c r="F91" s="14" t="n">
         <s:v>568.7</s:v>
       </s:c>
@@ -3729,7 +3909,9 @@
       <s:c r="D92" s="12" t="n">
         <s:v>30675.1</s:v>
       </s:c>
-      <s:c r="E92" s="13"/>
+      <s:c r="E92" s="13" t="n">
+        <s:v>9389.53</s:v>
+      </s:c>
       <s:c r="F92" s="14" t="n">
         <s:v>571.5</s:v>
       </s:c>
@@ -3755,7 +3937,9 @@
       <s:c r="D93" s="12" t="n">
         <s:v>30375.9</s:v>
       </s:c>
-      <s:c r="E93" s="13"/>
+      <s:c r="E93" s="13" t="n">
+        <s:v>9395.98</s:v>
+      </s:c>
       <s:c r="F93" s="14" t="n">
         <s:v>585.3</s:v>
       </s:c>
@@ -3781,7 +3965,9 @@
       <s:c r="D94" s="12" t="n">
         <s:v>29731.9</s:v>
       </s:c>
-      <s:c r="E94" s="13"/>
+      <s:c r="E94" s="13" t="n">
+        <s:v>9401.49</s:v>
+      </s:c>
       <s:c r="F94" s="14" t="n">
         <s:v>590.3</s:v>
       </s:c>
@@ -3807,7 +3993,9 @@
       <s:c r="D95" s="12" t="n">
         <s:v>29192.5</s:v>
       </s:c>
-      <s:c r="E95" s="13"/>
+      <s:c r="E95" s="13" t="n">
+        <s:v>9405.07</s:v>
+      </s:c>
       <s:c r="F95" s="14" t="n">
         <s:v>602.6</s:v>
       </s:c>
@@ -3833,7 +4021,9 @@
       <s:c r="D96" s="12" t="n">
         <s:v>28482.2</s:v>
       </s:c>
-      <s:c r="E96" s="13"/>
+      <s:c r="E96" s="13" t="n">
+        <s:v>9406.68</s:v>
+      </s:c>
       <s:c r="F96" s="14" t="n">
         <s:v>627.8</s:v>
       </s:c>
@@ -3861,7 +4051,9 @@
       <s:c r="D97" s="12" t="n">
         <s:v>28301.7</s:v>
       </s:c>
-      <s:c r="E97" s="13"/>
+      <s:c r="E97" s="13" t="n">
+        <s:v>9409.65</s:v>
+      </s:c>
       <s:c r="F97" s="14" t="n">
         <s:v>637.7</s:v>
       </s:c>
@@ -4052,36 +4244,16 @@
       <s:c r="E2" s="1" t="n">
         <s:v>394.08</s:v>
       </s:c>
-      <s:c r="F2" s="1" t="n">
-        <s:v>330</s:v>
-      </s:c>
-      <s:c r="G2" s="1" t="n">
-        <s:v>2387.17</s:v>
-      </s:c>
-      <s:c r="H2" s="1" t="n">
-        <s:v>0</s:v>
-      </s:c>
-      <s:c r="I2" s="1" t="n">
-        <s:v>3.7</s:v>
-      </s:c>
-      <s:c r="J2" s="1" t="n">
-        <s:v>0</s:v>
-      </s:c>
-      <s:c r="K2" s="1" t="n">
-        <s:v>0</s:v>
-      </s:c>
-      <s:c r="L2" s="1" t="n">
-        <s:v>0</s:v>
-      </s:c>
-      <s:c r="M2" s="1" t="n">
-        <s:v>0</s:v>
-      </s:c>
-      <s:c r="N2" s="1" t="n">
-        <s:v>17202.78</s:v>
-      </s:c>
-      <s:c r="O2" s="1" t="n">
-        <s:v>1084.75</s:v>
-      </s:c>
+      <s:c r="F2" s="1"/>
+      <s:c r="G2" s="1"/>
+      <s:c r="H2" s="1"/>
+      <s:c r="I2" s="1"/>
+      <s:c r="J2" s="1"/>
+      <s:c r="K2" s="1"/>
+      <s:c r="L2" s="1"/>
+      <s:c r="M2" s="1"/>
+      <s:c r="N2" s="1"/>
+      <s:c r="O2" s="1"/>
       <s:c r="P2" s="1" t="n">
         <s:v>69</s:v>
       </s:c>
@@ -4102,36 +4274,16 @@
       <s:c r="E3" s="1" t="n">
         <s:v>395.35</s:v>
       </s:c>
-      <s:c r="F3" s="1" t="n">
-        <s:v>600</s:v>
-      </s:c>
-      <s:c r="G3" s="1" t="n">
-        <s:v>2363.69</s:v>
-      </s:c>
-      <s:c r="H3" s="1" t="n">
-        <s:v>0</s:v>
-      </s:c>
-      <s:c r="I3" s="1" t="n">
-        <s:v>3.7</s:v>
-      </s:c>
-      <s:c r="J3" s="1" t="n">
-        <s:v>0</s:v>
-      </s:c>
-      <s:c r="K3" s="1" t="n">
-        <s:v>0</s:v>
-      </s:c>
-      <s:c r="L3" s="1" t="n">
-        <s:v>0</s:v>
-      </s:c>
-      <s:c r="M3" s="1" t="n">
-        <s:v>0</s:v>
-      </s:c>
-      <s:c r="N3" s="1" t="n">
-        <s:v>17141.21</s:v>
-      </s:c>
-      <s:c r="O3" s="1" t="n">
-        <s:v>1007.4</s:v>
-      </s:c>
+      <s:c r="F3" s="1"/>
+      <s:c r="G3" s="1"/>
+      <s:c r="H3" s="1"/>
+      <s:c r="I3" s="1"/>
+      <s:c r="J3" s="1"/>
+      <s:c r="K3" s="1"/>
+      <s:c r="L3" s="1"/>
+      <s:c r="M3" s="1"/>
+      <s:c r="N3" s="1"/>
+      <s:c r="O3" s="1"/>
       <s:c r="P3" s="1" t="n">
         <s:v>69</s:v>
       </s:c>
@@ -4152,36 +4304,16 @@
       <s:c r="E4" s="1" t="n">
         <s:v>384.72</s:v>
       </s:c>
-      <s:c r="F4" s="1" t="n">
-        <s:v>960</s:v>
-      </s:c>
-      <s:c r="G4" s="1" t="n">
-        <s:v>2363.31</s:v>
-      </s:c>
-      <s:c r="H4" s="1" t="n">
-        <s:v>0</s:v>
-      </s:c>
-      <s:c r="I4" s="1" t="n">
-        <s:v>3.7</s:v>
-      </s:c>
-      <s:c r="J4" s="1" t="n">
-        <s:v>0</s:v>
-      </s:c>
-      <s:c r="K4" s="1" t="n">
-        <s:v>0</s:v>
-      </s:c>
-      <s:c r="L4" s="1" t="n">
-        <s:v>0</s:v>
-      </s:c>
-      <s:c r="M4" s="1" t="n">
-        <s:v>0</s:v>
-      </s:c>
-      <s:c r="N4" s="1" t="n">
-        <s:v>16727.19</s:v>
-      </s:c>
-      <s:c r="O4" s="1" t="n">
-        <s:v>850.6</s:v>
-      </s:c>
+      <s:c r="F4" s="1"/>
+      <s:c r="G4" s="1"/>
+      <s:c r="H4" s="1"/>
+      <s:c r="I4" s="1"/>
+      <s:c r="J4" s="1"/>
+      <s:c r="K4" s="1"/>
+      <s:c r="L4" s="1"/>
+      <s:c r="M4" s="1"/>
+      <s:c r="N4" s="1"/>
+      <s:c r="O4" s="1"/>
       <s:c r="P4" s="1" t="n">
         <s:v>69</s:v>
       </s:c>
@@ -4202,36 +4334,16 @@
       <s:c r="E5" s="1" t="n">
         <s:v>384.42</s:v>
       </s:c>
-      <s:c r="F5" s="1" t="n">
-        <s:v>1010</s:v>
-      </s:c>
-      <s:c r="G5" s="1" t="n">
-        <s:v>2335.77</s:v>
-      </s:c>
-      <s:c r="H5" s="1" t="n">
-        <s:v>0</s:v>
-      </s:c>
-      <s:c r="I5" s="1" t="n">
-        <s:v>3.7</s:v>
-      </s:c>
-      <s:c r="J5" s="1" t="n">
-        <s:v>0</s:v>
-      </s:c>
-      <s:c r="K5" s="1" t="n">
-        <s:v>0</s:v>
-      </s:c>
-      <s:c r="L5" s="1" t="n">
-        <s:v>0</s:v>
-      </s:c>
-      <s:c r="M5" s="1" t="n">
-        <s:v>0</s:v>
-      </s:c>
-      <s:c r="N5" s="1" t="n">
-        <s:v>16563.72</s:v>
-      </s:c>
-      <s:c r="O5" s="1" t="n">
-        <s:v>752.22</s:v>
-      </s:c>
+      <s:c r="F5" s="1"/>
+      <s:c r="G5" s="1"/>
+      <s:c r="H5" s="1"/>
+      <s:c r="I5" s="1"/>
+      <s:c r="J5" s="1"/>
+      <s:c r="K5" s="1"/>
+      <s:c r="L5" s="1"/>
+      <s:c r="M5" s="1"/>
+      <s:c r="N5" s="1"/>
+      <s:c r="O5" s="1"/>
       <s:c r="P5" s="1" t="n">
         <s:v>69</s:v>
       </s:c>
@@ -4252,36 +4364,16 @@
       <s:c r="E6" s="1" t="n">
         <s:v>392.76</s:v>
       </s:c>
-      <s:c r="F6" s="1" t="n">
-        <s:v>1465</s:v>
-      </s:c>
-      <s:c r="G6" s="1" t="n">
-        <s:v>2340.46</s:v>
-      </s:c>
-      <s:c r="H6" s="1" t="n">
-        <s:v>0</s:v>
-      </s:c>
-      <s:c r="I6" s="1" t="n">
-        <s:v>3.7</s:v>
-      </s:c>
-      <s:c r="J6" s="1" t="n">
-        <s:v>0</s:v>
-      </s:c>
-      <s:c r="K6" s="1" t="n">
-        <s:v>265.4</s:v>
-      </s:c>
-      <s:c r="L6" s="1" t="n">
-        <s:v>0</s:v>
-      </s:c>
-      <s:c r="M6" s="1" t="n">
-        <s:v>0</s:v>
-      </s:c>
-      <s:c r="N6" s="1" t="n">
-        <s:v>17481.1</s:v>
-      </s:c>
-      <s:c r="O6" s="1" t="n">
-        <s:v>731.64</s:v>
-      </s:c>
+      <s:c r="F6" s="1"/>
+      <s:c r="G6" s="1"/>
+      <s:c r="H6" s="1"/>
+      <s:c r="I6" s="1"/>
+      <s:c r="J6" s="1"/>
+      <s:c r="K6" s="1"/>
+      <s:c r="L6" s="1"/>
+      <s:c r="M6" s="1"/>
+      <s:c r="N6" s="1"/>
+      <s:c r="O6" s="1"/>
       <s:c r="P6" s="1" t="n">
         <s:v>69</s:v>
       </s:c>
@@ -4302,36 +4394,16 @@
       <s:c r="E7" s="1" t="n">
         <s:v>395.57</s:v>
       </s:c>
-      <s:c r="F7" s="1" t="n">
-        <s:v>1490</s:v>
-      </s:c>
-      <s:c r="G7" s="1" t="n">
-        <s:v>2317.24</s:v>
-      </s:c>
-      <s:c r="H7" s="1" t="n">
-        <s:v>0</s:v>
-      </s:c>
-      <s:c r="I7" s="1" t="n">
-        <s:v>3.7</s:v>
-      </s:c>
-      <s:c r="J7" s="1" t="n">
-        <s:v>0</s:v>
-      </s:c>
-      <s:c r="K7" s="1" t="n">
-        <s:v>302.9</s:v>
-      </s:c>
-      <s:c r="L7" s="1" t="n">
-        <s:v>0</s:v>
-      </s:c>
-      <s:c r="M7" s="1" t="n">
-        <s:v>0</s:v>
-      </s:c>
-      <s:c r="N7" s="1" t="n">
-        <s:v>17857.19</s:v>
-      </s:c>
-      <s:c r="O7" s="1" t="n">
-        <s:v>644.88</s:v>
-      </s:c>
+      <s:c r="F7" s="1"/>
+      <s:c r="G7" s="1"/>
+      <s:c r="H7" s="1"/>
+      <s:c r="I7" s="1"/>
+      <s:c r="J7" s="1"/>
+      <s:c r="K7" s="1"/>
+      <s:c r="L7" s="1"/>
+      <s:c r="M7" s="1"/>
+      <s:c r="N7" s="1"/>
+      <s:c r="O7" s="1"/>
       <s:c r="P7" s="1" t="n">
         <s:v>69</s:v>
       </s:c>
@@ -4352,36 +4424,16 @@
       <s:c r="E8" s="1" t="n">
         <s:v>403.35</s:v>
       </s:c>
-      <s:c r="F8" s="1" t="n">
-        <s:v>1460</s:v>
-      </s:c>
-      <s:c r="G8" s="1" t="n">
-        <s:v>2292.9</s:v>
-      </s:c>
-      <s:c r="H8" s="1" t="n">
-        <s:v>0</s:v>
-      </s:c>
-      <s:c r="I8" s="1" t="n">
-        <s:v>3.7</s:v>
-      </s:c>
-      <s:c r="J8" s="1" t="n">
-        <s:v>0</s:v>
-      </s:c>
-      <s:c r="K8" s="1" t="n">
-        <s:v>302.2</s:v>
-      </s:c>
-      <s:c r="L8" s="1" t="n">
-        <s:v>0</s:v>
-      </s:c>
-      <s:c r="M8" s="1" t="n">
-        <s:v>0</s:v>
-      </s:c>
-      <s:c r="N8" s="1" t="n">
-        <s:v>17966.85</s:v>
-      </s:c>
-      <s:c r="O8" s="1" t="n">
-        <s:v>619.25</s:v>
-      </s:c>
+      <s:c r="F8" s="1"/>
+      <s:c r="G8" s="1"/>
+      <s:c r="H8" s="1"/>
+      <s:c r="I8" s="1"/>
+      <s:c r="J8" s="1"/>
+      <s:c r="K8" s="1"/>
+      <s:c r="L8" s="1"/>
+      <s:c r="M8" s="1"/>
+      <s:c r="N8" s="1"/>
+      <s:c r="O8" s="1"/>
       <s:c r="P8" s="1" t="n">
         <s:v>68</s:v>
       </s:c>
@@ -4402,36 +4454,16 @@
       <s:c r="E9" s="1" t="n">
         <s:v>393.85</s:v>
       </s:c>
-      <s:c r="F9" s="1" t="n">
-        <s:v>1337.7</s:v>
-      </s:c>
-      <s:c r="G9" s="1" t="n">
-        <s:v>2339.96</s:v>
-      </s:c>
-      <s:c r="H9" s="1" t="n">
-        <s:v>0</s:v>
-      </s:c>
-      <s:c r="I9" s="1" t="n">
-        <s:v>3.7</s:v>
-      </s:c>
-      <s:c r="J9" s="1" t="n">
-        <s:v>0</s:v>
-      </s:c>
-      <s:c r="K9" s="1" t="n">
-        <s:v>302.3</s:v>
-      </s:c>
-      <s:c r="L9" s="1" t="n">
-        <s:v>0</s:v>
-      </s:c>
-      <s:c r="M9" s="1" t="n">
-        <s:v>0</s:v>
-      </s:c>
-      <s:c r="N9" s="1" t="n">
-        <s:v>17215.68</s:v>
-      </s:c>
-      <s:c r="O9" s="1" t="n">
-        <s:v>602.26</s:v>
-      </s:c>
+      <s:c r="F9" s="1"/>
+      <s:c r="G9" s="1"/>
+      <s:c r="H9" s="1"/>
+      <s:c r="I9" s="1"/>
+      <s:c r="J9" s="1"/>
+      <s:c r="K9" s="1"/>
+      <s:c r="L9" s="1"/>
+      <s:c r="M9" s="1"/>
+      <s:c r="N9" s="1"/>
+      <s:c r="O9" s="1"/>
       <s:c r="P9" s="1" t="n">
         <s:v>68</s:v>
       </s:c>
@@ -4452,36 +4484,16 @@
       <s:c r="E10" s="1" t="n">
         <s:v>415.5</s:v>
       </s:c>
-      <s:c r="F10" s="1" t="n">
-        <s:v>842.7</s:v>
-      </s:c>
-      <s:c r="G10" s="1" t="n">
-        <s:v>2301.87</s:v>
-      </s:c>
-      <s:c r="H10" s="1" t="n">
-        <s:v>0</s:v>
-      </s:c>
-      <s:c r="I10" s="1" t="n">
-        <s:v>3.7</s:v>
-      </s:c>
-      <s:c r="J10" s="1" t="n">
-        <s:v>0</s:v>
-      </s:c>
-      <s:c r="K10" s="1" t="n">
-        <s:v>302.4</s:v>
-      </s:c>
-      <s:c r="L10" s="1" t="n">
-        <s:v>0</s:v>
-      </s:c>
-      <s:c r="M10" s="1" t="n">
-        <s:v>0</s:v>
-      </s:c>
-      <s:c r="N10" s="1" t="n">
-        <s:v>17866.76</s:v>
-      </s:c>
-      <s:c r="O10" s="1" t="n">
-        <s:v>526.57</s:v>
-      </s:c>
+      <s:c r="F10" s="1"/>
+      <s:c r="G10" s="1"/>
+      <s:c r="H10" s="1"/>
+      <s:c r="I10" s="1"/>
+      <s:c r="J10" s="1"/>
+      <s:c r="K10" s="1"/>
+      <s:c r="L10" s="1"/>
+      <s:c r="M10" s="1"/>
+      <s:c r="N10" s="1"/>
+      <s:c r="O10" s="1"/>
       <s:c r="P10" s="1" t="n">
         <s:v>67</s:v>
       </s:c>
@@ -4502,36 +4514,16 @@
       <s:c r="E11" s="1" t="n">
         <s:v>405.63</s:v>
       </s:c>
-      <s:c r="F11" s="1" t="n">
-        <s:v>440</s:v>
-      </s:c>
-      <s:c r="G11" s="1" t="n">
-        <s:v>2353.08</s:v>
-      </s:c>
-      <s:c r="H11" s="1" t="n">
-        <s:v>0</s:v>
-      </s:c>
-      <s:c r="I11" s="1" t="n">
-        <s:v>3.7</s:v>
-      </s:c>
-      <s:c r="J11" s="1" t="n">
-        <s:v>0</s:v>
-      </s:c>
-      <s:c r="K11" s="1" t="n">
-        <s:v>300</s:v>
-      </s:c>
-      <s:c r="L11" s="1" t="n">
-        <s:v>0</s:v>
-      </s:c>
-      <s:c r="M11" s="1" t="n">
-        <s:v>0</s:v>
-      </s:c>
-      <s:c r="N11" s="1" t="n">
-        <s:v>17787.37</s:v>
-      </s:c>
-      <s:c r="O11" s="1" t="n">
-        <s:v>518.06</s:v>
-      </s:c>
+      <s:c r="F11" s="1"/>
+      <s:c r="G11" s="1"/>
+      <s:c r="H11" s="1"/>
+      <s:c r="I11" s="1"/>
+      <s:c r="J11" s="1"/>
+      <s:c r="K11" s="1"/>
+      <s:c r="L11" s="1"/>
+      <s:c r="M11" s="1"/>
+      <s:c r="N11" s="1"/>
+      <s:c r="O11" s="1"/>
       <s:c r="P11" s="1" t="n">
         <s:v>66</s:v>
       </s:c>
@@ -4552,36 +4544,16 @@
       <s:c r="E12" s="1" t="n">
         <s:v>403.98</s:v>
       </s:c>
-      <s:c r="F12" s="1" t="n">
-        <s:v>170</s:v>
-      </s:c>
-      <s:c r="G12" s="1" t="n">
-        <s:v>2369.05</s:v>
-      </s:c>
-      <s:c r="H12" s="1" t="n">
-        <s:v>0</s:v>
-      </s:c>
-      <s:c r="I12" s="1" t="n">
-        <s:v>3.7</s:v>
-      </s:c>
-      <s:c r="J12" s="1" t="n">
-        <s:v>0</s:v>
-      </s:c>
-      <s:c r="K12" s="1" t="n">
-        <s:v>496.3</s:v>
-      </s:c>
-      <s:c r="L12" s="1" t="n">
-        <s:v>0</s:v>
-      </s:c>
-      <s:c r="M12" s="1" t="n">
-        <s:v>0</s:v>
-      </s:c>
-      <s:c r="N12" s="1" t="n">
-        <s:v>17488.32</s:v>
-      </s:c>
-      <s:c r="O12" s="1" t="n">
-        <s:v>502.43</s:v>
-      </s:c>
+      <s:c r="F12" s="1"/>
+      <s:c r="G12" s="1"/>
+      <s:c r="H12" s="1"/>
+      <s:c r="I12" s="1"/>
+      <s:c r="J12" s="1"/>
+      <s:c r="K12" s="1"/>
+      <s:c r="L12" s="1"/>
+      <s:c r="M12" s="1"/>
+      <s:c r="N12" s="1"/>
+      <s:c r="O12" s="1"/>
       <s:c r="P12" s="1" t="n">
         <s:v>66</s:v>
       </s:c>
@@ -4602,36 +4574,16 @@
       <s:c r="E13" s="1" t="n">
         <s:v>400.54</s:v>
       </s:c>
-      <s:c r="F13" s="1" t="n">
-        <s:v>170</s:v>
-      </s:c>
-      <s:c r="G13" s="1" t="n">
-        <s:v>2395.73</s:v>
-      </s:c>
-      <s:c r="H13" s="1" t="n">
-        <s:v>0</s:v>
-      </s:c>
-      <s:c r="I13" s="1" t="n">
-        <s:v>3.7</s:v>
-      </s:c>
-      <s:c r="J13" s="1" t="n">
-        <s:v>0</s:v>
-      </s:c>
-      <s:c r="K13" s="1" t="n">
-        <s:v>251</s:v>
-      </s:c>
-      <s:c r="L13" s="1" t="n">
-        <s:v>0</s:v>
-      </s:c>
-      <s:c r="M13" s="1" t="n">
-        <s:v>0</s:v>
-      </s:c>
-      <s:c r="N13" s="1" t="n">
-        <s:v>17211.88</s:v>
-      </s:c>
-      <s:c r="O13" s="1" t="n">
-        <s:v>470.29</s:v>
-      </s:c>
+      <s:c r="F13" s="1"/>
+      <s:c r="G13" s="1"/>
+      <s:c r="H13" s="1"/>
+      <s:c r="I13" s="1"/>
+      <s:c r="J13" s="1"/>
+      <s:c r="K13" s="1"/>
+      <s:c r="L13" s="1"/>
+      <s:c r="M13" s="1"/>
+      <s:c r="N13" s="1"/>
+      <s:c r="O13" s="1"/>
       <s:c r="P13" s="1" t="n">
         <s:v>66</s:v>
       </s:c>
@@ -4652,36 +4604,16 @@
       <s:c r="E14" s="1" t="n">
         <s:v>403.98</s:v>
       </s:c>
-      <s:c r="F14" s="1" t="n">
-        <s:v>0</s:v>
-      </s:c>
-      <s:c r="G14" s="1" t="n">
-        <s:v>2397.26</s:v>
-      </s:c>
-      <s:c r="H14" s="1" t="n">
-        <s:v>0</s:v>
-      </s:c>
-      <s:c r="I14" s="1" t="n">
-        <s:v>3.7</s:v>
-      </s:c>
-      <s:c r="J14" s="1" t="n">
-        <s:v>0</s:v>
-      </s:c>
-      <s:c r="K14" s="1" t="n">
-        <s:v>0</s:v>
-      </s:c>
-      <s:c r="L14" s="1" t="n">
-        <s:v>0</s:v>
-      </s:c>
-      <s:c r="M14" s="1" t="n">
-        <s:v>0</s:v>
-      </s:c>
-      <s:c r="N14" s="1" t="n">
-        <s:v>17508.07</s:v>
-      </s:c>
-      <s:c r="O14" s="1" t="n">
-        <s:v>458.67</s:v>
-      </s:c>
+      <s:c r="F14" s="1"/>
+      <s:c r="G14" s="1"/>
+      <s:c r="H14" s="1"/>
+      <s:c r="I14" s="1"/>
+      <s:c r="J14" s="1"/>
+      <s:c r="K14" s="1"/>
+      <s:c r="L14" s="1"/>
+      <s:c r="M14" s="1"/>
+      <s:c r="N14" s="1"/>
+      <s:c r="O14" s="1"/>
       <s:c r="P14" s="1" t="n">
         <s:v>66</s:v>
       </s:c>
@@ -4702,36 +4634,16 @@
       <s:c r="E15" s="1" t="n">
         <s:v>402.64</s:v>
       </s:c>
-      <s:c r="F15" s="1" t="n">
-        <s:v>0</s:v>
-      </s:c>
-      <s:c r="G15" s="1" t="n">
-        <s:v>2377.76</s:v>
-      </s:c>
-      <s:c r="H15" s="1" t="n">
-        <s:v>0</s:v>
-      </s:c>
-      <s:c r="I15" s="1" t="n">
-        <s:v>3.7</s:v>
-      </s:c>
-      <s:c r="J15" s="1" t="n">
-        <s:v>0</s:v>
-      </s:c>
-      <s:c r="K15" s="1" t="n">
-        <s:v>0</s:v>
-      </s:c>
-      <s:c r="L15" s="1" t="n">
-        <s:v>0</s:v>
-      </s:c>
-      <s:c r="M15" s="1" t="n">
-        <s:v>0</s:v>
-      </s:c>
-      <s:c r="N15" s="1" t="n">
-        <s:v>17321.57</s:v>
-      </s:c>
-      <s:c r="O15" s="1" t="n">
-        <s:v>443.17</s:v>
-      </s:c>
+      <s:c r="F15" s="1"/>
+      <s:c r="G15" s="1"/>
+      <s:c r="H15" s="1"/>
+      <s:c r="I15" s="1"/>
+      <s:c r="J15" s="1"/>
+      <s:c r="K15" s="1"/>
+      <s:c r="L15" s="1"/>
+      <s:c r="M15" s="1"/>
+      <s:c r="N15" s="1"/>
+      <s:c r="O15" s="1"/>
       <s:c r="P15" s="1" t="n">
         <s:v>66</s:v>
       </s:c>
@@ -4752,36 +4664,16 @@
       <s:c r="E16" s="1" t="n">
         <s:v>395.85</s:v>
       </s:c>
-      <s:c r="F16" s="1" t="n">
-        <s:v>0</s:v>
-      </s:c>
-      <s:c r="G16" s="1" t="n">
-        <s:v>2381.52</s:v>
-      </s:c>
-      <s:c r="H16" s="1" t="n">
-        <s:v>0</s:v>
-      </s:c>
-      <s:c r="I16" s="1" t="n">
-        <s:v>3.7</s:v>
-      </s:c>
-      <s:c r="J16" s="1" t="n">
-        <s:v>0</s:v>
-      </s:c>
-      <s:c r="K16" s="1" t="n">
-        <s:v>0</s:v>
-      </s:c>
-      <s:c r="L16" s="1" t="n">
-        <s:v>0</s:v>
-      </s:c>
-      <s:c r="M16" s="1" t="n">
-        <s:v>0</s:v>
-      </s:c>
-      <s:c r="N16" s="1" t="n">
-        <s:v>17199.69</s:v>
-      </s:c>
-      <s:c r="O16" s="1" t="n">
-        <s:v>421.99</s:v>
-      </s:c>
+      <s:c r="F16" s="1"/>
+      <s:c r="G16" s="1"/>
+      <s:c r="H16" s="1"/>
+      <s:c r="I16" s="1"/>
+      <s:c r="J16" s="1"/>
+      <s:c r="K16" s="1"/>
+      <s:c r="L16" s="1"/>
+      <s:c r="M16" s="1"/>
+      <s:c r="N16" s="1"/>
+      <s:c r="O16" s="1"/>
       <s:c r="P16" s="1" t="n">
         <s:v>66</s:v>
       </s:c>
@@ -4802,36 +4694,16 @@
       <s:c r="E17" s="1" t="n">
         <s:v>395.45</s:v>
       </s:c>
-      <s:c r="F17" s="1" t="n">
-        <s:v>0</s:v>
-      </s:c>
-      <s:c r="G17" s="1" t="n">
-        <s:v>2356.08</s:v>
-      </s:c>
-      <s:c r="H17" s="1" t="n">
-        <s:v>0</s:v>
-      </s:c>
-      <s:c r="I17" s="1" t="n">
-        <s:v>3.7</s:v>
-      </s:c>
-      <s:c r="J17" s="1" t="n">
-        <s:v>0</s:v>
-      </s:c>
-      <s:c r="K17" s="1" t="n">
-        <s:v>0</s:v>
-      </s:c>
-      <s:c r="L17" s="1" t="n">
-        <s:v>0</s:v>
-      </s:c>
-      <s:c r="M17" s="1" t="n">
-        <s:v>0</s:v>
-      </s:c>
-      <s:c r="N17" s="1" t="n">
-        <s:v>17053.9</s:v>
-      </s:c>
-      <s:c r="O17" s="1" t="n">
-        <s:v>407.13</s:v>
-      </s:c>
+      <s:c r="F17" s="1"/>
+      <s:c r="G17" s="1"/>
+      <s:c r="H17" s="1"/>
+      <s:c r="I17" s="1"/>
+      <s:c r="J17" s="1"/>
+      <s:c r="K17" s="1"/>
+      <s:c r="L17" s="1"/>
+      <s:c r="M17" s="1"/>
+      <s:c r="N17" s="1"/>
+      <s:c r="O17" s="1"/>
       <s:c r="P17" s="1" t="n">
         <s:v>66</s:v>
       </s:c>
@@ -4852,36 +4724,16 @@
       <s:c r="E18" s="1" t="n">
         <s:v>395.7</s:v>
       </s:c>
-      <s:c r="F18" s="1" t="n">
-        <s:v>0</s:v>
-      </s:c>
-      <s:c r="G18" s="1" t="n">
-        <s:v>2358.55</s:v>
-      </s:c>
-      <s:c r="H18" s="1" t="n">
-        <s:v>0</s:v>
-      </s:c>
-      <s:c r="I18" s="1" t="n">
-        <s:v>3.7</s:v>
-      </s:c>
-      <s:c r="J18" s="1" t="n">
-        <s:v>0</s:v>
-      </s:c>
-      <s:c r="K18" s="1" t="n">
-        <s:v>0</s:v>
-      </s:c>
-      <s:c r="L18" s="1" t="n">
-        <s:v>0</s:v>
-      </s:c>
-      <s:c r="M18" s="1" t="n">
-        <s:v>0</s:v>
-      </s:c>
-      <s:c r="N18" s="1" t="n">
-        <s:v>17040</s:v>
-      </s:c>
-      <s:c r="O18" s="1" t="n">
-        <s:v>420.65</s:v>
-      </s:c>
+      <s:c r="F18" s="1"/>
+      <s:c r="G18" s="1"/>
+      <s:c r="H18" s="1"/>
+      <s:c r="I18" s="1"/>
+      <s:c r="J18" s="1"/>
+      <s:c r="K18" s="1"/>
+      <s:c r="L18" s="1"/>
+      <s:c r="M18" s="1"/>
+      <s:c r="N18" s="1"/>
+      <s:c r="O18" s="1"/>
       <s:c r="P18" s="1" t="n">
         <s:v>66</s:v>
       </s:c>
@@ -4902,36 +4754,16 @@
       <s:c r="E19" s="1" t="n">
         <s:v>394.6</s:v>
       </s:c>
-      <s:c r="F19" s="1" t="n">
-        <s:v>0</s:v>
-      </s:c>
-      <s:c r="G19" s="1" t="n">
-        <s:v>2393.06</s:v>
-      </s:c>
-      <s:c r="H19" s="1" t="n">
-        <s:v>0</s:v>
-      </s:c>
-      <s:c r="I19" s="1" t="n">
-        <s:v>3.7</s:v>
-      </s:c>
-      <s:c r="J19" s="1" t="n">
-        <s:v>0</s:v>
-      </s:c>
-      <s:c r="K19" s="1" t="n">
-        <s:v>0</s:v>
-      </s:c>
-      <s:c r="L19" s="1" t="n">
-        <s:v>0</s:v>
-      </s:c>
-      <s:c r="M19" s="1" t="n">
-        <s:v>0</s:v>
-      </s:c>
-      <s:c r="N19" s="1" t="n">
-        <s:v>16873.22</s:v>
-      </s:c>
-      <s:c r="O19" s="1" t="n">
-        <s:v>385.62</s:v>
-      </s:c>
+      <s:c r="F19" s="1"/>
+      <s:c r="G19" s="1"/>
+      <s:c r="H19" s="1"/>
+      <s:c r="I19" s="1"/>
+      <s:c r="J19" s="1"/>
+      <s:c r="K19" s="1"/>
+      <s:c r="L19" s="1"/>
+      <s:c r="M19" s="1"/>
+      <s:c r="N19" s="1"/>
+      <s:c r="O19" s="1"/>
       <s:c r="P19" s="1" t="n">
         <s:v>66</s:v>
       </s:c>
@@ -4952,36 +4784,16 @@
       <s:c r="E20" s="1" t="n">
         <s:v>394.61</s:v>
       </s:c>
-      <s:c r="F20" s="1" t="n">
-        <s:v>0</s:v>
-      </s:c>
-      <s:c r="G20" s="1" t="n">
-        <s:v>2392.07</s:v>
-      </s:c>
-      <s:c r="H20" s="1" t="n">
-        <s:v>0</s:v>
-      </s:c>
-      <s:c r="I20" s="1" t="n">
-        <s:v>3.7</s:v>
-      </s:c>
-      <s:c r="J20" s="1" t="n">
-        <s:v>0</s:v>
-      </s:c>
-      <s:c r="K20" s="1" t="n">
-        <s:v>0</s:v>
-      </s:c>
-      <s:c r="L20" s="1" t="n">
-        <s:v>0</s:v>
-      </s:c>
-      <s:c r="M20" s="1" t="n">
-        <s:v>0</s:v>
-      </s:c>
-      <s:c r="N20" s="1" t="n">
-        <s:v>16926.07</s:v>
-      </s:c>
-      <s:c r="O20" s="1" t="n">
-        <s:v>400.96</s:v>
-      </s:c>
+      <s:c r="F20" s="1"/>
+      <s:c r="G20" s="1"/>
+      <s:c r="H20" s="1"/>
+      <s:c r="I20" s="1"/>
+      <s:c r="J20" s="1"/>
+      <s:c r="K20" s="1"/>
+      <s:c r="L20" s="1"/>
+      <s:c r="M20" s="1"/>
+      <s:c r="N20" s="1"/>
+      <s:c r="O20" s="1"/>
       <s:c r="P20" s="1" t="n">
         <s:v>66</s:v>
       </s:c>
@@ -5002,36 +4814,16 @@
       <s:c r="E21" s="1" t="n">
         <s:v>395.45</s:v>
       </s:c>
-      <s:c r="F21" s="1" t="n">
-        <s:v>0</s:v>
-      </s:c>
-      <s:c r="G21" s="1" t="n">
-        <s:v>2377.27</s:v>
-      </s:c>
-      <s:c r="H21" s="1" t="n">
-        <s:v>0</s:v>
-      </s:c>
-      <s:c r="I21" s="1" t="n">
-        <s:v>3.7</s:v>
-      </s:c>
-      <s:c r="J21" s="1" t="n">
-        <s:v>0</s:v>
-      </s:c>
-      <s:c r="K21" s="1" t="n">
-        <s:v>0</s:v>
-      </s:c>
-      <s:c r="L21" s="1" t="n">
-        <s:v>0</s:v>
-      </s:c>
-      <s:c r="M21" s="1" t="n">
-        <s:v>0</s:v>
-      </s:c>
-      <s:c r="N21" s="1" t="n">
-        <s:v>16999.46</s:v>
-      </s:c>
-      <s:c r="O21" s="1" t="n">
-        <s:v>443.76</s:v>
-      </s:c>
+      <s:c r="F21" s="1"/>
+      <s:c r="G21" s="1"/>
+      <s:c r="H21" s="1"/>
+      <s:c r="I21" s="1"/>
+      <s:c r="J21" s="1"/>
+      <s:c r="K21" s="1"/>
+      <s:c r="L21" s="1"/>
+      <s:c r="M21" s="1"/>
+      <s:c r="N21" s="1"/>
+      <s:c r="O21" s="1"/>
       <s:c r="P21" s="1" t="n">
         <s:v>66</s:v>
       </s:c>
@@ -5052,36 +4844,16 @@
       <s:c r="E22" s="1" t="n">
         <s:v>395.85</s:v>
       </s:c>
-      <s:c r="F22" s="1" t="n">
-        <s:v>0</s:v>
-      </s:c>
-      <s:c r="G22" s="1" t="n">
-        <s:v>2385.81</s:v>
-      </s:c>
-      <s:c r="H22" s="1" t="n">
-        <s:v>0</s:v>
-      </s:c>
-      <s:c r="I22" s="1" t="n">
-        <s:v>3.7</s:v>
-      </s:c>
-      <s:c r="J22" s="1" t="n">
-        <s:v>0</s:v>
-      </s:c>
-      <s:c r="K22" s="1" t="n">
-        <s:v>0</s:v>
-      </s:c>
-      <s:c r="L22" s="1" t="n">
-        <s:v>0</s:v>
-      </s:c>
-      <s:c r="M22" s="1" t="n">
-        <s:v>0</s:v>
-      </s:c>
-      <s:c r="N22" s="1" t="n">
-        <s:v>17127.12</s:v>
-      </s:c>
-      <s:c r="O22" s="1" t="n">
-        <s:v>452.07</s:v>
-      </s:c>
+      <s:c r="F22" s="1"/>
+      <s:c r="G22" s="1"/>
+      <s:c r="H22" s="1"/>
+      <s:c r="I22" s="1"/>
+      <s:c r="J22" s="1"/>
+      <s:c r="K22" s="1"/>
+      <s:c r="L22" s="1"/>
+      <s:c r="M22" s="1"/>
+      <s:c r="N22" s="1"/>
+      <s:c r="O22" s="1"/>
       <s:c r="P22" s="1" t="n">
         <s:v>66</s:v>
       </s:c>
@@ -5102,36 +4874,16 @@
       <s:c r="E23" s="1" t="n">
         <s:v>403</s:v>
       </s:c>
-      <s:c r="F23" s="1" t="n">
-        <s:v>0</s:v>
-      </s:c>
-      <s:c r="G23" s="1" t="n">
-        <s:v>2379.22</s:v>
-      </s:c>
-      <s:c r="H23" s="1" t="n">
-        <s:v>0</s:v>
-      </s:c>
-      <s:c r="I23" s="1" t="n">
-        <s:v>3.73</s:v>
-      </s:c>
-      <s:c r="J23" s="1" t="n">
-        <s:v>0</s:v>
-      </s:c>
-      <s:c r="K23" s="1" t="n">
-        <s:v>0</s:v>
-      </s:c>
-      <s:c r="L23" s="1" t="n">
-        <s:v>0</s:v>
-      </s:c>
-      <s:c r="M23" s="1" t="n">
-        <s:v>0</s:v>
-      </s:c>
-      <s:c r="N23" s="1" t="n">
-        <s:v>17296.13</s:v>
-      </s:c>
-      <s:c r="O23" s="1" t="n">
-        <s:v>459.02</s:v>
-      </s:c>
+      <s:c r="F23" s="1"/>
+      <s:c r="G23" s="1"/>
+      <s:c r="H23" s="1"/>
+      <s:c r="I23" s="1"/>
+      <s:c r="J23" s="1"/>
+      <s:c r="K23" s="1"/>
+      <s:c r="L23" s="1"/>
+      <s:c r="M23" s="1"/>
+      <s:c r="N23" s="1"/>
+      <s:c r="O23" s="1"/>
       <s:c r="P23" s="1" t="n">
         <s:v>66</s:v>
       </s:c>
@@ -5152,36 +4904,16 @@
       <s:c r="E24" s="1" t="n">
         <s:v>404.32</s:v>
       </s:c>
-      <s:c r="F24" s="1" t="n">
-        <s:v>100</s:v>
-      </s:c>
-      <s:c r="G24" s="1" t="n">
-        <s:v>2383.38</s:v>
-      </s:c>
-      <s:c r="H24" s="1" t="n">
-        <s:v>0</s:v>
-      </s:c>
-      <s:c r="I24" s="1" t="n">
-        <s:v>42</s:v>
-      </s:c>
-      <s:c r="J24" s="1" t="n">
-        <s:v>0</s:v>
-      </s:c>
-      <s:c r="K24" s="1" t="n">
-        <s:v>0</s:v>
-      </s:c>
-      <s:c r="L24" s="1" t="n">
-        <s:v>0</s:v>
-      </s:c>
-      <s:c r="M24" s="1" t="n">
-        <s:v>0</s:v>
-      </s:c>
-      <s:c r="N24" s="1" t="n">
-        <s:v>17492.57</s:v>
-      </s:c>
-      <s:c r="O24" s="1" t="n">
-        <s:v>417.25</s:v>
-      </s:c>
+      <s:c r="F24" s="1"/>
+      <s:c r="G24" s="1"/>
+      <s:c r="H24" s="1"/>
+      <s:c r="I24" s="1"/>
+      <s:c r="J24" s="1"/>
+      <s:c r="K24" s="1"/>
+      <s:c r="L24" s="1"/>
+      <s:c r="M24" s="1"/>
+      <s:c r="N24" s="1"/>
+      <s:c r="O24" s="1"/>
       <s:c r="P24" s="1" t="n">
         <s:v>66</s:v>
       </s:c>
@@ -5202,36 +4934,16 @@
       <s:c r="E25" s="1" t="n">
         <s:v>416.55</s:v>
       </s:c>
-      <s:c r="F25" s="1" t="n">
-        <s:v>130</s:v>
-      </s:c>
-      <s:c r="G25" s="1" t="n">
-        <s:v>2365.26</s:v>
-      </s:c>
-      <s:c r="H25" s="1" t="n">
-        <s:v>0</s:v>
-      </s:c>
-      <s:c r="I25" s="1" t="n">
-        <s:v>139.05</s:v>
-      </s:c>
-      <s:c r="J25" s="1" t="n">
-        <s:v>0</s:v>
-      </s:c>
-      <s:c r="K25" s="1" t="n">
-        <s:v>0</s:v>
-      </s:c>
-      <s:c r="L25" s="1" t="n">
-        <s:v>0</s:v>
-      </s:c>
-      <s:c r="M25" s="1" t="n">
-        <s:v>0</s:v>
-      </s:c>
-      <s:c r="N25" s="1" t="n">
-        <s:v>17990</s:v>
-      </s:c>
-      <s:c r="O25" s="1" t="n">
-        <s:v>400</s:v>
-      </s:c>
+      <s:c r="F25" s="1"/>
+      <s:c r="G25" s="1"/>
+      <s:c r="H25" s="1"/>
+      <s:c r="I25" s="1"/>
+      <s:c r="J25" s="1"/>
+      <s:c r="K25" s="1"/>
+      <s:c r="L25" s="1"/>
+      <s:c r="M25" s="1"/>
+      <s:c r="N25" s="1"/>
+      <s:c r="O25" s="1"/>
       <s:c r="P25" s="1" t="n">
         <s:v>66</s:v>
       </s:c>
@@ -5252,36 +4964,16 @@
       <s:c r="E26" s="1" t="n">
         <s:v>423.39</s:v>
       </s:c>
-      <s:c r="F26" s="1" t="n">
-        <s:v>570</s:v>
-      </s:c>
-      <s:c r="G26" s="1" t="n">
-        <s:v>2373.38</s:v>
-      </s:c>
-      <s:c r="H26" s="1" t="n">
-        <s:v>0</s:v>
-      </s:c>
-      <s:c r="I26" s="1" t="n">
-        <s:v>290.87</s:v>
-      </s:c>
-      <s:c r="J26" s="1" t="n">
-        <s:v>0</s:v>
-      </s:c>
-      <s:c r="K26" s="1" t="n">
-        <s:v>0</s:v>
-      </s:c>
-      <s:c r="L26" s="1" t="n">
-        <s:v>0</s:v>
-      </s:c>
-      <s:c r="M26" s="1" t="n">
-        <s:v>0</s:v>
-      </s:c>
-      <s:c r="N26" s="1" t="n">
-        <s:v>18259.25</s:v>
-      </s:c>
-      <s:c r="O26" s="1" t="n">
-        <s:v>387.51</s:v>
-      </s:c>
+      <s:c r="F26" s="1"/>
+      <s:c r="G26" s="1"/>
+      <s:c r="H26" s="1"/>
+      <s:c r="I26" s="1"/>
+      <s:c r="J26" s="1"/>
+      <s:c r="K26" s="1"/>
+      <s:c r="L26" s="1"/>
+      <s:c r="M26" s="1"/>
+      <s:c r="N26" s="1"/>
+      <s:c r="O26" s="1"/>
       <s:c r="P26" s="1" t="n">
         <s:v>66</s:v>
       </s:c>
@@ -5302,36 +4994,16 @@
       <s:c r="E27" s="1" t="n">
         <s:v>440.54</s:v>
       </s:c>
-      <s:c r="F27" s="1" t="n">
-        <s:v>630</s:v>
-      </s:c>
-      <s:c r="G27" s="1" t="n">
-        <s:v>2379.71</s:v>
-      </s:c>
-      <s:c r="H27" s="1" t="n">
-        <s:v>0</s:v>
-      </s:c>
-      <s:c r="I27" s="1" t="n">
-        <s:v>577.93</s:v>
-      </s:c>
-      <s:c r="J27" s="1" t="n">
-        <s:v>0</s:v>
-      </s:c>
-      <s:c r="K27" s="1" t="n">
-        <s:v>0</s:v>
-      </s:c>
-      <s:c r="L27" s="1" t="n">
-        <s:v>0</s:v>
-      </s:c>
-      <s:c r="M27" s="1" t="n">
-        <s:v>0</s:v>
-      </s:c>
-      <s:c r="N27" s="1" t="n">
-        <s:v>18978.79</s:v>
-      </s:c>
-      <s:c r="O27" s="1" t="n">
-        <s:v>400.68</s:v>
-      </s:c>
+      <s:c r="F27" s="1"/>
+      <s:c r="G27" s="1"/>
+      <s:c r="H27" s="1"/>
+      <s:c r="I27" s="1"/>
+      <s:c r="J27" s="1"/>
+      <s:c r="K27" s="1"/>
+      <s:c r="L27" s="1"/>
+      <s:c r="M27" s="1"/>
+      <s:c r="N27" s="1"/>
+      <s:c r="O27" s="1"/>
       <s:c r="P27" s="1" t="n">
         <s:v>66</s:v>
       </s:c>
@@ -5352,36 +5024,16 @@
       <s:c r="E28" s="1" t="n">
         <s:v>453.6</s:v>
       </s:c>
-      <s:c r="F28" s="1" t="n">
-        <s:v>540</s:v>
-      </s:c>
-      <s:c r="G28" s="1" t="n">
-        <s:v>2367.53</s:v>
-      </s:c>
-      <s:c r="H28" s="1" t="n">
-        <s:v>0</s:v>
-      </s:c>
-      <s:c r="I28" s="1" t="n">
-        <s:v>889.03</s:v>
-      </s:c>
-      <s:c r="J28" s="1" t="n">
-        <s:v>0</s:v>
-      </s:c>
-      <s:c r="K28" s="1" t="n">
-        <s:v>0</s:v>
-      </s:c>
-      <s:c r="L28" s="1" t="n">
-        <s:v>0</s:v>
-      </s:c>
-      <s:c r="M28" s="1" t="n">
-        <s:v>0</s:v>
-      </s:c>
-      <s:c r="N28" s="1" t="n">
-        <s:v>18921.34</s:v>
-      </s:c>
-      <s:c r="O28" s="1" t="n">
-        <s:v>410.9</s:v>
-      </s:c>
+      <s:c r="F28" s="1"/>
+      <s:c r="G28" s="1"/>
+      <s:c r="H28" s="1"/>
+      <s:c r="I28" s="1"/>
+      <s:c r="J28" s="1"/>
+      <s:c r="K28" s="1"/>
+      <s:c r="L28" s="1"/>
+      <s:c r="M28" s="1"/>
+      <s:c r="N28" s="1"/>
+      <s:c r="O28" s="1"/>
       <s:c r="P28" s="1" t="n">
         <s:v>66</s:v>
       </s:c>
@@ -5402,36 +5054,16 @@
       <s:c r="E29" s="1" t="n">
         <s:v>360</s:v>
       </s:c>
-      <s:c r="F29" s="1" t="n">
-        <s:v>330</s:v>
-      </s:c>
-      <s:c r="G29" s="1" t="n">
-        <s:v>2403.8</s:v>
-      </s:c>
-      <s:c r="H29" s="1" t="n">
-        <s:v>0</s:v>
-      </s:c>
-      <s:c r="I29" s="1" t="n">
-        <s:v>1259.95</s:v>
-      </s:c>
-      <s:c r="J29" s="1" t="n">
-        <s:v>0</s:v>
-      </s:c>
-      <s:c r="K29" s="1" t="n">
-        <s:v>150.9</s:v>
-      </s:c>
-      <s:c r="L29" s="1" t="n">
-        <s:v>0</s:v>
-      </s:c>
-      <s:c r="M29" s="1" t="n">
-        <s:v>0</s:v>
-      </s:c>
-      <s:c r="N29" s="1" t="n">
-        <s:v>18181.72</s:v>
-      </s:c>
-      <s:c r="O29" s="1" t="n">
-        <s:v>409.83</s:v>
-      </s:c>
+      <s:c r="F29" s="1"/>
+      <s:c r="G29" s="1"/>
+      <s:c r="H29" s="1"/>
+      <s:c r="I29" s="1"/>
+      <s:c r="J29" s="1"/>
+      <s:c r="K29" s="1"/>
+      <s:c r="L29" s="1"/>
+      <s:c r="M29" s="1"/>
+      <s:c r="N29" s="1"/>
+      <s:c r="O29" s="1"/>
       <s:c r="P29" s="1" t="n">
         <s:v>66</s:v>
       </s:c>
@@ -5452,36 +5084,16 @@
       <s:c r="E30" s="1" t="n">
         <s:v>431.69</s:v>
       </s:c>
-      <s:c r="F30" s="1" t="n">
-        <s:v>70</s:v>
-      </s:c>
-      <s:c r="G30" s="1" t="n">
-        <s:v>2414.45</s:v>
-      </s:c>
-      <s:c r="H30" s="1" t="n">
-        <s:v>0</s:v>
-      </s:c>
-      <s:c r="I30" s="1" t="n">
-        <s:v>1633.95</s:v>
-      </s:c>
-      <s:c r="J30" s="1" t="n">
-        <s:v>0</s:v>
-      </s:c>
-      <s:c r="K30" s="1" t="n">
-        <s:v>151.1</s:v>
-      </s:c>
-      <s:c r="L30" s="1" t="n">
-        <s:v>0</s:v>
-      </s:c>
-      <s:c r="M30" s="1" t="n">
-        <s:v>0</s:v>
-      </s:c>
-      <s:c r="N30" s="1" t="n">
-        <s:v>18386.03</s:v>
-      </s:c>
-      <s:c r="O30" s="1" t="n">
-        <s:v>372.58</s:v>
-      </s:c>
+      <s:c r="F30" s="1"/>
+      <s:c r="G30" s="1"/>
+      <s:c r="H30" s="1"/>
+      <s:c r="I30" s="1"/>
+      <s:c r="J30" s="1"/>
+      <s:c r="K30" s="1"/>
+      <s:c r="L30" s="1"/>
+      <s:c r="M30" s="1"/>
+      <s:c r="N30" s="1"/>
+      <s:c r="O30" s="1"/>
       <s:c r="P30" s="1" t="n">
         <s:v>66</s:v>
       </s:c>
@@ -5502,36 +5114,16 @@
       <s:c r="E31" s="1" t="n">
         <s:v>428.2</s:v>
       </s:c>
-      <s:c r="F31" s="1" t="n">
-        <s:v>0</s:v>
-      </s:c>
-      <s:c r="G31" s="1" t="n">
-        <s:v>2453.35</s:v>
-      </s:c>
-      <s:c r="H31" s="1" t="n">
-        <s:v>0</s:v>
-      </s:c>
-      <s:c r="I31" s="1" t="n">
-        <s:v>2189.83</s:v>
-      </s:c>
-      <s:c r="J31" s="1" t="n">
-        <s:v>0</s:v>
-      </s:c>
-      <s:c r="K31" s="1" t="n">
-        <s:v>0</s:v>
-      </s:c>
-      <s:c r="L31" s="1" t="n">
-        <s:v>0</s:v>
-      </s:c>
-      <s:c r="M31" s="1" t="n">
-        <s:v>0</s:v>
-      </s:c>
-      <s:c r="N31" s="1" t="n">
-        <s:v>17910.92</s:v>
-      </s:c>
-      <s:c r="O31" s="1" t="n">
-        <s:v>330.2</s:v>
-      </s:c>
+      <s:c r="F31" s="1"/>
+      <s:c r="G31" s="1"/>
+      <s:c r="H31" s="1"/>
+      <s:c r="I31" s="1"/>
+      <s:c r="J31" s="1"/>
+      <s:c r="K31" s="1"/>
+      <s:c r="L31" s="1"/>
+      <s:c r="M31" s="1"/>
+      <s:c r="N31" s="1"/>
+      <s:c r="O31" s="1"/>
       <s:c r="P31" s="1" t="n">
         <s:v>66</s:v>
       </s:c>
@@ -5552,36 +5144,16 @@
       <s:c r="E32" s="1" t="n">
         <s:v>404.58</s:v>
       </s:c>
-      <s:c r="F32" s="1" t="n">
-        <s:v>0</s:v>
-      </s:c>
-      <s:c r="G32" s="1" t="n">
-        <s:v>2467.07</s:v>
-      </s:c>
-      <s:c r="H32" s="1" t="n">
-        <s:v>0</s:v>
-      </s:c>
-      <s:c r="I32" s="1" t="n">
-        <s:v>2676.07</s:v>
-      </s:c>
-      <s:c r="J32" s="1" t="n">
-        <s:v>0</s:v>
-      </s:c>
-      <s:c r="K32" s="1" t="n">
-        <s:v>0</s:v>
-      </s:c>
-      <s:c r="L32" s="1" t="n">
-        <s:v>0</s:v>
-      </s:c>
-      <s:c r="M32" s="1" t="n">
-        <s:v>0</s:v>
-      </s:c>
-      <s:c r="N32" s="1" t="n">
-        <s:v>16900.62</s:v>
-      </s:c>
-      <s:c r="O32" s="1" t="n">
-        <s:v>312.44</s:v>
-      </s:c>
+      <s:c r="F32" s="1"/>
+      <s:c r="G32" s="1"/>
+      <s:c r="H32" s="1"/>
+      <s:c r="I32" s="1"/>
+      <s:c r="J32" s="1"/>
+      <s:c r="K32" s="1"/>
+      <s:c r="L32" s="1"/>
+      <s:c r="M32" s="1"/>
+      <s:c r="N32" s="1"/>
+      <s:c r="O32" s="1"/>
       <s:c r="P32" s="1" t="n">
         <s:v>66</s:v>
       </s:c>
@@ -5602,36 +5174,16 @@
       <s:c r="E33" s="1" t="n">
         <s:v>394.75</s:v>
       </s:c>
-      <s:c r="F33" s="1" t="n">
-        <s:v>0</s:v>
-      </s:c>
-      <s:c r="G33" s="1" t="n">
-        <s:v>2537.84</s:v>
-      </s:c>
-      <s:c r="H33" s="1" t="n">
-        <s:v>0</s:v>
-      </s:c>
-      <s:c r="I33" s="1" t="n">
-        <s:v>3130.42</s:v>
-      </s:c>
-      <s:c r="J33" s="1" t="n">
-        <s:v>0</s:v>
-      </s:c>
-      <s:c r="K33" s="1" t="n">
-        <s:v>0</s:v>
-      </s:c>
-      <s:c r="L33" s="1" t="n">
-        <s:v>0</s:v>
-      </s:c>
-      <s:c r="M33" s="1" t="n">
-        <s:v>0</s:v>
-      </s:c>
-      <s:c r="N33" s="1" t="n">
-        <s:v>15855.94</s:v>
-      </s:c>
-      <s:c r="O33" s="1" t="n">
-        <s:v>295.9</s:v>
-      </s:c>
+      <s:c r="F33" s="1"/>
+      <s:c r="G33" s="1"/>
+      <s:c r="H33" s="1"/>
+      <s:c r="I33" s="1"/>
+      <s:c r="J33" s="1"/>
+      <s:c r="K33" s="1"/>
+      <s:c r="L33" s="1"/>
+      <s:c r="M33" s="1"/>
+      <s:c r="N33" s="1"/>
+      <s:c r="O33" s="1"/>
       <s:c r="P33" s="1" t="n">
         <s:v>66</s:v>
       </s:c>
@@ -5652,36 +5204,16 @@
       <s:c r="E34" s="1" t="n">
         <s:v>404.42</s:v>
       </s:c>
-      <s:c r="F34" s="1" t="n">
-        <s:v>0</s:v>
-      </s:c>
-      <s:c r="G34" s="1" t="n">
-        <s:v>2582.29</s:v>
-      </s:c>
-      <s:c r="H34" s="1" t="n">
-        <s:v>0</s:v>
-      </s:c>
-      <s:c r="I34" s="1" t="n">
-        <s:v>3611.5</s:v>
-      </s:c>
-      <s:c r="J34" s="1" t="n">
-        <s:v>0</s:v>
-      </s:c>
-      <s:c r="K34" s="1" t="n">
-        <s:v>0</s:v>
-      </s:c>
-      <s:c r="L34" s="1" t="n">
-        <s:v>0</s:v>
-      </s:c>
-      <s:c r="M34" s="1" t="n">
-        <s:v>0</s:v>
-      </s:c>
-      <s:c r="N34" s="1" t="n">
-        <s:v>15884.8</s:v>
-      </s:c>
-      <s:c r="O34" s="1" t="n">
-        <s:v>263.31</s:v>
-      </s:c>
+      <s:c r="F34" s="1"/>
+      <s:c r="G34" s="1"/>
+      <s:c r="H34" s="1"/>
+      <s:c r="I34" s="1"/>
+      <s:c r="J34" s="1"/>
+      <s:c r="K34" s="1"/>
+      <s:c r="L34" s="1"/>
+      <s:c r="M34" s="1"/>
+      <s:c r="N34" s="1"/>
+      <s:c r="O34" s="1"/>
       <s:c r="P34" s="1" t="n">
         <s:v>66</s:v>
       </s:c>
@@ -5702,36 +5234,16 @@
       <s:c r="E35" s="1" t="n">
         <s:v>404.95</s:v>
       </s:c>
-      <s:c r="F35" s="1" t="n">
-        <s:v>0</s:v>
-      </s:c>
-      <s:c r="G35" s="1" t="n">
-        <s:v>2593.45</s:v>
-      </s:c>
-      <s:c r="H35" s="1" t="n">
-        <s:v>0</s:v>
-      </s:c>
-      <s:c r="I35" s="1" t="n">
-        <s:v>4017.15</s:v>
-      </s:c>
-      <s:c r="J35" s="1" t="n">
-        <s:v>0</s:v>
-      </s:c>
-      <s:c r="K35" s="1" t="n">
-        <s:v>0</s:v>
-      </s:c>
-      <s:c r="L35" s="1" t="n">
-        <s:v>0</s:v>
-      </s:c>
-      <s:c r="M35" s="1" t="n">
-        <s:v>0</s:v>
-      </s:c>
-      <s:c r="N35" s="1" t="n">
-        <s:v>15201.67</s:v>
-      </s:c>
-      <s:c r="O35" s="1" t="n">
-        <s:v>227.43</s:v>
-      </s:c>
+      <s:c r="F35" s="1"/>
+      <s:c r="G35" s="1"/>
+      <s:c r="H35" s="1"/>
+      <s:c r="I35" s="1"/>
+      <s:c r="J35" s="1"/>
+      <s:c r="K35" s="1"/>
+      <s:c r="L35" s="1"/>
+      <s:c r="M35" s="1"/>
+      <s:c r="N35" s="1"/>
+      <s:c r="O35" s="1"/>
       <s:c r="P35" s="1" t="n">
         <s:v>66</s:v>
       </s:c>
@@ -5752,36 +5264,16 @@
       <s:c r="E36" s="1" t="n">
         <s:v>431.76</s:v>
       </s:c>
-      <s:c r="F36" s="1" t="n">
-        <s:v>0</s:v>
-      </s:c>
-      <s:c r="G36" s="1" t="n">
-        <s:v>2633.98</s:v>
-      </s:c>
-      <s:c r="H36" s="1" t="n">
-        <s:v>0</s:v>
-      </s:c>
-      <s:c r="I36" s="1" t="n">
-        <s:v>4496.22</s:v>
-      </s:c>
-      <s:c r="J36" s="1" t="n">
-        <s:v>0</s:v>
-      </s:c>
-      <s:c r="K36" s="1" t="n">
-        <s:v>-3.3</s:v>
-      </s:c>
-      <s:c r="L36" s="1" t="n">
-        <s:v>0</s:v>
-      </s:c>
-      <s:c r="M36" s="1" t="n">
-        <s:v>0</s:v>
-      </s:c>
-      <s:c r="N36" s="1" t="n">
-        <s:v>14250.37</s:v>
-      </s:c>
-      <s:c r="O36" s="1" t="n">
-        <s:v>210.42</s:v>
-      </s:c>
+      <s:c r="F36" s="1"/>
+      <s:c r="G36" s="1"/>
+      <s:c r="H36" s="1"/>
+      <s:c r="I36" s="1"/>
+      <s:c r="J36" s="1"/>
+      <s:c r="K36" s="1"/>
+      <s:c r="L36" s="1"/>
+      <s:c r="M36" s="1"/>
+      <s:c r="N36" s="1"/>
+      <s:c r="O36" s="1"/>
       <s:c r="P36" s="1" t="n">
         <s:v>66</s:v>
       </s:c>
@@ -5802,36 +5294,16 @@
       <s:c r="E37" s="1" t="n">
         <s:v>381.54</s:v>
       </s:c>
-      <s:c r="F37" s="1" t="n">
-        <s:v>0</s:v>
-      </s:c>
-      <s:c r="G37" s="1" t="n">
-        <s:v>2665.43</s:v>
-      </s:c>
-      <s:c r="H37" s="1" t="n">
-        <s:v>0</s:v>
-      </s:c>
-      <s:c r="I37" s="1" t="n">
-        <s:v>5187.09</s:v>
-      </s:c>
-      <s:c r="J37" s="1" t="n">
-        <s:v>0</s:v>
-      </s:c>
-      <s:c r="K37" s="1" t="n">
-        <s:v>-6.6</s:v>
-      </s:c>
-      <s:c r="L37" s="1" t="n">
-        <s:v>0</s:v>
-      </s:c>
-      <s:c r="M37" s="1" t="n">
-        <s:v>0</s:v>
-      </s:c>
-      <s:c r="N37" s="1" t="n">
-        <s:v>12493.81</s:v>
-      </s:c>
-      <s:c r="O37" s="1" t="n">
-        <s:v>224.47</s:v>
-      </s:c>
+      <s:c r="F37" s="1"/>
+      <s:c r="G37" s="1"/>
+      <s:c r="H37" s="1"/>
+      <s:c r="I37" s="1"/>
+      <s:c r="J37" s="1"/>
+      <s:c r="K37" s="1"/>
+      <s:c r="L37" s="1"/>
+      <s:c r="M37" s="1"/>
+      <s:c r="N37" s="1"/>
+      <s:c r="O37" s="1"/>
       <s:c r="P37" s="1" t="n">
         <s:v>66</s:v>
       </s:c>
@@ -5852,36 +5324,16 @@
       <s:c r="E38" s="1" t="n">
         <s:v>372.17</s:v>
       </s:c>
-      <s:c r="F38" s="1" t="n">
-        <s:v>-300</s:v>
-      </s:c>
-      <s:c r="G38" s="1" t="n">
-        <s:v>2730</s:v>
-      </s:c>
-      <s:c r="H38" s="1" t="n">
-        <s:v>1</s:v>
-      </s:c>
-      <s:c r="I38" s="1" t="n">
-        <s:v>5790.02</s:v>
-      </s:c>
-      <s:c r="J38" s="1" t="n">
-        <s:v>0</s:v>
-      </s:c>
-      <s:c r="K38" s="1" t="n">
-        <s:v>-258.5</s:v>
-      </s:c>
-      <s:c r="L38" s="1" t="n">
-        <s:v>0</s:v>
-      </s:c>
-      <s:c r="M38" s="1" t="n">
-        <s:v>0</s:v>
-      </s:c>
-      <s:c r="N38" s="1" t="n">
-        <s:v>11402.08</s:v>
-      </s:c>
-      <s:c r="O38" s="1" t="n">
-        <s:v>246.9</s:v>
-      </s:c>
+      <s:c r="F38" s="1"/>
+      <s:c r="G38" s="1"/>
+      <s:c r="H38" s="1"/>
+      <s:c r="I38" s="1"/>
+      <s:c r="J38" s="1"/>
+      <s:c r="K38" s="1"/>
+      <s:c r="L38" s="1"/>
+      <s:c r="M38" s="1"/>
+      <s:c r="N38" s="1"/>
+      <s:c r="O38" s="1"/>
       <s:c r="P38" s="1" t="n">
         <s:v>66</s:v>
       </s:c>
@@ -5902,36 +5354,16 @@
       <s:c r="E39" s="1" t="n">
         <s:v>429.45</s:v>
       </s:c>
-      <s:c r="F39" s="1" t="n">
-        <s:v>-840</s:v>
-      </s:c>
-      <s:c r="G39" s="1" t="n">
-        <s:v>2768.53</s:v>
-      </s:c>
-      <s:c r="H39" s="1" t="n">
-        <s:v>1</s:v>
-      </s:c>
-      <s:c r="I39" s="1" t="n">
-        <s:v>6323.04</s:v>
-      </s:c>
-      <s:c r="J39" s="1" t="n">
-        <s:v>0</s:v>
-      </s:c>
-      <s:c r="K39" s="1" t="n">
-        <s:v>-260.2</s:v>
-      </s:c>
-      <s:c r="L39" s="1" t="n">
-        <s:v>0</s:v>
-      </s:c>
-      <s:c r="M39" s="1" t="n">
-        <s:v>0</s:v>
-      </s:c>
-      <s:c r="N39" s="1" t="n">
-        <s:v>11305.22</s:v>
-      </s:c>
-      <s:c r="O39" s="1" t="n">
-        <s:v>242.39</s:v>
-      </s:c>
+      <s:c r="F39" s="1"/>
+      <s:c r="G39" s="1"/>
+      <s:c r="H39" s="1"/>
+      <s:c r="I39" s="1"/>
+      <s:c r="J39" s="1"/>
+      <s:c r="K39" s="1"/>
+      <s:c r="L39" s="1"/>
+      <s:c r="M39" s="1"/>
+      <s:c r="N39" s="1"/>
+      <s:c r="O39" s="1"/>
       <s:c r="P39" s="1" t="n">
         <s:v>64</s:v>
       </s:c>
@@ -5952,36 +5384,16 @@
       <s:c r="E40" s="1" t="n">
         <s:v>381.73</s:v>
       </s:c>
-      <s:c r="F40" s="1" t="n">
-        <s:v>-1363</s:v>
-      </s:c>
-      <s:c r="G40" s="1" t="n">
-        <s:v>2829.6</s:v>
-      </s:c>
-      <s:c r="H40" s="1" t="n">
-        <s:v>1</s:v>
-      </s:c>
-      <s:c r="I40" s="1" t="n">
-        <s:v>6909.32</s:v>
-      </s:c>
-      <s:c r="J40" s="1" t="n">
-        <s:v>0</s:v>
-      </s:c>
-      <s:c r="K40" s="1" t="n">
-        <s:v>-511</s:v>
-      </s:c>
-      <s:c r="L40" s="1" t="n">
-        <s:v>0</s:v>
-      </s:c>
-      <s:c r="M40" s="1" t="n">
-        <s:v>0</s:v>
-      </s:c>
-      <s:c r="N40" s="1" t="n">
-        <s:v>10356.39</s:v>
-      </s:c>
-      <s:c r="O40" s="1" t="n">
-        <s:v>243.87</s:v>
-      </s:c>
+      <s:c r="F40" s="1"/>
+      <s:c r="G40" s="1"/>
+      <s:c r="H40" s="1"/>
+      <s:c r="I40" s="1"/>
+      <s:c r="J40" s="1"/>
+      <s:c r="K40" s="1"/>
+      <s:c r="L40" s="1"/>
+      <s:c r="M40" s="1"/>
+      <s:c r="N40" s="1"/>
+      <s:c r="O40" s="1"/>
       <s:c r="P40" s="1" t="n">
         <s:v>64</s:v>
       </s:c>
@@ -6002,36 +5414,16 @@
       <s:c r="E41" s="1" t="n">
         <s:v>369.73</s:v>
       </s:c>
-      <s:c r="F41" s="1" t="n">
-        <s:v>-1568</s:v>
-      </s:c>
-      <s:c r="G41" s="1" t="n">
-        <s:v>2818.59</s:v>
-      </s:c>
-      <s:c r="H41" s="1" t="n">
-        <s:v>1</s:v>
-      </s:c>
-      <s:c r="I41" s="1" t="n">
-        <s:v>7472.56</s:v>
-      </s:c>
-      <s:c r="J41" s="1" t="n">
-        <s:v>0</s:v>
-      </s:c>
-      <s:c r="K41" s="1" t="n">
-        <s:v>-508.9</s:v>
-      </s:c>
-      <s:c r="L41" s="1" t="n">
-        <s:v>0</s:v>
-      </s:c>
-      <s:c r="M41" s="1" t="n">
-        <s:v>0</s:v>
-      </s:c>
-      <s:c r="N41" s="1" t="n">
-        <s:v>9659.1</s:v>
-      </s:c>
-      <s:c r="O41" s="1" t="n">
-        <s:v>209.55</s:v>
-      </s:c>
+      <s:c r="F41" s="1"/>
+      <s:c r="G41" s="1"/>
+      <s:c r="H41" s="1"/>
+      <s:c r="I41" s="1"/>
+      <s:c r="J41" s="1"/>
+      <s:c r="K41" s="1"/>
+      <s:c r="L41" s="1"/>
+      <s:c r="M41" s="1"/>
+      <s:c r="N41" s="1"/>
+      <s:c r="O41" s="1"/>
       <s:c r="P41" s="1" t="n">
         <s:v>64</s:v>
       </s:c>
@@ -6052,36 +5444,16 @@
       <s:c r="E42" s="1" t="n">
         <s:v>395.79</s:v>
       </s:c>
-      <s:c r="F42" s="1" t="n">
-        <s:v>-2773</s:v>
-      </s:c>
-      <s:c r="G42" s="1" t="n">
-        <s:v>2899.08</s:v>
-      </s:c>
-      <s:c r="H42" s="1" t="n">
-        <s:v>0</s:v>
-      </s:c>
-      <s:c r="I42" s="1" t="n">
-        <s:v>7969.69</s:v>
-      </s:c>
-      <s:c r="J42" s="1" t="n">
-        <s:v>0</s:v>
-      </s:c>
-      <s:c r="K42" s="1" t="n">
-        <s:v>-509.2</s:v>
-      </s:c>
-      <s:c r="L42" s="1" t="n">
-        <s:v>0</s:v>
-      </s:c>
-      <s:c r="M42" s="1" t="n">
-        <s:v>0</s:v>
-      </s:c>
-      <s:c r="N42" s="1" t="n">
-        <s:v>10399.05</s:v>
-      </s:c>
-      <s:c r="O42" s="1" t="n">
-        <s:v>198.08</s:v>
-      </s:c>
+      <s:c r="F42" s="1"/>
+      <s:c r="G42" s="1"/>
+      <s:c r="H42" s="1"/>
+      <s:c r="I42" s="1"/>
+      <s:c r="J42" s="1"/>
+      <s:c r="K42" s="1"/>
+      <s:c r="L42" s="1"/>
+      <s:c r="M42" s="1"/>
+      <s:c r="N42" s="1"/>
+      <s:c r="O42" s="1"/>
       <s:c r="P42" s="1" t="n">
         <s:v>64</s:v>
       </s:c>
@@ -6102,36 +5474,16 @@
       <s:c r="E43" s="1" t="n">
         <s:v>383.52</s:v>
       </s:c>
-      <s:c r="F43" s="1" t="n">
-        <s:v>-3233</s:v>
-      </s:c>
-      <s:c r="G43" s="1" t="n">
-        <s:v>2950.79</s:v>
-      </s:c>
-      <s:c r="H43" s="1" t="n">
-        <s:v>0</s:v>
-      </s:c>
-      <s:c r="I43" s="1" t="n">
-        <s:v>8409.68</s:v>
-      </s:c>
-      <s:c r="J43" s="1" t="n">
-        <s:v>0</s:v>
-      </s:c>
-      <s:c r="K43" s="1" t="n">
-        <s:v>-513.3</s:v>
-      </s:c>
-      <s:c r="L43" s="1" t="n">
-        <s:v>0</s:v>
-      </s:c>
-      <s:c r="M43" s="1" t="n">
-        <s:v>0</s:v>
-      </s:c>
-      <s:c r="N43" s="1" t="n">
-        <s:v>9883.95</s:v>
-      </s:c>
-      <s:c r="O43" s="1" t="n">
-        <s:v>186.68</s:v>
-      </s:c>
+      <s:c r="F43" s="1"/>
+      <s:c r="G43" s="1"/>
+      <s:c r="H43" s="1"/>
+      <s:c r="I43" s="1"/>
+      <s:c r="J43" s="1"/>
+      <s:c r="K43" s="1"/>
+      <s:c r="L43" s="1"/>
+      <s:c r="M43" s="1"/>
+      <s:c r="N43" s="1"/>
+      <s:c r="O43" s="1"/>
       <s:c r="P43" s="1" t="n">
         <s:v>64</s:v>
       </s:c>
@@ -6152,36 +5504,16 @@
       <s:c r="E44" s="1" t="n">
         <s:v>380.98</s:v>
       </s:c>
-      <s:c r="F44" s="1" t="n">
-        <s:v>-3483</s:v>
-      </s:c>
-      <s:c r="G44" s="1" t="n">
-        <s:v>2964.38</s:v>
-      </s:c>
-      <s:c r="H44" s="1" t="n">
-        <s:v>0</s:v>
-      </s:c>
-      <s:c r="I44" s="1" t="n">
-        <s:v>8705.24</s:v>
-      </s:c>
-      <s:c r="J44" s="1" t="n">
-        <s:v>0</s:v>
-      </s:c>
-      <s:c r="K44" s="1" t="n">
-        <s:v>-512.2</s:v>
-      </s:c>
-      <s:c r="L44" s="1" t="n">
-        <s:v>0</s:v>
-      </s:c>
-      <s:c r="M44" s="1" t="n">
-        <s:v>0</s:v>
-      </s:c>
-      <s:c r="N44" s="1" t="n">
-        <s:v>9600.61</s:v>
-      </s:c>
-      <s:c r="O44" s="1" t="n">
-        <s:v>194.28</s:v>
-      </s:c>
+      <s:c r="F44" s="1"/>
+      <s:c r="G44" s="1"/>
+      <s:c r="H44" s="1"/>
+      <s:c r="I44" s="1"/>
+      <s:c r="J44" s="1"/>
+      <s:c r="K44" s="1"/>
+      <s:c r="L44" s="1"/>
+      <s:c r="M44" s="1"/>
+      <s:c r="N44" s="1"/>
+      <s:c r="O44" s="1"/>
       <s:c r="P44" s="1" t="n">
         <s:v>62</s:v>
       </s:c>
@@ -6202,36 +5534,16 @@
       <s:c r="E45" s="1" t="n">
         <s:v>393.23</s:v>
       </s:c>
-      <s:c r="F45" s="1" t="n">
-        <s:v>-3493</s:v>
-      </s:c>
-      <s:c r="G45" s="1" t="n">
-        <s:v>2945.22</s:v>
-      </s:c>
-      <s:c r="H45" s="1" t="n">
-        <s:v>0</s:v>
-      </s:c>
-      <s:c r="I45" s="1" t="n">
-        <s:v>8997.76</s:v>
-      </s:c>
-      <s:c r="J45" s="1" t="n">
-        <s:v>0</s:v>
-      </s:c>
-      <s:c r="K45" s="1" t="n">
-        <s:v>-807.6</s:v>
-      </s:c>
-      <s:c r="L45" s="1" t="n">
-        <s:v>0</s:v>
-      </s:c>
-      <s:c r="M45" s="1" t="n">
-        <s:v>0</s:v>
-      </s:c>
-      <s:c r="N45" s="1" t="n">
-        <s:v>9628.72</s:v>
-      </s:c>
-      <s:c r="O45" s="1" t="n">
-        <s:v>183.89</s:v>
-      </s:c>
+      <s:c r="F45" s="1"/>
+      <s:c r="G45" s="1"/>
+      <s:c r="H45" s="1"/>
+      <s:c r="I45" s="1"/>
+      <s:c r="J45" s="1"/>
+      <s:c r="K45" s="1"/>
+      <s:c r="L45" s="1"/>
+      <s:c r="M45" s="1"/>
+      <s:c r="N45" s="1"/>
+      <s:c r="O45" s="1"/>
       <s:c r="P45" s="1" t="n">
         <s:v>62</s:v>
       </s:c>
@@ -6252,36 +5564,16 @@
       <s:c r="E46" s="1" t="n">
         <s:v>430</s:v>
       </s:c>
-      <s:c r="F46" s="1" t="n">
-        <s:v>-3563</s:v>
-      </s:c>
-      <s:c r="G46" s="1" t="n">
-        <s:v>2895.92</s:v>
-      </s:c>
-      <s:c r="H46" s="1" t="n">
-        <s:v>0</s:v>
-      </s:c>
-      <s:c r="I46" s="1" t="n">
-        <s:v>9258.08</s:v>
-      </s:c>
-      <s:c r="J46" s="1" t="n">
-        <s:v>0</s:v>
-      </s:c>
-      <s:c r="K46" s="1" t="n">
-        <s:v>-806.3</s:v>
-      </s:c>
-      <s:c r="L46" s="1" t="n">
-        <s:v>0</s:v>
-      </s:c>
-      <s:c r="M46" s="1" t="n">
-        <s:v>0</s:v>
-      </s:c>
-      <s:c r="N46" s="1" t="n">
-        <s:v>9921.75</s:v>
-      </s:c>
-      <s:c r="O46" s="1" t="n">
-        <s:v>190.65</s:v>
-      </s:c>
+      <s:c r="F46" s="1"/>
+      <s:c r="G46" s="1"/>
+      <s:c r="H46" s="1"/>
+      <s:c r="I46" s="1"/>
+      <s:c r="J46" s="1"/>
+      <s:c r="K46" s="1"/>
+      <s:c r="L46" s="1"/>
+      <s:c r="M46" s="1"/>
+      <s:c r="N46" s="1"/>
+      <s:c r="O46" s="1"/>
       <s:c r="P46" s="1" t="n">
         <s:v>62</s:v>
       </s:c>
@@ -6302,36 +5594,16 @@
       <s:c r="E47" s="1" t="n">
         <s:v>430</s:v>
       </s:c>
-      <s:c r="F47" s="1" t="n">
-        <s:v>-3658</s:v>
-      </s:c>
-      <s:c r="G47" s="1" t="n">
-        <s:v>2930.96</s:v>
-      </s:c>
-      <s:c r="H47" s="1" t="n">
-        <s:v>0</s:v>
-      </s:c>
-      <s:c r="I47" s="1" t="n">
-        <s:v>9183.39</s:v>
-      </s:c>
-      <s:c r="J47" s="1" t="n">
-        <s:v>0</s:v>
-      </s:c>
-      <s:c r="K47" s="1" t="n">
-        <s:v>-810.8</s:v>
-      </s:c>
-      <s:c r="L47" s="1" t="n">
-        <s:v>0</s:v>
-      </s:c>
-      <s:c r="M47" s="1" t="n">
-        <s:v>0</s:v>
-      </s:c>
-      <s:c r="N47" s="1" t="n">
-        <s:v>10451.44</s:v>
-      </s:c>
-      <s:c r="O47" s="1" t="n">
-        <s:v>212.04</s:v>
-      </s:c>
+      <s:c r="F47" s="1"/>
+      <s:c r="G47" s="1"/>
+      <s:c r="H47" s="1"/>
+      <s:c r="I47" s="1"/>
+      <s:c r="J47" s="1"/>
+      <s:c r="K47" s="1"/>
+      <s:c r="L47" s="1"/>
+      <s:c r="M47" s="1"/>
+      <s:c r="N47" s="1"/>
+      <s:c r="O47" s="1"/>
       <s:c r="P47" s="1" t="n">
         <s:v>62</s:v>
       </s:c>
@@ -6352,36 +5624,16 @@
       <s:c r="E48" s="1" t="n">
         <s:v>403.79</s:v>
       </s:c>
-      <s:c r="F48" s="1" t="n">
-        <s:v>-3703</s:v>
-      </s:c>
-      <s:c r="G48" s="1" t="n">
-        <s:v>2955.26</s:v>
-      </s:c>
-      <s:c r="H48" s="1" t="n">
-        <s:v>0</s:v>
-      </s:c>
-      <s:c r="I48" s="1" t="n">
-        <s:v>9470.81</s:v>
-      </s:c>
-      <s:c r="J48" s="1" t="n">
-        <s:v>0</s:v>
-      </s:c>
-      <s:c r="K48" s="1" t="n">
-        <s:v>-809.2</s:v>
-      </s:c>
-      <s:c r="L48" s="1" t="n">
-        <s:v>0</s:v>
-      </s:c>
-      <s:c r="M48" s="1" t="n">
-        <s:v>0</s:v>
-      </s:c>
-      <s:c r="N48" s="1" t="n">
-        <s:v>10026.45</s:v>
-      </s:c>
-      <s:c r="O48" s="1" t="n">
-        <s:v>215.28</s:v>
-      </s:c>
+      <s:c r="F48" s="1"/>
+      <s:c r="G48" s="1"/>
+      <s:c r="H48" s="1"/>
+      <s:c r="I48" s="1"/>
+      <s:c r="J48" s="1"/>
+      <s:c r="K48" s="1"/>
+      <s:c r="L48" s="1"/>
+      <s:c r="M48" s="1"/>
+      <s:c r="N48" s="1"/>
+      <s:c r="O48" s="1"/>
       <s:c r="P48" s="1" t="n">
         <s:v>62</s:v>
       </s:c>
@@ -6402,36 +5654,16 @@
       <s:c r="E49" s="1" t="n">
         <s:v>393.23</s:v>
       </s:c>
-      <s:c r="F49" s="1" t="n">
-        <s:v>-3713</s:v>
-      </s:c>
-      <s:c r="G49" s="1" t="n">
-        <s:v>2931.47</s:v>
-      </s:c>
-      <s:c r="H49" s="1" t="n">
-        <s:v>0</s:v>
-      </s:c>
-      <s:c r="I49" s="1" t="n">
-        <s:v>9415.12</s:v>
-      </s:c>
-      <s:c r="J49" s="1" t="n">
-        <s:v>0</s:v>
-      </s:c>
-      <s:c r="K49" s="1" t="n">
-        <s:v>-807.9</s:v>
-      </s:c>
-      <s:c r="L49" s="1" t="n">
-        <s:v>0</s:v>
-      </s:c>
-      <s:c r="M49" s="1" t="n">
-        <s:v>0</s:v>
-      </s:c>
-      <s:c r="N49" s="1" t="n">
-        <s:v>9714.9</s:v>
-      </s:c>
-      <s:c r="O49" s="1" t="n">
-        <s:v>223.32</s:v>
-      </s:c>
+      <s:c r="F49" s="1"/>
+      <s:c r="G49" s="1"/>
+      <s:c r="H49" s="1"/>
+      <s:c r="I49" s="1"/>
+      <s:c r="J49" s="1"/>
+      <s:c r="K49" s="1"/>
+      <s:c r="L49" s="1"/>
+      <s:c r="M49" s="1"/>
+      <s:c r="N49" s="1"/>
+      <s:c r="O49" s="1"/>
       <s:c r="P49" s="1" t="n">
         <s:v>62</s:v>
       </s:c>
@@ -6452,36 +5684,16 @@
       <s:c r="E50" s="1" t="n">
         <s:v>440.04</s:v>
       </s:c>
-      <s:c r="F50" s="1" t="n">
-        <s:v>-2933</s:v>
-      </s:c>
-      <s:c r="G50" s="1" t="n">
-        <s:v>2935.42</s:v>
-      </s:c>
-      <s:c r="H50" s="1" t="n">
-        <s:v>0</s:v>
-      </s:c>
-      <s:c r="I50" s="1" t="n">
-        <s:v>9470.55</s:v>
-      </s:c>
-      <s:c r="J50" s="1" t="n">
-        <s:v>0</s:v>
-      </s:c>
-      <s:c r="K50" s="1" t="n">
-        <s:v>-803.2</s:v>
-      </s:c>
-      <s:c r="L50" s="1" t="n">
-        <s:v>0</s:v>
-      </s:c>
-      <s:c r="M50" s="1" t="n">
-        <s:v>0</s:v>
-      </s:c>
-      <s:c r="N50" s="1" t="n">
-        <s:v>10678.21</s:v>
-      </s:c>
-      <s:c r="O50" s="1" t="n">
-        <s:v>232.85</s:v>
-      </s:c>
+      <s:c r="F50" s="1"/>
+      <s:c r="G50" s="1"/>
+      <s:c r="H50" s="1"/>
+      <s:c r="I50" s="1"/>
+      <s:c r="J50" s="1"/>
+      <s:c r="K50" s="1"/>
+      <s:c r="L50" s="1"/>
+      <s:c r="M50" s="1"/>
+      <s:c r="N50" s="1"/>
+      <s:c r="O50" s="1"/>
       <s:c r="P50" s="1" t="n">
         <s:v>62</s:v>
       </s:c>
@@ -6502,36 +5714,16 @@
       <s:c r="E51" s="1" t="n">
         <s:v>416.95</s:v>
       </s:c>
-      <s:c r="F51" s="1" t="n">
-        <s:v>-2813</s:v>
-      </s:c>
-      <s:c r="G51" s="1" t="n">
-        <s:v>2926.48</s:v>
-      </s:c>
-      <s:c r="H51" s="1" t="n">
-        <s:v>0</s:v>
-      </s:c>
-      <s:c r="I51" s="1" t="n">
-        <s:v>9344.62</s:v>
-      </s:c>
-      <s:c r="J51" s="1" t="n">
-        <s:v>0</s:v>
-      </s:c>
-      <s:c r="K51" s="1" t="n">
-        <s:v>-560.3</s:v>
-      </s:c>
-      <s:c r="L51" s="1" t="n">
-        <s:v>0</s:v>
-      </s:c>
-      <s:c r="M51" s="1" t="n">
-        <s:v>0</s:v>
-      </s:c>
-      <s:c r="N51" s="1" t="n">
-        <s:v>11064.17</s:v>
-      </s:c>
-      <s:c r="O51" s="1" t="n">
-        <s:v>235.53</s:v>
-      </s:c>
+      <s:c r="F51" s="1"/>
+      <s:c r="G51" s="1"/>
+      <s:c r="H51" s="1"/>
+      <s:c r="I51" s="1"/>
+      <s:c r="J51" s="1"/>
+      <s:c r="K51" s="1"/>
+      <s:c r="L51" s="1"/>
+      <s:c r="M51" s="1"/>
+      <s:c r="N51" s="1"/>
+      <s:c r="O51" s="1"/>
       <s:c r="P51" s="1" t="n">
         <s:v>62</s:v>
       </s:c>
@@ -6552,36 +5744,16 @@
       <s:c r="E52" s="1" t="n">
         <s:v>430</s:v>
       </s:c>
-      <s:c r="F52" s="1" t="n">
-        <s:v>-2653</s:v>
-      </s:c>
-      <s:c r="G52" s="1" t="n">
-        <s:v>2902.34</s:v>
-      </s:c>
-      <s:c r="H52" s="1" t="n">
-        <s:v>0</s:v>
-      </s:c>
-      <s:c r="I52" s="1" t="n">
-        <s:v>9231.21</s:v>
-      </s:c>
-      <s:c r="J52" s="1" t="n">
-        <s:v>0</s:v>
-      </s:c>
-      <s:c r="K52" s="1" t="n">
-        <s:v>-802.2</s:v>
-      </s:c>
-      <s:c r="L52" s="1" t="n">
-        <s:v>0</s:v>
-      </s:c>
-      <s:c r="M52" s="1" t="n">
-        <s:v>0</s:v>
-      </s:c>
-      <s:c r="N52" s="1" t="n">
-        <s:v>10754.79</s:v>
-      </s:c>
-      <s:c r="O52" s="1" t="n">
-        <s:v>245.25</s:v>
-      </s:c>
+      <s:c r="F52" s="1"/>
+      <s:c r="G52" s="1"/>
+      <s:c r="H52" s="1"/>
+      <s:c r="I52" s="1"/>
+      <s:c r="J52" s="1"/>
+      <s:c r="K52" s="1"/>
+      <s:c r="L52" s="1"/>
+      <s:c r="M52" s="1"/>
+      <s:c r="N52" s="1"/>
+      <s:c r="O52" s="1"/>
       <s:c r="P52" s="1" t="n">
         <s:v>62</s:v>
       </s:c>
@@ -6602,36 +5774,16 @@
       <s:c r="E53" s="1" t="n">
         <s:v>370.89</s:v>
       </s:c>
-      <s:c r="F53" s="1" t="n">
-        <s:v>-2593</s:v>
-      </s:c>
-      <s:c r="G53" s="1" t="n">
-        <s:v>2934.98</s:v>
-      </s:c>
-      <s:c r="H53" s="1" t="n">
-        <s:v>0</s:v>
-      </s:c>
-      <s:c r="I53" s="1" t="n">
-        <s:v>9289.34</s:v>
-      </s:c>
-      <s:c r="J53" s="1" t="n">
-        <s:v>0</s:v>
-      </s:c>
-      <s:c r="K53" s="1" t="n">
-        <s:v>-802.4</s:v>
-      </s:c>
-      <s:c r="L53" s="1" t="n">
-        <s:v>0</s:v>
-      </s:c>
-      <s:c r="M53" s="1" t="n">
-        <s:v>0</s:v>
-      </s:c>
-      <s:c r="N53" s="1" t="n">
-        <s:v>10156.72</s:v>
-      </s:c>
-      <s:c r="O53" s="1" t="n">
-        <s:v>247.56</s:v>
-      </s:c>
+      <s:c r="F53" s="1"/>
+      <s:c r="G53" s="1"/>
+      <s:c r="H53" s="1"/>
+      <s:c r="I53" s="1"/>
+      <s:c r="J53" s="1"/>
+      <s:c r="K53" s="1"/>
+      <s:c r="L53" s="1"/>
+      <s:c r="M53" s="1"/>
+      <s:c r="N53" s="1"/>
+      <s:c r="O53" s="1"/>
       <s:c r="P53" s="1" t="n">
         <s:v>62</s:v>
       </s:c>
@@ -6652,36 +5804,16 @@
       <s:c r="E54" s="1" t="n">
         <s:v>370.14</s:v>
       </s:c>
-      <s:c r="F54" s="1" t="n">
-        <s:v>-2383</s:v>
-      </s:c>
-      <s:c r="G54" s="1" t="n">
-        <s:v>2930.35</s:v>
-      </s:c>
-      <s:c r="H54" s="1" t="n">
-        <s:v>0</s:v>
-      </s:c>
-      <s:c r="I54" s="1" t="n">
-        <s:v>9189.69</s:v>
-      </s:c>
-      <s:c r="J54" s="1" t="n">
-        <s:v>0</s:v>
-      </s:c>
-      <s:c r="K54" s="1" t="n">
-        <s:v>-799.2</s:v>
-      </s:c>
-      <s:c r="L54" s="1" t="n">
-        <s:v>0</s:v>
-      </s:c>
-      <s:c r="M54" s="1" t="n">
-        <s:v>0</s:v>
-      </s:c>
-      <s:c r="N54" s="1" t="n">
-        <s:v>10510.39</s:v>
-      </s:c>
-      <s:c r="O54" s="1" t="n">
-        <s:v>260.87</s:v>
-      </s:c>
+      <s:c r="F54" s="1"/>
+      <s:c r="G54" s="1"/>
+      <s:c r="H54" s="1"/>
+      <s:c r="I54" s="1"/>
+      <s:c r="J54" s="1"/>
+      <s:c r="K54" s="1"/>
+      <s:c r="L54" s="1"/>
+      <s:c r="M54" s="1"/>
+      <s:c r="N54" s="1"/>
+      <s:c r="O54" s="1"/>
       <s:c r="P54" s="1" t="n">
         <s:v>62</s:v>
       </s:c>
@@ -6702,36 +5834,16 @@
       <s:c r="E55" s="1" t="n">
         <s:v>372.17</s:v>
       </s:c>
-      <s:c r="F55" s="1" t="n">
-        <s:v>-2273</s:v>
-      </s:c>
-      <s:c r="G55" s="1" t="n">
-        <s:v>2959.54</s:v>
-      </s:c>
-      <s:c r="H55" s="1" t="n">
-        <s:v>0</s:v>
-      </s:c>
-      <s:c r="I55" s="1" t="n">
-        <s:v>8884.4</s:v>
-      </s:c>
-      <s:c r="J55" s="1" t="n">
-        <s:v>0</s:v>
-      </s:c>
-      <s:c r="K55" s="1" t="n">
-        <s:v>-800</s:v>
-      </s:c>
-      <s:c r="L55" s="1" t="n">
-        <s:v>0</s:v>
-      </s:c>
-      <s:c r="M55" s="1" t="n">
-        <s:v>0</s:v>
-      </s:c>
-      <s:c r="N55" s="1" t="n">
-        <s:v>10850.04</s:v>
-      </s:c>
-      <s:c r="O55" s="1" t="n">
-        <s:v>278.61</s:v>
-      </s:c>
+      <s:c r="F55" s="1"/>
+      <s:c r="G55" s="1"/>
+      <s:c r="H55" s="1"/>
+      <s:c r="I55" s="1"/>
+      <s:c r="J55" s="1"/>
+      <s:c r="K55" s="1"/>
+      <s:c r="L55" s="1"/>
+      <s:c r="M55" s="1"/>
+      <s:c r="N55" s="1"/>
+      <s:c r="O55" s="1"/>
       <s:c r="P55" s="1" t="n">
         <s:v>62</s:v>
       </s:c>
@@ -6752,36 +5864,16 @@
       <s:c r="E56" s="1" t="n">
         <s:v>358.92</s:v>
       </s:c>
-      <s:c r="F56" s="1" t="n">
-        <s:v>-1760</s:v>
-      </s:c>
-      <s:c r="G56" s="1" t="n">
-        <s:v>2911.97</s:v>
-      </s:c>
-      <s:c r="H56" s="1" t="n">
-        <s:v>0</s:v>
-      </s:c>
-      <s:c r="I56" s="1" t="n">
-        <s:v>8869.84</s:v>
-      </s:c>
-      <s:c r="J56" s="1" t="n">
-        <s:v>0</s:v>
-      </s:c>
-      <s:c r="K56" s="1" t="n">
-        <s:v>-799.6</s:v>
-      </s:c>
-      <s:c r="L56" s="1" t="n">
-        <s:v>0</s:v>
-      </s:c>
-      <s:c r="M56" s="1" t="n">
-        <s:v>0</s:v>
-      </s:c>
-      <s:c r="N56" s="1" t="n">
-        <s:v>10592.87</s:v>
-      </s:c>
-      <s:c r="O56" s="1" t="n">
-        <s:v>293.01</s:v>
-      </s:c>
+      <s:c r="F56" s="1"/>
+      <s:c r="G56" s="1"/>
+      <s:c r="H56" s="1"/>
+      <s:c r="I56" s="1"/>
+      <s:c r="J56" s="1"/>
+      <s:c r="K56" s="1"/>
+      <s:c r="L56" s="1"/>
+      <s:c r="M56" s="1"/>
+      <s:c r="N56" s="1"/>
+      <s:c r="O56" s="1"/>
       <s:c r="P56" s="1" t="n">
         <s:v>62</s:v>
       </s:c>
@@ -6802,36 +5894,16 @@
       <s:c r="E57" s="1" t="n">
         <s:v>354.26</s:v>
       </s:c>
-      <s:c r="F57" s="1" t="n">
-        <s:v>-1250</s:v>
-      </s:c>
-      <s:c r="G57" s="1" t="n">
-        <s:v>2887.73</s:v>
-      </s:c>
-      <s:c r="H57" s="1" t="n">
-        <s:v>0</s:v>
-      </s:c>
-      <s:c r="I57" s="1" t="n">
-        <s:v>8940.36</s:v>
-      </s:c>
-      <s:c r="J57" s="1" t="n">
-        <s:v>0</s:v>
-      </s:c>
-      <s:c r="K57" s="1" t="n">
-        <s:v>-551.1</s:v>
-      </s:c>
-      <s:c r="L57" s="1" t="n">
-        <s:v>0</s:v>
-      </s:c>
-      <s:c r="M57" s="1" t="n">
-        <s:v>0</s:v>
-      </s:c>
-      <s:c r="N57" s="1" t="n">
-        <s:v>11171.27</s:v>
-      </s:c>
-      <s:c r="O57" s="1" t="n">
-        <s:v>276.11</s:v>
-      </s:c>
+      <s:c r="F57" s="1"/>
+      <s:c r="G57" s="1"/>
+      <s:c r="H57" s="1"/>
+      <s:c r="I57" s="1"/>
+      <s:c r="J57" s="1"/>
+      <s:c r="K57" s="1"/>
+      <s:c r="L57" s="1"/>
+      <s:c r="M57" s="1"/>
+      <s:c r="N57" s="1"/>
+      <s:c r="O57" s="1"/>
       <s:c r="P57" s="1" t="n">
         <s:v>65</s:v>
       </s:c>
@@ -6852,36 +5924,16 @@
       <s:c r="E58" s="1" t="n">
         <s:v>204.63</s:v>
       </s:c>
-      <s:c r="F58" s="1" t="n">
-        <s:v>-670</s:v>
-      </s:c>
-      <s:c r="G58" s="1" t="n">
-        <s:v>2823.84</s:v>
-      </s:c>
-      <s:c r="H58" s="1" t="n">
-        <s:v>1</s:v>
-      </s:c>
-      <s:c r="I58" s="1" t="n">
-        <s:v>8341.16</s:v>
-      </s:c>
-      <s:c r="J58" s="1" t="n">
-        <s:v>0</s:v>
-      </s:c>
-      <s:c r="K58" s="1" t="n">
-        <s:v>-795.8</s:v>
-      </s:c>
-      <s:c r="L58" s="1" t="n">
-        <s:v>0</s:v>
-      </s:c>
-      <s:c r="M58" s="1" t="n">
-        <s:v>0</s:v>
-      </s:c>
-      <s:c r="N58" s="1" t="n">
-        <s:v>10776.12</s:v>
-      </s:c>
-      <s:c r="O58" s="1" t="n">
-        <s:v>294.68</s:v>
-      </s:c>
+      <s:c r="F58" s="1"/>
+      <s:c r="G58" s="1"/>
+      <s:c r="H58" s="1"/>
+      <s:c r="I58" s="1"/>
+      <s:c r="J58" s="1"/>
+      <s:c r="K58" s="1"/>
+      <s:c r="L58" s="1"/>
+      <s:c r="M58" s="1"/>
+      <s:c r="N58" s="1"/>
+      <s:c r="O58" s="1"/>
       <s:c r="P58" s="1" t="n">
         <s:v>65</s:v>
       </s:c>
@@ -6902,36 +5954,16 @@
       <s:c r="E59" s="1" t="n">
         <s:v>204.63</s:v>
       </s:c>
-      <s:c r="F59" s="1" t="n">
-        <s:v>-410</s:v>
-      </s:c>
-      <s:c r="G59" s="1" t="n">
-        <s:v>2837.68</s:v>
-      </s:c>
-      <s:c r="H59" s="1" t="n">
-        <s:v>1</s:v>
-      </s:c>
-      <s:c r="I59" s="1" t="n">
-        <s:v>7765.35</s:v>
-      </s:c>
-      <s:c r="J59" s="1" t="n">
-        <s:v>0</s:v>
-      </s:c>
-      <s:c r="K59" s="1" t="n">
-        <s:v>-795</s:v>
-      </s:c>
-      <s:c r="L59" s="1" t="n">
-        <s:v>0</s:v>
-      </s:c>
-      <s:c r="M59" s="1" t="n">
-        <s:v>0</s:v>
-      </s:c>
-      <s:c r="N59" s="1" t="n">
-        <s:v>11849.75</s:v>
-      </s:c>
-      <s:c r="O59" s="1" t="n">
-        <s:v>309.89</s:v>
-      </s:c>
+      <s:c r="F59" s="1"/>
+      <s:c r="G59" s="1"/>
+      <s:c r="H59" s="1"/>
+      <s:c r="I59" s="1"/>
+      <s:c r="J59" s="1"/>
+      <s:c r="K59" s="1"/>
+      <s:c r="L59" s="1"/>
+      <s:c r="M59" s="1"/>
+      <s:c r="N59" s="1"/>
+      <s:c r="O59" s="1"/>
       <s:c r="P59" s="1" t="n">
         <s:v>65</s:v>
       </s:c>
@@ -6952,36 +5984,16 @@
       <s:c r="E60" s="1" t="n">
         <s:v>204.63</s:v>
       </s:c>
-      <s:c r="F60" s="1" t="n">
-        <s:v>-90</s:v>
-      </s:c>
-      <s:c r="G60" s="1" t="n">
-        <s:v>2909.23</s:v>
-      </s:c>
-      <s:c r="H60" s="1" t="n">
-        <s:v>1</s:v>
-      </s:c>
-      <s:c r="I60" s="1" t="n">
-        <s:v>7548.34</s:v>
-      </s:c>
-      <s:c r="J60" s="1" t="n">
-        <s:v>0</s:v>
-      </s:c>
-      <s:c r="K60" s="1" t="n">
-        <s:v>-549.9</s:v>
-      </s:c>
-      <s:c r="L60" s="1" t="n">
-        <s:v>0</s:v>
-      </s:c>
-      <s:c r="M60" s="1" t="n">
-        <s:v>0</s:v>
-      </s:c>
-      <s:c r="N60" s="1" t="n">
-        <s:v>13354.3</s:v>
-      </s:c>
-      <s:c r="O60" s="1" t="n">
-        <s:v>315.64</s:v>
-      </s:c>
+      <s:c r="F60" s="1"/>
+      <s:c r="G60" s="1"/>
+      <s:c r="H60" s="1"/>
+      <s:c r="I60" s="1"/>
+      <s:c r="J60" s="1"/>
+      <s:c r="K60" s="1"/>
+      <s:c r="L60" s="1"/>
+      <s:c r="M60" s="1"/>
+      <s:c r="N60" s="1"/>
+      <s:c r="O60" s="1"/>
       <s:c r="P60" s="1" t="n">
         <s:v>65</s:v>
       </s:c>
@@ -7002,36 +6014,16 @@
       <s:c r="E61" s="1" t="n">
         <s:v>271.14</s:v>
       </s:c>
-      <s:c r="F61" s="1" t="n">
-        <s:v>0</s:v>
-      </s:c>
-      <s:c r="G61" s="1" t="n">
-        <s:v>2886.08</s:v>
-      </s:c>
-      <s:c r="H61" s="1" t="n">
-        <s:v>1</s:v>
-      </s:c>
-      <s:c r="I61" s="1" t="n">
-        <s:v>7042.14</s:v>
-      </s:c>
-      <s:c r="J61" s="1" t="n">
-        <s:v>0</s:v>
-      </s:c>
-      <s:c r="K61" s="1" t="n">
-        <s:v>-549.8</s:v>
-      </s:c>
-      <s:c r="L61" s="1" t="n">
-        <s:v>0</s:v>
-      </s:c>
-      <s:c r="M61" s="1" t="n">
-        <s:v>0</s:v>
-      </s:c>
-      <s:c r="N61" s="1" t="n">
-        <s:v>14322.14</s:v>
-      </s:c>
-      <s:c r="O61" s="1" t="n">
-        <s:v>326.87</s:v>
-      </s:c>
+      <s:c r="F61" s="1"/>
+      <s:c r="G61" s="1"/>
+      <s:c r="H61" s="1"/>
+      <s:c r="I61" s="1"/>
+      <s:c r="J61" s="1"/>
+      <s:c r="K61" s="1"/>
+      <s:c r="L61" s="1"/>
+      <s:c r="M61" s="1"/>
+      <s:c r="N61" s="1"/>
+      <s:c r="O61" s="1"/>
       <s:c r="P61" s="1" t="n">
         <s:v>64</s:v>
       </s:c>
@@ -7052,36 +6044,16 @@
       <s:c r="E62" s="1" t="n">
         <s:v>206</s:v>
       </s:c>
-      <s:c r="F62" s="1" t="n">
-        <s:v>0</s:v>
-      </s:c>
-      <s:c r="G62" s="1" t="n">
-        <s:v>2839.1</s:v>
-      </s:c>
-      <s:c r="H62" s="1" t="n">
-        <s:v>0</s:v>
-      </s:c>
-      <s:c r="I62" s="1" t="n">
-        <s:v>6380.59</s:v>
-      </s:c>
-      <s:c r="J62" s="1" t="n">
-        <s:v>0</s:v>
-      </s:c>
-      <s:c r="K62" s="1" t="n">
-        <s:v>-796.7</s:v>
-      </s:c>
-      <s:c r="L62" s="1" t="n">
-        <s:v>0</s:v>
-      </s:c>
-      <s:c r="M62" s="1" t="n">
-        <s:v>0</s:v>
-      </s:c>
-      <s:c r="N62" s="1" t="n">
-        <s:v>15911.19</s:v>
-      </s:c>
-      <s:c r="O62" s="1" t="n">
-        <s:v>315.95</s:v>
-      </s:c>
+      <s:c r="F62" s="1"/>
+      <s:c r="G62" s="1"/>
+      <s:c r="H62" s="1"/>
+      <s:c r="I62" s="1"/>
+      <s:c r="J62" s="1"/>
+      <s:c r="K62" s="1"/>
+      <s:c r="L62" s="1"/>
+      <s:c r="M62" s="1"/>
+      <s:c r="N62" s="1"/>
+      <s:c r="O62" s="1"/>
       <s:c r="P62" s="1" t="n">
         <s:v>64</s:v>
       </s:c>
@@ -7102,36 +6074,16 @@
       <s:c r="E63" s="1" t="n">
         <s:v>204.63</s:v>
       </s:c>
-      <s:c r="F63" s="1" t="n">
-        <s:v>0</s:v>
-      </s:c>
-      <s:c r="G63" s="1" t="n">
-        <s:v>2820.43</s:v>
-      </s:c>
-      <s:c r="H63" s="1" t="n">
-        <s:v>0</s:v>
-      </s:c>
-      <s:c r="I63" s="1" t="n">
-        <s:v>5926.63</s:v>
-      </s:c>
-      <s:c r="J63" s="1" t="n">
-        <s:v>0</s:v>
-      </s:c>
-      <s:c r="K63" s="1" t="n">
-        <s:v>-792.1</s:v>
-      </s:c>
-      <s:c r="L63" s="1" t="n">
-        <s:v>200</s:v>
-      </s:c>
-      <s:c r="M63" s="1" t="n">
-        <s:v>0</s:v>
-      </s:c>
-      <s:c r="N63" s="1" t="n">
-        <s:v>15536.48</s:v>
-      </s:c>
-      <s:c r="O63" s="1" t="n">
-        <s:v>315.04</s:v>
-      </s:c>
+      <s:c r="F63" s="1"/>
+      <s:c r="G63" s="1"/>
+      <s:c r="H63" s="1"/>
+      <s:c r="I63" s="1"/>
+      <s:c r="J63" s="1"/>
+      <s:c r="K63" s="1"/>
+      <s:c r="L63" s="1"/>
+      <s:c r="M63" s="1"/>
+      <s:c r="N63" s="1"/>
+      <s:c r="O63" s="1"/>
       <s:c r="P63" s="1" t="n">
         <s:v>64</s:v>
       </s:c>
@@ -7152,36 +6104,16 @@
       <s:c r="E64" s="1" t="n">
         <s:v>417.64</s:v>
       </s:c>
-      <s:c r="F64" s="1" t="n">
-        <s:v>0</s:v>
-      </s:c>
-      <s:c r="G64" s="1" t="n">
-        <s:v>2776.44</s:v>
-      </s:c>
-      <s:c r="H64" s="1" t="n">
-        <s:v>0</s:v>
-      </s:c>
-      <s:c r="I64" s="1" t="n">
-        <s:v>5272.75</s:v>
-      </s:c>
-      <s:c r="J64" s="1" t="n">
-        <s:v>0</s:v>
-      </s:c>
-      <s:c r="K64" s="1" t="n">
-        <s:v>-791.5</s:v>
-      </s:c>
-      <s:c r="L64" s="1" t="n">
-        <s:v>12.66</s:v>
-      </s:c>
-      <s:c r="M64" s="1" t="n">
-        <s:v>0</s:v>
-      </s:c>
-      <s:c r="N64" s="1" t="n">
-        <s:v>15838.69</s:v>
-      </s:c>
-      <s:c r="O64" s="1" t="n">
-        <s:v>298.35</s:v>
-      </s:c>
+      <s:c r="F64" s="1"/>
+      <s:c r="G64" s="1"/>
+      <s:c r="H64" s="1"/>
+      <s:c r="I64" s="1"/>
+      <s:c r="J64" s="1"/>
+      <s:c r="K64" s="1"/>
+      <s:c r="L64" s="1"/>
+      <s:c r="M64" s="1"/>
+      <s:c r="N64" s="1"/>
+      <s:c r="O64" s="1"/>
       <s:c r="P64" s="1" t="n">
         <s:v>64</s:v>
       </s:c>
@@ -7202,36 +6134,16 @@
       <s:c r="E65" s="1" t="n">
         <s:v>418.94</s:v>
       </s:c>
-      <s:c r="F65" s="1" t="n">
-        <s:v>0</s:v>
-      </s:c>
-      <s:c r="G65" s="1" t="n">
-        <s:v>2761.16</s:v>
-      </s:c>
-      <s:c r="H65" s="1" t="n">
-        <s:v>0</s:v>
-      </s:c>
-      <s:c r="I65" s="1" t="n">
-        <s:v>4682.03</s:v>
-      </s:c>
-      <s:c r="J65" s="1" t="n">
-        <s:v>0</s:v>
-      </s:c>
-      <s:c r="K65" s="1" t="n">
-        <s:v>-789.8</s:v>
-      </s:c>
-      <s:c r="L65" s="1" t="n">
-        <s:v>60.15</s:v>
-      </s:c>
-      <s:c r="M65" s="1" t="n">
-        <s:v>0</s:v>
-      </s:c>
-      <s:c r="N65" s="1" t="n">
-        <s:v>16311.64</s:v>
-      </s:c>
-      <s:c r="O65" s="1" t="n">
-        <s:v>321.03</s:v>
-      </s:c>
+      <s:c r="F65" s="1"/>
+      <s:c r="G65" s="1"/>
+      <s:c r="H65" s="1"/>
+      <s:c r="I65" s="1"/>
+      <s:c r="J65" s="1"/>
+      <s:c r="K65" s="1"/>
+      <s:c r="L65" s="1"/>
+      <s:c r="M65" s="1"/>
+      <s:c r="N65" s="1"/>
+      <s:c r="O65" s="1"/>
       <s:c r="P65" s="1" t="n">
         <s:v>64</s:v>
       </s:c>
@@ -7252,36 +6164,16 @@
       <s:c r="E66" s="1" t="n">
         <s:v>429.66</s:v>
       </s:c>
-      <s:c r="F66" s="1" t="n">
-        <s:v>220</s:v>
-      </s:c>
-      <s:c r="G66" s="1" t="n">
-        <s:v>2722.58</s:v>
-      </s:c>
-      <s:c r="H66" s="1" t="n">
-        <s:v>1</s:v>
-      </s:c>
-      <s:c r="I66" s="1" t="n">
-        <s:v>4157.06</s:v>
-      </s:c>
-      <s:c r="J66" s="1" t="n">
-        <s:v>0</s:v>
-      </s:c>
-      <s:c r="K66" s="1" t="n">
-        <s:v>-493.5</s:v>
-      </s:c>
-      <s:c r="L66" s="1" t="n">
-        <s:v>74.72</s:v>
-      </s:c>
-      <s:c r="M66" s="1" t="n">
-        <s:v>0</s:v>
-      </s:c>
-      <s:c r="N66" s="1" t="n">
-        <s:v>16295.43</s:v>
-      </s:c>
-      <s:c r="O66" s="1" t="n">
-        <s:v>338.01</s:v>
-      </s:c>
+      <s:c r="F66" s="1"/>
+      <s:c r="G66" s="1"/>
+      <s:c r="H66" s="1"/>
+      <s:c r="I66" s="1"/>
+      <s:c r="J66" s="1"/>
+      <s:c r="K66" s="1"/>
+      <s:c r="L66" s="1"/>
+      <s:c r="M66" s="1"/>
+      <s:c r="N66" s="1"/>
+      <s:c r="O66" s="1"/>
       <s:c r="P66" s="1" t="n">
         <s:v>64</s:v>
       </s:c>
@@ -7302,36 +6194,16 @@
       <s:c r="E67" s="1" t="n">
         <s:v>415.73</s:v>
       </s:c>
-      <s:c r="F67" s="1" t="n">
-        <s:v>520</s:v>
-      </s:c>
-      <s:c r="G67" s="1" t="n">
-        <s:v>2693.21</s:v>
-      </s:c>
-      <s:c r="H67" s="1" t="n">
-        <s:v>1</s:v>
-      </s:c>
-      <s:c r="I67" s="1" t="n">
-        <s:v>3745.87</s:v>
-      </s:c>
-      <s:c r="J67" s="1" t="n">
-        <s:v>0</s:v>
-      </s:c>
-      <s:c r="K67" s="1" t="n">
-        <s:v>0</s:v>
-      </s:c>
-      <s:c r="L67" s="1" t="n">
-        <s:v>74.72</s:v>
-      </s:c>
-      <s:c r="M67" s="1" t="n">
-        <s:v>0</s:v>
-      </s:c>
-      <s:c r="N67" s="1" t="n">
-        <s:v>16125.94</s:v>
-      </s:c>
-      <s:c r="O67" s="1" t="n">
-        <s:v>358.56</s:v>
-      </s:c>
+      <s:c r="F67" s="1"/>
+      <s:c r="G67" s="1"/>
+      <s:c r="H67" s="1"/>
+      <s:c r="I67" s="1"/>
+      <s:c r="J67" s="1"/>
+      <s:c r="K67" s="1"/>
+      <s:c r="L67" s="1"/>
+      <s:c r="M67" s="1"/>
+      <s:c r="N67" s="1"/>
+      <s:c r="O67" s="1"/>
       <s:c r="P67" s="1" t="n">
         <s:v>64</s:v>
       </s:c>
@@ -7352,36 +6224,16 @@
       <s:c r="E68" s="1" t="n">
         <s:v>414.98</s:v>
       </s:c>
-      <s:c r="F68" s="1" t="n">
-        <s:v>970</s:v>
-      </s:c>
-      <s:c r="G68" s="1" t="n">
-        <s:v>2724.11</s:v>
-      </s:c>
-      <s:c r="H68" s="1" t="n">
-        <s:v>1</s:v>
-      </s:c>
-      <s:c r="I68" s="1" t="n">
-        <s:v>3160.46</s:v>
-      </s:c>
-      <s:c r="J68" s="1" t="n">
-        <s:v>0</s:v>
-      </s:c>
-      <s:c r="K68" s="1" t="n">
-        <s:v>0</s:v>
-      </s:c>
-      <s:c r="L68" s="1" t="n">
-        <s:v>145.71</s:v>
-      </s:c>
-      <s:c r="M68" s="1" t="n">
-        <s:v>0</s:v>
-      </s:c>
-      <s:c r="N68" s="1" t="n">
-        <s:v>16511.17</s:v>
-      </s:c>
-      <s:c r="O68" s="1" t="n">
-        <s:v>350.35</s:v>
-      </s:c>
+      <s:c r="F68" s="1"/>
+      <s:c r="G68" s="1"/>
+      <s:c r="H68" s="1"/>
+      <s:c r="I68" s="1"/>
+      <s:c r="J68" s="1"/>
+      <s:c r="K68" s="1"/>
+      <s:c r="L68" s="1"/>
+      <s:c r="M68" s="1"/>
+      <s:c r="N68" s="1"/>
+      <s:c r="O68" s="1"/>
       <s:c r="P68" s="1" t="n">
         <s:v>64</s:v>
       </s:c>
@@ -7402,36 +6254,16 @@
       <s:c r="E69" s="1" t="n">
         <s:v>416.01</s:v>
       </s:c>
-      <s:c r="F69" s="1" t="n">
-        <s:v>1355</s:v>
-      </s:c>
-      <s:c r="G69" s="1" t="n">
-        <s:v>2695.86</s:v>
-      </s:c>
-      <s:c r="H69" s="1" t="n">
-        <s:v>1</s:v>
-      </s:c>
-      <s:c r="I69" s="1" t="n">
-        <s:v>2754.07</s:v>
-      </s:c>
-      <s:c r="J69" s="1" t="n">
-        <s:v>0</s:v>
-      </s:c>
-      <s:c r="K69" s="1" t="n">
-        <s:v>151.9</s:v>
-      </s:c>
-      <s:c r="L69" s="1" t="n">
-        <s:v>393.76</s:v>
-      </s:c>
-      <s:c r="M69" s="1" t="n">
-        <s:v>0</s:v>
-      </s:c>
-      <s:c r="N69" s="1" t="n">
-        <s:v>16264.62</s:v>
-      </s:c>
-      <s:c r="O69" s="1" t="n">
-        <s:v>431.5</s:v>
-      </s:c>
+      <s:c r="F69" s="1"/>
+      <s:c r="G69" s="1"/>
+      <s:c r="H69" s="1"/>
+      <s:c r="I69" s="1"/>
+      <s:c r="J69" s="1"/>
+      <s:c r="K69" s="1"/>
+      <s:c r="L69" s="1"/>
+      <s:c r="M69" s="1"/>
+      <s:c r="N69" s="1"/>
+      <s:c r="O69" s="1"/>
       <s:c r="P69" s="1" t="n">
         <s:v>64</s:v>
       </s:c>
@@ -7452,36 +6284,16 @@
       <s:c r="E70" s="1" t="n">
         <s:v>404.58</s:v>
       </s:c>
-      <s:c r="F70" s="1" t="n">
-        <s:v>2735</s:v>
-      </s:c>
-      <s:c r="G70" s="1" t="n">
-        <s:v>2705.4</s:v>
-      </s:c>
-      <s:c r="H70" s="1" t="n">
-        <s:v>1</s:v>
-      </s:c>
-      <s:c r="I70" s="1" t="n">
-        <s:v>2167.91</s:v>
-      </s:c>
-      <s:c r="J70" s="1" t="n">
-        <s:v>0</s:v>
-      </s:c>
-      <s:c r="K70" s="1" t="n">
-        <s:v>251.9</s:v>
-      </s:c>
-      <s:c r="L70" s="1" t="n">
-        <s:v>400</s:v>
-      </s:c>
-      <s:c r="M70" s="1" t="n">
-        <s:v>0</s:v>
-      </s:c>
-      <s:c r="N70" s="1" t="n">
-        <s:v>16041.65</s:v>
-      </s:c>
-      <s:c r="O70" s="1" t="n">
-        <s:v>453.04</s:v>
-      </s:c>
+      <s:c r="F70" s="1"/>
+      <s:c r="G70" s="1"/>
+      <s:c r="H70" s="1"/>
+      <s:c r="I70" s="1"/>
+      <s:c r="J70" s="1"/>
+      <s:c r="K70" s="1"/>
+      <s:c r="L70" s="1"/>
+      <s:c r="M70" s="1"/>
+      <s:c r="N70" s="1"/>
+      <s:c r="O70" s="1"/>
       <s:c r="P70" s="1" t="n">
         <s:v>64</s:v>
       </s:c>
@@ -7502,36 +6314,16 @@
       <s:c r="E71" s="1" t="n">
         <s:v>372.17</s:v>
       </s:c>
-      <s:c r="F71" s="1" t="n">
-        <s:v>3130</s:v>
-      </s:c>
-      <s:c r="G71" s="1" t="n">
-        <s:v>2695.81</s:v>
-      </s:c>
-      <s:c r="H71" s="1" t="n">
-        <s:v>1</s:v>
-      </s:c>
-      <s:c r="I71" s="1" t="n">
-        <s:v>1715.82</s:v>
-      </s:c>
-      <s:c r="J71" s="1" t="n">
-        <s:v>0</s:v>
-      </s:c>
-      <s:c r="K71" s="1" t="n">
-        <s:v>301.5</s:v>
-      </s:c>
-      <s:c r="L71" s="1" t="n">
-        <s:v>400</s:v>
-      </s:c>
-      <s:c r="M71" s="1" t="n">
-        <s:v>0</s:v>
-      </s:c>
-      <s:c r="N71" s="1" t="n">
-        <s:v>15101.28</s:v>
-      </s:c>
-      <s:c r="O71" s="1" t="n">
-        <s:v>457.2</s:v>
-      </s:c>
+      <s:c r="F71" s="1"/>
+      <s:c r="G71" s="1"/>
+      <s:c r="H71" s="1"/>
+      <s:c r="I71" s="1"/>
+      <s:c r="J71" s="1"/>
+      <s:c r="K71" s="1"/>
+      <s:c r="L71" s="1"/>
+      <s:c r="M71" s="1"/>
+      <s:c r="N71" s="1"/>
+      <s:c r="O71" s="1"/>
       <s:c r="P71" s="1" t="n">
         <s:v>65</s:v>
       </s:c>
@@ -7552,36 +6344,16 @@
       <s:c r="E72" s="1" t="n">
         <s:v>369.69</s:v>
       </s:c>
-      <s:c r="F72" s="1" t="n">
-        <s:v>3230</s:v>
-      </s:c>
-      <s:c r="G72" s="1" t="n">
-        <s:v>2658.07</s:v>
-      </s:c>
-      <s:c r="H72" s="1" t="n">
-        <s:v>1</s:v>
-      </s:c>
-      <s:c r="I72" s="1" t="n">
-        <s:v>1282.09</s:v>
-      </s:c>
-      <s:c r="J72" s="1" t="n">
-        <s:v>0</s:v>
-      </s:c>
-      <s:c r="K72" s="1" t="n">
-        <s:v>448.5</s:v>
-      </s:c>
-      <s:c r="L72" s="1" t="n">
-        <s:v>400</s:v>
-      </s:c>
-      <s:c r="M72" s="1" t="n">
-        <s:v>0</s:v>
-      </s:c>
-      <s:c r="N72" s="1" t="n">
-        <s:v>14955.92</s:v>
-      </s:c>
-      <s:c r="O72" s="1" t="n">
-        <s:v>413.62</s:v>
-      </s:c>
+      <s:c r="F72" s="1"/>
+      <s:c r="G72" s="1"/>
+      <s:c r="H72" s="1"/>
+      <s:c r="I72" s="1"/>
+      <s:c r="J72" s="1"/>
+      <s:c r="K72" s="1"/>
+      <s:c r="L72" s="1"/>
+      <s:c r="M72" s="1"/>
+      <s:c r="N72" s="1"/>
+      <s:c r="O72" s="1"/>
       <s:c r="P72" s="1" t="n">
         <s:v>65</s:v>
       </s:c>
@@ -7602,36 +6374,16 @@
       <s:c r="E73" s="1" t="n">
         <s:v>271.14</s:v>
       </s:c>
-      <s:c r="F73" s="1" t="n">
-        <s:v>3167.3</s:v>
-      </s:c>
-      <s:c r="G73" s="1" t="n">
-        <s:v>2661.85</s:v>
-      </s:c>
-      <s:c r="H73" s="1" t="n">
-        <s:v>1</s:v>
-      </s:c>
-      <s:c r="I73" s="1" t="n">
-        <s:v>1044.34</s:v>
-      </s:c>
-      <s:c r="J73" s="1" t="n">
-        <s:v>0</s:v>
-      </s:c>
-      <s:c r="K73" s="1" t="n">
-        <s:v>449.5</s:v>
-      </s:c>
-      <s:c r="L73" s="1" t="n">
-        <s:v>400</s:v>
-      </s:c>
-      <s:c r="M73" s="1" t="n">
-        <s:v>0</s:v>
-      </s:c>
-      <s:c r="N73" s="1" t="n">
-        <s:v>14478.35</s:v>
-      </s:c>
-      <s:c r="O73" s="1" t="n">
-        <s:v>401.76</s:v>
-      </s:c>
+      <s:c r="F73" s="1"/>
+      <s:c r="G73" s="1"/>
+      <s:c r="H73" s="1"/>
+      <s:c r="I73" s="1"/>
+      <s:c r="J73" s="1"/>
+      <s:c r="K73" s="1"/>
+      <s:c r="L73" s="1"/>
+      <s:c r="M73" s="1"/>
+      <s:c r="N73" s="1"/>
+      <s:c r="O73" s="1"/>
       <s:c r="P73" s="1" t="n">
         <s:v>66</s:v>
       </s:c>
@@ -7652,36 +6404,16 @@
       <s:c r="E74" s="1" t="n">
         <s:v>371.92</s:v>
       </s:c>
-      <s:c r="F74" s="1" t="n">
-        <s:v>2972.3</s:v>
-      </s:c>
-      <s:c r="G74" s="1" t="n">
-        <s:v>2624.84</s:v>
-      </s:c>
-      <s:c r="H74" s="1" t="n">
-        <s:v>1</s:v>
-      </s:c>
-      <s:c r="I74" s="1" t="n">
-        <s:v>775.43</s:v>
-      </s:c>
-      <s:c r="J74" s="1" t="n">
-        <s:v>0</s:v>
-      </s:c>
-      <s:c r="K74" s="1" t="n">
-        <s:v>550.2</s:v>
-      </s:c>
-      <s:c r="L74" s="1" t="n">
-        <s:v>400</s:v>
-      </s:c>
-      <s:c r="M74" s="1" t="n">
-        <s:v>0</s:v>
-      </s:c>
-      <s:c r="N74" s="1" t="n">
-        <s:v>14337.69</s:v>
-      </s:c>
-      <s:c r="O74" s="1" t="n">
-        <s:v>403.04</s:v>
-      </s:c>
+      <s:c r="F74" s="1"/>
+      <s:c r="G74" s="1"/>
+      <s:c r="H74" s="1"/>
+      <s:c r="I74" s="1"/>
+      <s:c r="J74" s="1"/>
+      <s:c r="K74" s="1"/>
+      <s:c r="L74" s="1"/>
+      <s:c r="M74" s="1"/>
+      <s:c r="N74" s="1"/>
+      <s:c r="O74" s="1"/>
       <s:c r="P74" s="1" t="n">
         <s:v>64</s:v>
       </s:c>
@@ -7702,36 +6434,16 @@
       <s:c r="E75" s="1" t="n">
         <s:v>370.58</s:v>
       </s:c>
-      <s:c r="F75" s="1" t="n">
-        <s:v>2860</s:v>
-      </s:c>
-      <s:c r="G75" s="1" t="n">
-        <s:v>2605.5</s:v>
-      </s:c>
-      <s:c r="H75" s="1" t="n">
-        <s:v>1</s:v>
-      </s:c>
-      <s:c r="I75" s="1" t="n">
-        <s:v>585.28</s:v>
-      </s:c>
-      <s:c r="J75" s="1" t="n">
-        <s:v>0</s:v>
-      </s:c>
-      <s:c r="K75" s="1" t="n">
-        <s:v>551.2</s:v>
-      </s:c>
-      <s:c r="L75" s="1" t="n">
-        <s:v>400</s:v>
-      </s:c>
-      <s:c r="M75" s="1" t="n">
-        <s:v>0</s:v>
-      </s:c>
-      <s:c r="N75" s="1" t="n">
-        <s:v>14855.52</s:v>
-      </s:c>
-      <s:c r="O75" s="1" t="n">
-        <s:v>393.6</s:v>
-      </s:c>
+      <s:c r="F75" s="1"/>
+      <s:c r="G75" s="1"/>
+      <s:c r="H75" s="1"/>
+      <s:c r="I75" s="1"/>
+      <s:c r="J75" s="1"/>
+      <s:c r="K75" s="1"/>
+      <s:c r="L75" s="1"/>
+      <s:c r="M75" s="1"/>
+      <s:c r="N75" s="1"/>
+      <s:c r="O75" s="1"/>
       <s:c r="P75" s="1" t="n">
         <s:v>64</s:v>
       </s:c>
@@ -7752,36 +6464,16 @@
       <s:c r="E76" s="1" t="n">
         <s:v>371.45</s:v>
       </s:c>
-      <s:c r="F76" s="1" t="n">
-        <s:v>2680</s:v>
-      </s:c>
-      <s:c r="G76" s="1" t="n">
-        <s:v>2594.86</s:v>
-      </s:c>
-      <s:c r="H76" s="1" t="n">
-        <s:v>1</s:v>
-      </s:c>
-      <s:c r="I76" s="1" t="n">
-        <s:v>378.99</s:v>
-      </s:c>
-      <s:c r="J76" s="1" t="n">
-        <s:v>0</s:v>
-      </s:c>
-      <s:c r="K76" s="1" t="n">
-        <s:v>448.1</s:v>
-      </s:c>
-      <s:c r="L76" s="1" t="n">
-        <s:v>400</s:v>
-      </s:c>
-      <s:c r="M76" s="1" t="n">
-        <s:v>0</s:v>
-      </s:c>
-      <s:c r="N76" s="1" t="n">
-        <s:v>15543.19</s:v>
-      </s:c>
-      <s:c r="O76" s="1" t="n">
-        <s:v>389.37</s:v>
-      </s:c>
+      <s:c r="F76" s="1"/>
+      <s:c r="G76" s="1"/>
+      <s:c r="H76" s="1"/>
+      <s:c r="I76" s="1"/>
+      <s:c r="J76" s="1"/>
+      <s:c r="K76" s="1"/>
+      <s:c r="L76" s="1"/>
+      <s:c r="M76" s="1"/>
+      <s:c r="N76" s="1"/>
+      <s:c r="O76" s="1"/>
       <s:c r="P76" s="1" t="n">
         <s:v>64</s:v>
       </s:c>
@@ -7802,36 +6494,16 @@
       <s:c r="E77" s="1" t="n">
         <s:v>394.08</s:v>
       </s:c>
-      <s:c r="F77" s="1" t="n">
-        <s:v>2145</s:v>
-      </s:c>
-      <s:c r="G77" s="1" t="n">
-        <s:v>2621.39</s:v>
-      </s:c>
-      <s:c r="H77" s="1" t="n">
-        <s:v>1</s:v>
-      </s:c>
-      <s:c r="I77" s="1" t="n">
-        <s:v>213.75</s:v>
-      </s:c>
-      <s:c r="J77" s="1" t="n">
-        <s:v>0</s:v>
-      </s:c>
-      <s:c r="K77" s="1" t="n">
-        <s:v>302.9</s:v>
-      </s:c>
-      <s:c r="L77" s="1" t="n">
-        <s:v>400</s:v>
-      </s:c>
-      <s:c r="M77" s="1" t="n">
-        <s:v>0</s:v>
-      </s:c>
-      <s:c r="N77" s="1" t="n">
-        <s:v>15753.2</s:v>
-      </s:c>
-      <s:c r="O77" s="1" t="n">
-        <s:v>374.86</s:v>
-      </s:c>
+      <s:c r="F77" s="1"/>
+      <s:c r="G77" s="1"/>
+      <s:c r="H77" s="1"/>
+      <s:c r="I77" s="1"/>
+      <s:c r="J77" s="1"/>
+      <s:c r="K77" s="1"/>
+      <s:c r="L77" s="1"/>
+      <s:c r="M77" s="1"/>
+      <s:c r="N77" s="1"/>
+      <s:c r="O77" s="1"/>
       <s:c r="P77" s="1" t="n">
         <s:v>64</s:v>
       </s:c>
@@ -7852,36 +6524,16 @@
       <s:c r="E78" s="1" t="n">
         <s:v>393.85</s:v>
       </s:c>
-      <s:c r="F78" s="1" t="n">
-        <s:v>1270</s:v>
-      </s:c>
-      <s:c r="G78" s="1" t="n">
-        <s:v>2619.89</s:v>
-      </s:c>
-      <s:c r="H78" s="1" t="n">
-        <s:v>1</s:v>
-      </s:c>
-      <s:c r="I78" s="1" t="n">
-        <s:v>202.95</s:v>
-      </s:c>
-      <s:c r="J78" s="1" t="n">
-        <s:v>0</s:v>
-      </s:c>
-      <s:c r="K78" s="1" t="n">
-        <s:v>300.5</s:v>
-      </s:c>
-      <s:c r="L78" s="1" t="n">
-        <s:v>400</s:v>
-      </s:c>
-      <s:c r="M78" s="1" t="n">
-        <s:v>0</s:v>
-      </s:c>
-      <s:c r="N78" s="1" t="n">
-        <s:v>16263.8</s:v>
-      </s:c>
-      <s:c r="O78" s="1" t="n">
-        <s:v>377.47</s:v>
-      </s:c>
+      <s:c r="F78" s="1"/>
+      <s:c r="G78" s="1"/>
+      <s:c r="H78" s="1"/>
+      <s:c r="I78" s="1"/>
+      <s:c r="J78" s="1"/>
+      <s:c r="K78" s="1"/>
+      <s:c r="L78" s="1"/>
+      <s:c r="M78" s="1"/>
+      <s:c r="N78" s="1"/>
+      <s:c r="O78" s="1"/>
       <s:c r="P78" s="1" t="n">
         <s:v>64</s:v>
       </s:c>
@@ -7902,36 +6554,16 @@
       <s:c r="E79" s="1" t="n">
         <s:v>394.6</s:v>
       </s:c>
-      <s:c r="F79" s="1" t="n">
-        <s:v>850</s:v>
-      </s:c>
-      <s:c r="G79" s="1" t="n">
-        <s:v>2599.87</s:v>
-      </s:c>
-      <s:c r="H79" s="1" t="n">
-        <s:v>1</s:v>
-      </s:c>
-      <s:c r="I79" s="1" t="n">
-        <s:v>216.75</s:v>
-      </s:c>
-      <s:c r="J79" s="1" t="n">
-        <s:v>0</s:v>
-      </s:c>
-      <s:c r="K79" s="1" t="n">
-        <s:v>300.2</s:v>
-      </s:c>
-      <s:c r="L79" s="1" t="n">
-        <s:v>400</s:v>
-      </s:c>
-      <s:c r="M79" s="1" t="n">
-        <s:v>0</s:v>
-      </s:c>
-      <s:c r="N79" s="1" t="n">
-        <s:v>16625.82</s:v>
-      </s:c>
-      <s:c r="O79" s="1" t="n">
-        <s:v>381.25</s:v>
-      </s:c>
+      <s:c r="F79" s="1"/>
+      <s:c r="G79" s="1"/>
+      <s:c r="H79" s="1"/>
+      <s:c r="I79" s="1"/>
+      <s:c r="J79" s="1"/>
+      <s:c r="K79" s="1"/>
+      <s:c r="L79" s="1"/>
+      <s:c r="M79" s="1"/>
+      <s:c r="N79" s="1"/>
+      <s:c r="O79" s="1"/>
       <s:c r="P79" s="1" t="n">
         <s:v>64</s:v>
       </s:c>
@@ -7952,36 +6584,16 @@
       <s:c r="E80" s="1" t="n">
         <s:v>389.54</s:v>
       </s:c>
-      <s:c r="F80" s="1" t="n">
-        <s:v>330</s:v>
-      </s:c>
-      <s:c r="G80" s="1" t="n">
-        <s:v>2589.37</s:v>
-      </s:c>
-      <s:c r="H80" s="1" t="n">
-        <s:v>1</s:v>
-      </s:c>
-      <s:c r="I80" s="1" t="n">
-        <s:v>148.2</s:v>
-      </s:c>
-      <s:c r="J80" s="1" t="n">
-        <s:v>0</s:v>
-      </s:c>
-      <s:c r="K80" s="1" t="n">
-        <s:v>300.4</s:v>
-      </s:c>
-      <s:c r="L80" s="1" t="n">
-        <s:v>400</s:v>
-      </s:c>
-      <s:c r="M80" s="1" t="n">
-        <s:v>0</s:v>
-      </s:c>
-      <s:c r="N80" s="1" t="n">
-        <s:v>17090.55</s:v>
-      </s:c>
-      <s:c r="O80" s="1" t="n">
-        <s:v>370.47</s:v>
-      </s:c>
+      <s:c r="F80" s="1"/>
+      <s:c r="G80" s="1"/>
+      <s:c r="H80" s="1"/>
+      <s:c r="I80" s="1"/>
+      <s:c r="J80" s="1"/>
+      <s:c r="K80" s="1"/>
+      <s:c r="L80" s="1"/>
+      <s:c r="M80" s="1"/>
+      <s:c r="N80" s="1"/>
+      <s:c r="O80" s="1"/>
       <s:c r="P80" s="1" t="n">
         <s:v>64</s:v>
       </s:c>
@@ -8002,36 +6614,16 @@
       <s:c r="E81" s="1" t="n">
         <s:v>385</s:v>
       </s:c>
-      <s:c r="F81" s="1" t="n">
-        <s:v>130</s:v>
-      </s:c>
-      <s:c r="G81" s="1" t="n">
-        <s:v>2610.16</s:v>
-      </s:c>
-      <s:c r="H81" s="1" t="n">
-        <s:v>1</s:v>
-      </s:c>
-      <s:c r="I81" s="1" t="n">
-        <s:v>142.2</s:v>
-      </s:c>
-      <s:c r="J81" s="1" t="n">
-        <s:v>0</s:v>
-      </s:c>
-      <s:c r="K81" s="1" t="n">
-        <s:v>150</s:v>
-      </s:c>
-      <s:c r="L81" s="1" t="n">
-        <s:v>400</s:v>
-      </s:c>
-      <s:c r="M81" s="1" t="n">
-        <s:v>0</s:v>
-      </s:c>
-      <s:c r="N81" s="1" t="n">
-        <s:v>16739.58</s:v>
-      </s:c>
-      <s:c r="O81" s="1" t="n">
-        <s:v>406.66</s:v>
-      </s:c>
+      <s:c r="F81" s="1"/>
+      <s:c r="G81" s="1"/>
+      <s:c r="H81" s="1"/>
+      <s:c r="I81" s="1"/>
+      <s:c r="J81" s="1"/>
+      <s:c r="K81" s="1"/>
+      <s:c r="L81" s="1"/>
+      <s:c r="M81" s="1"/>
+      <s:c r="N81" s="1"/>
+      <s:c r="O81" s="1"/>
       <s:c r="P81" s="1" t="n">
         <s:v>64</s:v>
       </s:c>
@@ -8052,36 +6644,16 @@
       <s:c r="E82" s="1" t="n">
         <s:v>395.75</s:v>
       </s:c>
-      <s:c r="F82" s="1" t="n">
-        <s:v>0</s:v>
-      </s:c>
-      <s:c r="G82" s="1" t="n">
-        <s:v>2614.64</s:v>
-      </s:c>
-      <s:c r="H82" s="1" t="n">
-        <s:v>1</s:v>
-      </s:c>
-      <s:c r="I82" s="1" t="n">
-        <s:v>126.5</s:v>
-      </s:c>
-      <s:c r="J82" s="1" t="n">
-        <s:v>0</s:v>
-      </s:c>
-      <s:c r="K82" s="1" t="n">
-        <s:v>0</s:v>
-      </s:c>
-      <s:c r="L82" s="1" t="n">
-        <s:v>400</s:v>
-      </s:c>
-      <s:c r="M82" s="1" t="n">
-        <s:v>0</s:v>
-      </s:c>
-      <s:c r="N82" s="1" t="n">
-        <s:v>16683</s:v>
-      </s:c>
-      <s:c r="O82" s="1" t="n">
-        <s:v>430.97</s:v>
-      </s:c>
+      <s:c r="F82" s="1"/>
+      <s:c r="G82" s="1"/>
+      <s:c r="H82" s="1"/>
+      <s:c r="I82" s="1"/>
+      <s:c r="J82" s="1"/>
+      <s:c r="K82" s="1"/>
+      <s:c r="L82" s="1"/>
+      <s:c r="M82" s="1"/>
+      <s:c r="N82" s="1"/>
+      <s:c r="O82" s="1"/>
       <s:c r="P82" s="1" t="n">
         <s:v>64</s:v>
       </s:c>
@@ -8102,36 +6674,16 @@
       <s:c r="E83" s="1" t="n">
         <s:v>383.1</s:v>
       </s:c>
-      <s:c r="F83" s="1" t="n">
-        <s:v>90</s:v>
-      </s:c>
-      <s:c r="G83" s="1" t="n">
-        <s:v>2654.09</s:v>
-      </s:c>
-      <s:c r="H83" s="1" t="n">
-        <s:v>1</s:v>
-      </s:c>
-      <s:c r="I83" s="1" t="n">
-        <s:v>123.5</s:v>
-      </s:c>
-      <s:c r="J83" s="1" t="n">
-        <s:v>0</s:v>
-      </s:c>
-      <s:c r="K83" s="1" t="n">
-        <s:v>0</s:v>
-      </s:c>
-      <s:c r="L83" s="1" t="n">
-        <s:v>400</s:v>
-      </s:c>
-      <s:c r="M83" s="1" t="n">
-        <s:v>0</s:v>
-      </s:c>
-      <s:c r="N83" s="1" t="n">
-        <s:v>16460.45</s:v>
-      </s:c>
-      <s:c r="O83" s="1" t="n">
-        <s:v>437.75</s:v>
-      </s:c>
+      <s:c r="F83" s="1"/>
+      <s:c r="G83" s="1"/>
+      <s:c r="H83" s="1"/>
+      <s:c r="I83" s="1"/>
+      <s:c r="J83" s="1"/>
+      <s:c r="K83" s="1"/>
+      <s:c r="L83" s="1"/>
+      <s:c r="M83" s="1"/>
+      <s:c r="N83" s="1"/>
+      <s:c r="O83" s="1"/>
       <s:c r="P83" s="1" t="n">
         <s:v>64</s:v>
       </s:c>
@@ -8152,36 +6704,16 @@
       <s:c r="E84" s="1" t="n">
         <s:v>380.98</s:v>
       </s:c>
-      <s:c r="F84" s="1" t="n">
-        <s:v>90</s:v>
-      </s:c>
-      <s:c r="G84" s="1" t="n">
-        <s:v>2658.15</s:v>
-      </s:c>
-      <s:c r="H84" s="1" t="n">
-        <s:v>1</s:v>
-      </s:c>
-      <s:c r="I84" s="1" t="n">
-        <s:v>109.9</s:v>
-      </s:c>
-      <s:c r="J84" s="1" t="n">
-        <s:v>0</s:v>
-      </s:c>
-      <s:c r="K84" s="1" t="n">
-        <s:v>0</s:v>
-      </s:c>
-      <s:c r="L84" s="1" t="n">
-        <s:v>400</s:v>
-      </s:c>
-      <s:c r="M84" s="1" t="n">
-        <s:v>0</s:v>
-      </s:c>
-      <s:c r="N84" s="1" t="n">
-        <s:v>15932.29</s:v>
-      </s:c>
-      <s:c r="O84" s="1" t="n">
-        <s:v>435.86</s:v>
-      </s:c>
+      <s:c r="F84" s="1"/>
+      <s:c r="G84" s="1"/>
+      <s:c r="H84" s="1"/>
+      <s:c r="I84" s="1"/>
+      <s:c r="J84" s="1"/>
+      <s:c r="K84" s="1"/>
+      <s:c r="L84" s="1"/>
+      <s:c r="M84" s="1"/>
+      <s:c r="N84" s="1"/>
+      <s:c r="O84" s="1"/>
       <s:c r="P84" s="1" t="n">
         <s:v>64</s:v>
       </s:c>
@@ -8202,36 +6734,16 @@
       <s:c r="E85" s="1" t="n">
         <s:v>393.23</s:v>
       </s:c>
-      <s:c r="F85" s="1" t="n">
-        <s:v>90</s:v>
-      </s:c>
-      <s:c r="G85" s="1" t="n">
-        <s:v>2674.89</s:v>
-      </s:c>
-      <s:c r="H85" s="1" t="n">
-        <s:v>1</s:v>
-      </s:c>
-      <s:c r="I85" s="1" t="n">
-        <s:v>100.45</s:v>
-      </s:c>
-      <s:c r="J85" s="1" t="n">
-        <s:v>0</s:v>
-      </s:c>
-      <s:c r="K85" s="1" t="n">
-        <s:v>0</s:v>
-      </s:c>
-      <s:c r="L85" s="1" t="n">
-        <s:v>400</s:v>
-      </s:c>
-      <s:c r="M85" s="1" t="n">
-        <s:v>0</s:v>
-      </s:c>
-      <s:c r="N85" s="1" t="n">
-        <s:v>16051.82</s:v>
-      </s:c>
-      <s:c r="O85" s="1" t="n">
-        <s:v>427.64</s:v>
-      </s:c>
+      <s:c r="F85" s="1"/>
+      <s:c r="G85" s="1"/>
+      <s:c r="H85" s="1"/>
+      <s:c r="I85" s="1"/>
+      <s:c r="J85" s="1"/>
+      <s:c r="K85" s="1"/>
+      <s:c r="L85" s="1"/>
+      <s:c r="M85" s="1"/>
+      <s:c r="N85" s="1"/>
+      <s:c r="O85" s="1"/>
       <s:c r="P85" s="1" t="n">
         <s:v>64</s:v>
       </s:c>
@@ -8252,36 +6764,16 @@
       <s:c r="E86" s="1" t="n">
         <s:v>392.7</s:v>
       </s:c>
-      <s:c r="F86" s="1" t="n">
-        <s:v>90</s:v>
-      </s:c>
-      <s:c r="G86" s="1" t="n">
-        <s:v>2677.38</s:v>
-      </s:c>
-      <s:c r="H86" s="1" t="n">
-        <s:v>1</s:v>
-      </s:c>
-      <s:c r="I86" s="1" t="n">
-        <s:v>42.6</s:v>
-      </s:c>
-      <s:c r="J86" s="1" t="n">
-        <s:v>0</s:v>
-      </s:c>
-      <s:c r="K86" s="1" t="n">
-        <s:v>0</s:v>
-      </s:c>
-      <s:c r="L86" s="1" t="n">
-        <s:v>400</s:v>
-      </s:c>
-      <s:c r="M86" s="1" t="n">
-        <s:v>0</s:v>
-      </s:c>
-      <s:c r="N86" s="1" t="n">
-        <s:v>15960.45</s:v>
-      </s:c>
-      <s:c r="O86" s="1" t="n">
-        <s:v>460.48</s:v>
-      </s:c>
+      <s:c r="F86" s="1"/>
+      <s:c r="G86" s="1"/>
+      <s:c r="H86" s="1"/>
+      <s:c r="I86" s="1"/>
+      <s:c r="J86" s="1"/>
+      <s:c r="K86" s="1"/>
+      <s:c r="L86" s="1"/>
+      <s:c r="M86" s="1"/>
+      <s:c r="N86" s="1"/>
+      <s:c r="O86" s="1"/>
       <s:c r="P86" s="1" t="n">
         <s:v>64</s:v>
       </s:c>
@@ -8302,36 +6794,16 @@
       <s:c r="E87" s="1" t="n">
         <s:v>394.51</s:v>
       </s:c>
-      <s:c r="F87" s="1" t="n">
-        <s:v>190</s:v>
-      </s:c>
-      <s:c r="G87" s="1" t="n">
-        <s:v>2672.98</s:v>
-      </s:c>
-      <s:c r="H87" s="1" t="n">
-        <s:v>1</s:v>
-      </s:c>
-      <s:c r="I87" s="1" t="n">
-        <s:v>41.7</s:v>
-      </s:c>
-      <s:c r="J87" s="1" t="n">
-        <s:v>0</s:v>
-      </s:c>
-      <s:c r="K87" s="1" t="n">
-        <s:v>0</s:v>
-      </s:c>
-      <s:c r="L87" s="1" t="n">
-        <s:v>400</s:v>
-      </s:c>
-      <s:c r="M87" s="1" t="n">
-        <s:v>0</s:v>
-      </s:c>
-      <s:c r="N87" s="1" t="n">
-        <s:v>16115.6</s:v>
-      </s:c>
-      <s:c r="O87" s="1" t="n">
-        <s:v>505.52</s:v>
-      </s:c>
+      <s:c r="F87" s="1"/>
+      <s:c r="G87" s="1"/>
+      <s:c r="H87" s="1"/>
+      <s:c r="I87" s="1"/>
+      <s:c r="J87" s="1"/>
+      <s:c r="K87" s="1"/>
+      <s:c r="L87" s="1"/>
+      <s:c r="M87" s="1"/>
+      <s:c r="N87" s="1"/>
+      <s:c r="O87" s="1"/>
       <s:c r="P87" s="1" t="n">
         <s:v>64</s:v>
       </s:c>
@@ -8352,36 +6824,16 @@
       <s:c r="E88" s="1" t="n">
         <s:v>400.54</s:v>
       </s:c>
-      <s:c r="F88" s="1" t="n">
-        <s:v>190</s:v>
-      </s:c>
-      <s:c r="G88" s="1" t="n">
-        <s:v>2664.79</s:v>
-      </s:c>
-      <s:c r="H88" s="1" t="n">
-        <s:v>1</s:v>
-      </s:c>
-      <s:c r="I88" s="1" t="n">
-        <s:v>41.7</s:v>
-      </s:c>
-      <s:c r="J88" s="1" t="n">
-        <s:v>0</s:v>
-      </s:c>
-      <s:c r="K88" s="1" t="n">
-        <s:v>0</s:v>
-      </s:c>
-      <s:c r="L88" s="1" t="n">
-        <s:v>400</s:v>
-      </s:c>
-      <s:c r="M88" s="1" t="n">
-        <s:v>0</s:v>
-      </s:c>
-      <s:c r="N88" s="1" t="n">
-        <s:v>16405.43</s:v>
-      </s:c>
-      <s:c r="O88" s="1" t="n">
-        <s:v>550.17</s:v>
-      </s:c>
+      <s:c r="F88" s="1"/>
+      <s:c r="G88" s="1"/>
+      <s:c r="H88" s="1"/>
+      <s:c r="I88" s="1"/>
+      <s:c r="J88" s="1"/>
+      <s:c r="K88" s="1"/>
+      <s:c r="L88" s="1"/>
+      <s:c r="M88" s="1"/>
+      <s:c r="N88" s="1"/>
+      <s:c r="O88" s="1"/>
       <s:c r="P88" s="1" t="n">
         <s:v>64</s:v>
       </s:c>
@@ -8402,36 +6854,16 @@
       <s:c r="E89" s="1" t="n">
         <s:v>395.79</s:v>
       </s:c>
-      <s:c r="F89" s="1" t="n">
-        <s:v>420</s:v>
-      </s:c>
-      <s:c r="G89" s="1" t="n">
-        <s:v>2646.7</s:v>
-      </s:c>
-      <s:c r="H89" s="1" t="n">
-        <s:v>1</s:v>
-      </s:c>
-      <s:c r="I89" s="1" t="n">
-        <s:v>41.7</s:v>
-      </s:c>
-      <s:c r="J89" s="1" t="n">
-        <s:v>0</s:v>
-      </s:c>
-      <s:c r="K89" s="1" t="n">
-        <s:v>0</s:v>
-      </s:c>
-      <s:c r="L89" s="1" t="n">
-        <s:v>400</s:v>
-      </s:c>
-      <s:c r="M89" s="1" t="n">
-        <s:v>0</s:v>
-      </s:c>
-      <s:c r="N89" s="1" t="n">
-        <s:v>16360.23</s:v>
-      </s:c>
-      <s:c r="O89" s="1" t="n">
-        <s:v>566.57</s:v>
-      </s:c>
+      <s:c r="F89" s="1"/>
+      <s:c r="G89" s="1"/>
+      <s:c r="H89" s="1"/>
+      <s:c r="I89" s="1"/>
+      <s:c r="J89" s="1"/>
+      <s:c r="K89" s="1"/>
+      <s:c r="L89" s="1"/>
+      <s:c r="M89" s="1"/>
+      <s:c r="N89" s="1"/>
+      <s:c r="O89" s="1"/>
       <s:c r="P89" s="1" t="n">
         <s:v>64</s:v>
       </s:c>
@@ -8452,36 +6884,16 @@
       <s:c r="E90" s="1" t="n">
         <s:v>395.45</s:v>
       </s:c>
-      <s:c r="F90" s="1" t="n">
-        <s:v>950</s:v>
-      </s:c>
-      <s:c r="G90" s="1" t="n">
-        <s:v>2635.56</s:v>
-      </s:c>
-      <s:c r="H90" s="1" t="n">
-        <s:v>1</s:v>
-      </s:c>
-      <s:c r="I90" s="1" t="n">
-        <s:v>41.7</s:v>
-      </s:c>
-      <s:c r="J90" s="1" t="n">
-        <s:v>0</s:v>
-      </s:c>
-      <s:c r="K90" s="1" t="n">
-        <s:v>0</s:v>
-      </s:c>
-      <s:c r="L90" s="1" t="n">
-        <s:v>400</s:v>
-      </s:c>
-      <s:c r="M90" s="1" t="n">
-        <s:v>0</s:v>
-      </s:c>
-      <s:c r="N90" s="1" t="n">
-        <s:v>16187.6</s:v>
-      </s:c>
-      <s:c r="O90" s="1" t="n">
-        <s:v>598.04</s:v>
-      </s:c>
+      <s:c r="F90" s="1"/>
+      <s:c r="G90" s="1"/>
+      <s:c r="H90" s="1"/>
+      <s:c r="I90" s="1"/>
+      <s:c r="J90" s="1"/>
+      <s:c r="K90" s="1"/>
+      <s:c r="L90" s="1"/>
+      <s:c r="M90" s="1"/>
+      <s:c r="N90" s="1"/>
+      <s:c r="O90" s="1"/>
       <s:c r="P90" s="1" t="n">
         <s:v>64</s:v>
       </s:c>
@@ -8502,36 +6914,16 @@
       <s:c r="E91" s="1" t="n">
         <s:v>395.75</s:v>
       </s:c>
-      <s:c r="F91" s="1" t="n">
-        <s:v>1220</s:v>
-      </s:c>
-      <s:c r="G91" s="1" t="n">
-        <s:v>2635.16</s:v>
-      </s:c>
-      <s:c r="H91" s="1" t="n">
-        <s:v>1</s:v>
-      </s:c>
-      <s:c r="I91" s="1" t="n">
-        <s:v>23.7</s:v>
-      </s:c>
-      <s:c r="J91" s="1" t="n">
-        <s:v>0</s:v>
-      </s:c>
-      <s:c r="K91" s="1" t="n">
-        <s:v>0</s:v>
-      </s:c>
-      <s:c r="L91" s="1" t="n">
-        <s:v>400</s:v>
-      </s:c>
-      <s:c r="M91" s="1" t="n">
-        <s:v>0</s:v>
-      </s:c>
-      <s:c r="N91" s="1" t="n">
-        <s:v>16180.16</s:v>
-      </s:c>
-      <s:c r="O91" s="1" t="n">
-        <s:v>607.98</s:v>
-      </s:c>
+      <s:c r="F91" s="1"/>
+      <s:c r="G91" s="1"/>
+      <s:c r="H91" s="1"/>
+      <s:c r="I91" s="1"/>
+      <s:c r="J91" s="1"/>
+      <s:c r="K91" s="1"/>
+      <s:c r="L91" s="1"/>
+      <s:c r="M91" s="1"/>
+      <s:c r="N91" s="1"/>
+      <s:c r="O91" s="1"/>
       <s:c r="P91" s="1" t="n">
         <s:v>64</s:v>
       </s:c>
@@ -8552,36 +6944,16 @@
       <s:c r="E92" s="1" t="n">
         <s:v>395.35</s:v>
       </s:c>
-      <s:c r="F92" s="1" t="n">
-        <s:v>1520</s:v>
-      </s:c>
-      <s:c r="G92" s="1" t="n">
-        <s:v>2600.98</s:v>
-      </s:c>
-      <s:c r="H92" s="1" t="n">
-        <s:v>1</s:v>
-      </s:c>
-      <s:c r="I92" s="1" t="n">
-        <s:v>23.7</s:v>
-      </s:c>
-      <s:c r="J92" s="1" t="n">
-        <s:v>0</s:v>
-      </s:c>
-      <s:c r="K92" s="1" t="n">
-        <s:v>150.4</s:v>
-      </s:c>
-      <s:c r="L92" s="1" t="n">
-        <s:v>400</s:v>
-      </s:c>
-      <s:c r="M92" s="1" t="n">
-        <s:v>0</s:v>
-      </s:c>
-      <s:c r="N92" s="1" t="n">
-        <s:v>15947.11</s:v>
-      </s:c>
-      <s:c r="O92" s="1" t="n">
-        <s:v>622.11</s:v>
-      </s:c>
+      <s:c r="F92" s="1"/>
+      <s:c r="G92" s="1"/>
+      <s:c r="H92" s="1"/>
+      <s:c r="I92" s="1"/>
+      <s:c r="J92" s="1"/>
+      <s:c r="K92" s="1"/>
+      <s:c r="L92" s="1"/>
+      <s:c r="M92" s="1"/>
+      <s:c r="N92" s="1"/>
+      <s:c r="O92" s="1"/>
       <s:c r="P92" s="1" t="n">
         <s:v>64</s:v>
       </s:c>
@@ -8602,36 +6974,16 @@
       <s:c r="E93" s="1" t="n">
         <s:v>403.98</s:v>
       </s:c>
-      <s:c r="F93" s="1" t="n">
-        <s:v>1620</s:v>
-      </s:c>
-      <s:c r="G93" s="1" t="n">
-        <s:v>2579.25</s:v>
-      </s:c>
-      <s:c r="H93" s="1" t="n">
-        <s:v>1</s:v>
-      </s:c>
-      <s:c r="I93" s="1" t="n">
-        <s:v>23.7</s:v>
-      </s:c>
-      <s:c r="J93" s="1" t="n">
-        <s:v>0</s:v>
-      </s:c>
-      <s:c r="K93" s="1" t="n">
-        <s:v>151.6</s:v>
-      </s:c>
-      <s:c r="L93" s="1" t="n">
-        <s:v>400</s:v>
-      </s:c>
-      <s:c r="M93" s="1" t="n">
-        <s:v>0</s:v>
-      </s:c>
-      <s:c r="N93" s="1" t="n">
-        <s:v>16370.05</s:v>
-      </s:c>
-      <s:c r="O93" s="1" t="n">
-        <s:v>635.7</s:v>
-      </s:c>
+      <s:c r="F93" s="1"/>
+      <s:c r="G93" s="1"/>
+      <s:c r="H93" s="1"/>
+      <s:c r="I93" s="1"/>
+      <s:c r="J93" s="1"/>
+      <s:c r="K93" s="1"/>
+      <s:c r="L93" s="1"/>
+      <s:c r="M93" s="1"/>
+      <s:c r="N93" s="1"/>
+      <s:c r="O93" s="1"/>
       <s:c r="P93" s="1" t="n">
         <s:v>64</s:v>
       </s:c>
@@ -8652,36 +7004,16 @@
       <s:c r="E94" s="1" t="n">
         <s:v>402.3</s:v>
       </s:c>
-      <s:c r="F94" s="1" t="n">
-        <s:v>2260</s:v>
-      </s:c>
-      <s:c r="G94" s="1" t="n">
-        <s:v>2537.73</s:v>
-      </s:c>
-      <s:c r="H94" s="1" t="n">
-        <s:v>1</s:v>
-      </s:c>
-      <s:c r="I94" s="1" t="n">
-        <s:v>23.7</s:v>
-      </s:c>
-      <s:c r="J94" s="1" t="n">
-        <s:v>0</s:v>
-      </s:c>
-      <s:c r="K94" s="1" t="n">
-        <s:v>251.3</s:v>
-      </s:c>
-      <s:c r="L94" s="1" t="n">
-        <s:v>400</s:v>
-      </s:c>
-      <s:c r="M94" s="1" t="n">
-        <s:v>0</s:v>
-      </s:c>
-      <s:c r="N94" s="1" t="n">
-        <s:v>16263.43</s:v>
-      </s:c>
-      <s:c r="O94" s="1" t="n">
-        <s:v>667.94</s:v>
-      </s:c>
+      <s:c r="F94" s="1"/>
+      <s:c r="G94" s="1"/>
+      <s:c r="H94" s="1"/>
+      <s:c r="I94" s="1"/>
+      <s:c r="J94" s="1"/>
+      <s:c r="K94" s="1"/>
+      <s:c r="L94" s="1"/>
+      <s:c r="M94" s="1"/>
+      <s:c r="N94" s="1"/>
+      <s:c r="O94" s="1"/>
       <s:c r="P94" s="1" t="n">
         <s:v>64</s:v>
       </s:c>
@@ -8702,36 +7034,16 @@
       <s:c r="E95" s="1" t="n">
         <s:v>383.97</s:v>
       </s:c>
-      <s:c r="F95" s="1" t="n">
-        <s:v>2390</s:v>
-      </s:c>
-      <s:c r="G95" s="1" t="n">
-        <s:v>2535.8</s:v>
-      </s:c>
-      <s:c r="H95" s="1" t="n">
-        <s:v>1</s:v>
-      </s:c>
-      <s:c r="I95" s="1" t="n">
-        <s:v>15.7</s:v>
-      </s:c>
-      <s:c r="J95" s="1" t="n">
-        <s:v>0</s:v>
-      </s:c>
-      <s:c r="K95" s="1" t="n">
-        <s:v>250.2</s:v>
-      </s:c>
-      <s:c r="L95" s="1" t="n">
-        <s:v>400</s:v>
-      </s:c>
-      <s:c r="M95" s="1" t="n">
-        <s:v>0</s:v>
-      </s:c>
-      <s:c r="N95" s="1" t="n">
-        <s:v>15641.33</s:v>
-      </s:c>
-      <s:c r="O95" s="1" t="n">
-        <s:v>686.76</s:v>
-      </s:c>
+      <s:c r="F95" s="1"/>
+      <s:c r="G95" s="1"/>
+      <s:c r="H95" s="1"/>
+      <s:c r="I95" s="1"/>
+      <s:c r="J95" s="1"/>
+      <s:c r="K95" s="1"/>
+      <s:c r="L95" s="1"/>
+      <s:c r="M95" s="1"/>
+      <s:c r="N95" s="1"/>
+      <s:c r="O95" s="1"/>
       <s:c r="P95" s="1" t="n">
         <s:v>64</s:v>
       </s:c>
@@ -8752,36 +7064,16 @@
       <s:c r="E96" s="1" t="n">
         <s:v>403.57</s:v>
       </s:c>
-      <s:c r="F96" s="1" t="n">
-        <s:v>1960</s:v>
-      </s:c>
-      <s:c r="G96" s="1" t="n">
-        <s:v>2537.52</s:v>
-      </s:c>
-      <s:c r="H96" s="1" t="n">
-        <s:v>1</s:v>
-      </s:c>
-      <s:c r="I96" s="1" t="n">
-        <s:v>9.7</s:v>
-      </s:c>
-      <s:c r="J96" s="1" t="n">
-        <s:v>0</s:v>
-      </s:c>
-      <s:c r="K96" s="1" t="n">
-        <s:v>151.1</s:v>
-      </s:c>
-      <s:c r="L96" s="1" t="n">
-        <s:v>400</s:v>
-      </s:c>
-      <s:c r="M96" s="1" t="n">
-        <s:v>0</s:v>
-      </s:c>
-      <s:c r="N96" s="1" t="n">
-        <s:v>15913.32</s:v>
-      </s:c>
-      <s:c r="O96" s="1" t="n">
-        <s:v>696.56</s:v>
-      </s:c>
+      <s:c r="F96" s="1"/>
+      <s:c r="G96" s="1"/>
+      <s:c r="H96" s="1"/>
+      <s:c r="I96" s="1"/>
+      <s:c r="J96" s="1"/>
+      <s:c r="K96" s="1"/>
+      <s:c r="L96" s="1"/>
+      <s:c r="M96" s="1"/>
+      <s:c r="N96" s="1"/>
+      <s:c r="O96" s="1"/>
       <s:c r="P96" s="1" t="n">
         <s:v>64</s:v>
       </s:c>
@@ -8804,36 +7096,16 @@
       <s:c r="E97" s="1" t="n">
         <s:v>429.66</s:v>
       </s:c>
-      <s:c r="F97" s="1" t="n">
-        <s:v>1060</s:v>
-      </s:c>
-      <s:c r="G97" s="1" t="n">
-        <s:v>2544.86</s:v>
-      </s:c>
-      <s:c r="H97" s="1" t="n">
-        <s:v>1</s:v>
-      </s:c>
-      <s:c r="I97" s="1" t="n">
-        <s:v>3.7</s:v>
-      </s:c>
-      <s:c r="J97" s="1" t="n">
-        <s:v>0</s:v>
-      </s:c>
-      <s:c r="K97" s="1" t="n">
-        <s:v>150.7</s:v>
-      </s:c>
-      <s:c r="L97" s="1" t="n">
-        <s:v>400</s:v>
-      </s:c>
-      <s:c r="M97" s="1" t="n">
-        <s:v>0</s:v>
-      </s:c>
-      <s:c r="N97" s="1" t="n">
-        <s:v>16646.15</s:v>
-      </s:c>
-      <s:c r="O97" s="1" t="n">
-        <s:v>715.49</s:v>
-      </s:c>
+      <s:c r="F97" s="1"/>
+      <s:c r="G97" s="1"/>
+      <s:c r="H97" s="1"/>
+      <s:c r="I97" s="1"/>
+      <s:c r="J97" s="1"/>
+      <s:c r="K97" s="1"/>
+      <s:c r="L97" s="1"/>
+      <s:c r="M97" s="1"/>
+      <s:c r="N97" s="1"/>
+      <s:c r="O97" s="1"/>
       <s:c r="P97" s="1" t="n">
         <s:v>64</s:v>
       </s:c>

--- a/review-results/河北实时运行及市场出清数据-20260829.xlsx
+++ b/review-results/河北实时运行及市场出清数据-20260829.xlsx
@@ -4244,16 +4244,36 @@
       <s:c r="E2" s="1" t="n">
         <s:v>394.08</s:v>
       </s:c>
-      <s:c r="F2" s="1"/>
-      <s:c r="G2" s="1"/>
-      <s:c r="H2" s="1"/>
-      <s:c r="I2" s="1"/>
-      <s:c r="J2" s="1"/>
-      <s:c r="K2" s="1"/>
-      <s:c r="L2" s="1"/>
-      <s:c r="M2" s="1"/>
-      <s:c r="N2" s="1"/>
-      <s:c r="O2" s="1"/>
+      <s:c r="F2" s="1" t="n">
+        <s:v>330</s:v>
+      </s:c>
+      <s:c r="G2" s="1" t="n">
+        <s:v>2387.17</s:v>
+      </s:c>
+      <s:c r="H2" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="I2" s="1" t="n">
+        <s:v>3.7</s:v>
+      </s:c>
+      <s:c r="J2" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="K2" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="L2" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="M2" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="N2" s="1" t="n">
+        <s:v>17202.78</s:v>
+      </s:c>
+      <s:c r="O2" s="1" t="n">
+        <s:v>1084.75</s:v>
+      </s:c>
       <s:c r="P2" s="1" t="n">
         <s:v>69</s:v>
       </s:c>
@@ -4274,16 +4294,36 @@
       <s:c r="E3" s="1" t="n">
         <s:v>395.35</s:v>
       </s:c>
-      <s:c r="F3" s="1"/>
-      <s:c r="G3" s="1"/>
-      <s:c r="H3" s="1"/>
-      <s:c r="I3" s="1"/>
-      <s:c r="J3" s="1"/>
-      <s:c r="K3" s="1"/>
-      <s:c r="L3" s="1"/>
-      <s:c r="M3" s="1"/>
-      <s:c r="N3" s="1"/>
-      <s:c r="O3" s="1"/>
+      <s:c r="F3" s="1" t="n">
+        <s:v>600</s:v>
+      </s:c>
+      <s:c r="G3" s="1" t="n">
+        <s:v>2363.69</s:v>
+      </s:c>
+      <s:c r="H3" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="I3" s="1" t="n">
+        <s:v>3.7</s:v>
+      </s:c>
+      <s:c r="J3" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="K3" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="L3" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="M3" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="N3" s="1" t="n">
+        <s:v>17141.21</s:v>
+      </s:c>
+      <s:c r="O3" s="1" t="n">
+        <s:v>1007.4</s:v>
+      </s:c>
       <s:c r="P3" s="1" t="n">
         <s:v>69</s:v>
       </s:c>
@@ -4304,16 +4344,36 @@
       <s:c r="E4" s="1" t="n">
         <s:v>384.72</s:v>
       </s:c>
-      <s:c r="F4" s="1"/>
-      <s:c r="G4" s="1"/>
-      <s:c r="H4" s="1"/>
-      <s:c r="I4" s="1"/>
-      <s:c r="J4" s="1"/>
-      <s:c r="K4" s="1"/>
-      <s:c r="L4" s="1"/>
-      <s:c r="M4" s="1"/>
-      <s:c r="N4" s="1"/>
-      <s:c r="O4" s="1"/>
+      <s:c r="F4" s="1" t="n">
+        <s:v>960</s:v>
+      </s:c>
+      <s:c r="G4" s="1" t="n">
+        <s:v>2363.31</s:v>
+      </s:c>
+      <s:c r="H4" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="I4" s="1" t="n">
+        <s:v>3.7</s:v>
+      </s:c>
+      <s:c r="J4" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="K4" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="L4" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="M4" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="N4" s="1" t="n">
+        <s:v>16727.19</s:v>
+      </s:c>
+      <s:c r="O4" s="1" t="n">
+        <s:v>850.6</s:v>
+      </s:c>
       <s:c r="P4" s="1" t="n">
         <s:v>69</s:v>
       </s:c>
@@ -4334,16 +4394,36 @@
       <s:c r="E5" s="1" t="n">
         <s:v>384.42</s:v>
       </s:c>
-      <s:c r="F5" s="1"/>
-      <s:c r="G5" s="1"/>
-      <s:c r="H5" s="1"/>
-      <s:c r="I5" s="1"/>
-      <s:c r="J5" s="1"/>
-      <s:c r="K5" s="1"/>
-      <s:c r="L5" s="1"/>
-      <s:c r="M5" s="1"/>
-      <s:c r="N5" s="1"/>
-      <s:c r="O5" s="1"/>
+      <s:c r="F5" s="1" t="n">
+        <s:v>1010</s:v>
+      </s:c>
+      <s:c r="G5" s="1" t="n">
+        <s:v>2335.77</s:v>
+      </s:c>
+      <s:c r="H5" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="I5" s="1" t="n">
+        <s:v>3.7</s:v>
+      </s:c>
+      <s:c r="J5" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="K5" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="L5" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="M5" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="N5" s="1" t="n">
+        <s:v>16563.72</s:v>
+      </s:c>
+      <s:c r="O5" s="1" t="n">
+        <s:v>752.22</s:v>
+      </s:c>
       <s:c r="P5" s="1" t="n">
         <s:v>69</s:v>
       </s:c>
@@ -4364,16 +4444,36 @@
       <s:c r="E6" s="1" t="n">
         <s:v>392.76</s:v>
       </s:c>
-      <s:c r="F6" s="1"/>
-      <s:c r="G6" s="1"/>
-      <s:c r="H6" s="1"/>
-      <s:c r="I6" s="1"/>
-      <s:c r="J6" s="1"/>
-      <s:c r="K6" s="1"/>
-      <s:c r="L6" s="1"/>
-      <s:c r="M6" s="1"/>
-      <s:c r="N6" s="1"/>
-      <s:c r="O6" s="1"/>
+      <s:c r="F6" s="1" t="n">
+        <s:v>1465</s:v>
+      </s:c>
+      <s:c r="G6" s="1" t="n">
+        <s:v>2340.46</s:v>
+      </s:c>
+      <s:c r="H6" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="I6" s="1" t="n">
+        <s:v>3.7</s:v>
+      </s:c>
+      <s:c r="J6" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="K6" s="1" t="n">
+        <s:v>265.4</s:v>
+      </s:c>
+      <s:c r="L6" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="M6" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="N6" s="1" t="n">
+        <s:v>17481.1</s:v>
+      </s:c>
+      <s:c r="O6" s="1" t="n">
+        <s:v>731.64</s:v>
+      </s:c>
       <s:c r="P6" s="1" t="n">
         <s:v>69</s:v>
       </s:c>
@@ -4394,16 +4494,36 @@
       <s:c r="E7" s="1" t="n">
         <s:v>395.57</s:v>
       </s:c>
-      <s:c r="F7" s="1"/>
-      <s:c r="G7" s="1"/>
-      <s:c r="H7" s="1"/>
-      <s:c r="I7" s="1"/>
-      <s:c r="J7" s="1"/>
-      <s:c r="K7" s="1"/>
-      <s:c r="L7" s="1"/>
-      <s:c r="M7" s="1"/>
-      <s:c r="N7" s="1"/>
-      <s:c r="O7" s="1"/>
+      <s:c r="F7" s="1" t="n">
+        <s:v>1490</s:v>
+      </s:c>
+      <s:c r="G7" s="1" t="n">
+        <s:v>2317.24</s:v>
+      </s:c>
+      <s:c r="H7" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="I7" s="1" t="n">
+        <s:v>3.7</s:v>
+      </s:c>
+      <s:c r="J7" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="K7" s="1" t="n">
+        <s:v>302.9</s:v>
+      </s:c>
+      <s:c r="L7" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="M7" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="N7" s="1" t="n">
+        <s:v>17857.19</s:v>
+      </s:c>
+      <s:c r="O7" s="1" t="n">
+        <s:v>644.88</s:v>
+      </s:c>
       <s:c r="P7" s="1" t="n">
         <s:v>69</s:v>
       </s:c>
@@ -4424,16 +4544,36 @@
       <s:c r="E8" s="1" t="n">
         <s:v>403.35</s:v>
       </s:c>
-      <s:c r="F8" s="1"/>
-      <s:c r="G8" s="1"/>
-      <s:c r="H8" s="1"/>
-      <s:c r="I8" s="1"/>
-      <s:c r="J8" s="1"/>
-      <s:c r="K8" s="1"/>
-      <s:c r="L8" s="1"/>
-      <s:c r="M8" s="1"/>
-      <s:c r="N8" s="1"/>
-      <s:c r="O8" s="1"/>
+      <s:c r="F8" s="1" t="n">
+        <s:v>1460</s:v>
+      </s:c>
+      <s:c r="G8" s="1" t="n">
+        <s:v>2292.9</s:v>
+      </s:c>
+      <s:c r="H8" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="I8" s="1" t="n">
+        <s:v>3.7</s:v>
+      </s:c>
+      <s:c r="J8" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="K8" s="1" t="n">
+        <s:v>302.2</s:v>
+      </s:c>
+      <s:c r="L8" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="M8" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="N8" s="1" t="n">
+        <s:v>17966.85</s:v>
+      </s:c>
+      <s:c r="O8" s="1" t="n">
+        <s:v>619.25</s:v>
+      </s:c>
       <s:c r="P8" s="1" t="n">
         <s:v>68</s:v>
       </s:c>
@@ -4454,16 +4594,36 @@
       <s:c r="E9" s="1" t="n">
         <s:v>393.85</s:v>
       </s:c>
-      <s:c r="F9" s="1"/>
-      <s:c r="G9" s="1"/>
-      <s:c r="H9" s="1"/>
-      <s:c r="I9" s="1"/>
-      <s:c r="J9" s="1"/>
-      <s:c r="K9" s="1"/>
-      <s:c r="L9" s="1"/>
-      <s:c r="M9" s="1"/>
-      <s:c r="N9" s="1"/>
-      <s:c r="O9" s="1"/>
+      <s:c r="F9" s="1" t="n">
+        <s:v>1337.7</s:v>
+      </s:c>
+      <s:c r="G9" s="1" t="n">
+        <s:v>2339.96</s:v>
+      </s:c>
+      <s:c r="H9" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="I9" s="1" t="n">
+        <s:v>3.7</s:v>
+      </s:c>
+      <s:c r="J9" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="K9" s="1" t="n">
+        <s:v>302.3</s:v>
+      </s:c>
+      <s:c r="L9" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="M9" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="N9" s="1" t="n">
+        <s:v>17215.68</s:v>
+      </s:c>
+      <s:c r="O9" s="1" t="n">
+        <s:v>602.26</s:v>
+      </s:c>
       <s:c r="P9" s="1" t="n">
         <s:v>68</s:v>
       </s:c>
@@ -4484,16 +4644,36 @@
       <s:c r="E10" s="1" t="n">
         <s:v>415.5</s:v>
       </s:c>
-      <s:c r="F10" s="1"/>
-      <s:c r="G10" s="1"/>
-      <s:c r="H10" s="1"/>
-      <s:c r="I10" s="1"/>
-      <s:c r="J10" s="1"/>
-      <s:c r="K10" s="1"/>
-      <s:c r="L10" s="1"/>
-      <s:c r="M10" s="1"/>
-      <s:c r="N10" s="1"/>
-      <s:c r="O10" s="1"/>
+      <s:c r="F10" s="1" t="n">
+        <s:v>842.7</s:v>
+      </s:c>
+      <s:c r="G10" s="1" t="n">
+        <s:v>2301.87</s:v>
+      </s:c>
+      <s:c r="H10" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="I10" s="1" t="n">
+        <s:v>3.7</s:v>
+      </s:c>
+      <s:c r="J10" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="K10" s="1" t="n">
+        <s:v>302.4</s:v>
+      </s:c>
+      <s:c r="L10" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="M10" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="N10" s="1" t="n">
+        <s:v>17866.76</s:v>
+      </s:c>
+      <s:c r="O10" s="1" t="n">
+        <s:v>526.57</s:v>
+      </s:c>
       <s:c r="P10" s="1" t="n">
         <s:v>67</s:v>
       </s:c>
@@ -4514,16 +4694,36 @@
       <s:c r="E11" s="1" t="n">
         <s:v>405.63</s:v>
       </s:c>
-      <s:c r="F11" s="1"/>
-      <s:c r="G11" s="1"/>
-      <s:c r="H11" s="1"/>
-      <s:c r="I11" s="1"/>
-      <s:c r="J11" s="1"/>
-      <s:c r="K11" s="1"/>
-      <s:c r="L11" s="1"/>
-      <s:c r="M11" s="1"/>
-      <s:c r="N11" s="1"/>
-      <s:c r="O11" s="1"/>
+      <s:c r="F11" s="1" t="n">
+        <s:v>440</s:v>
+      </s:c>
+      <s:c r="G11" s="1" t="n">
+        <s:v>2353.08</s:v>
+      </s:c>
+      <s:c r="H11" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="I11" s="1" t="n">
+        <s:v>3.7</s:v>
+      </s:c>
+      <s:c r="J11" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="K11" s="1" t="n">
+        <s:v>300</s:v>
+      </s:c>
+      <s:c r="L11" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="M11" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="N11" s="1" t="n">
+        <s:v>17787.37</s:v>
+      </s:c>
+      <s:c r="O11" s="1" t="n">
+        <s:v>518.06</s:v>
+      </s:c>
       <s:c r="P11" s="1" t="n">
         <s:v>66</s:v>
       </s:c>
@@ -4544,16 +4744,36 @@
       <s:c r="E12" s="1" t="n">
         <s:v>403.98</s:v>
       </s:c>
-      <s:c r="F12" s="1"/>
-      <s:c r="G12" s="1"/>
-      <s:c r="H12" s="1"/>
-      <s:c r="I12" s="1"/>
-      <s:c r="J12" s="1"/>
-      <s:c r="K12" s="1"/>
-      <s:c r="L12" s="1"/>
-      <s:c r="M12" s="1"/>
-      <s:c r="N12" s="1"/>
-      <s:c r="O12" s="1"/>
+      <s:c r="F12" s="1" t="n">
+        <s:v>170</s:v>
+      </s:c>
+      <s:c r="G12" s="1" t="n">
+        <s:v>2369.05</s:v>
+      </s:c>
+      <s:c r="H12" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="I12" s="1" t="n">
+        <s:v>3.7</s:v>
+      </s:c>
+      <s:c r="J12" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="K12" s="1" t="n">
+        <s:v>496.3</s:v>
+      </s:c>
+      <s:c r="L12" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="M12" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="N12" s="1" t="n">
+        <s:v>17488.32</s:v>
+      </s:c>
+      <s:c r="O12" s="1" t="n">
+        <s:v>502.43</s:v>
+      </s:c>
       <s:c r="P12" s="1" t="n">
         <s:v>66</s:v>
       </s:c>
@@ -4574,16 +4794,36 @@
       <s:c r="E13" s="1" t="n">
         <s:v>400.54</s:v>
       </s:c>
-      <s:c r="F13" s="1"/>
-      <s:c r="G13" s="1"/>
-      <s:c r="H13" s="1"/>
-      <s:c r="I13" s="1"/>
-      <s:c r="J13" s="1"/>
-      <s:c r="K13" s="1"/>
-      <s:c r="L13" s="1"/>
-      <s:c r="M13" s="1"/>
-      <s:c r="N13" s="1"/>
-      <s:c r="O13" s="1"/>
+      <s:c r="F13" s="1" t="n">
+        <s:v>170</s:v>
+      </s:c>
+      <s:c r="G13" s="1" t="n">
+        <s:v>2395.73</s:v>
+      </s:c>
+      <s:c r="H13" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="I13" s="1" t="n">
+        <s:v>3.7</s:v>
+      </s:c>
+      <s:c r="J13" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="K13" s="1" t="n">
+        <s:v>251</s:v>
+      </s:c>
+      <s:c r="L13" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="M13" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="N13" s="1" t="n">
+        <s:v>17211.88</s:v>
+      </s:c>
+      <s:c r="O13" s="1" t="n">
+        <s:v>470.29</s:v>
+      </s:c>
       <s:c r="P13" s="1" t="n">
         <s:v>66</s:v>
       </s:c>
@@ -4604,16 +4844,36 @@
       <s:c r="E14" s="1" t="n">
         <s:v>403.98</s:v>
       </s:c>
-      <s:c r="F14" s="1"/>
-      <s:c r="G14" s="1"/>
-      <s:c r="H14" s="1"/>
-      <s:c r="I14" s="1"/>
-      <s:c r="J14" s="1"/>
-      <s:c r="K14" s="1"/>
-      <s:c r="L14" s="1"/>
-      <s:c r="M14" s="1"/>
-      <s:c r="N14" s="1"/>
-      <s:c r="O14" s="1"/>
+      <s:c r="F14" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="G14" s="1" t="n">
+        <s:v>2397.26</s:v>
+      </s:c>
+      <s:c r="H14" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="I14" s="1" t="n">
+        <s:v>3.7</s:v>
+      </s:c>
+      <s:c r="J14" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="K14" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="L14" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="M14" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="N14" s="1" t="n">
+        <s:v>17508.07</s:v>
+      </s:c>
+      <s:c r="O14" s="1" t="n">
+        <s:v>458.67</s:v>
+      </s:c>
       <s:c r="P14" s="1" t="n">
         <s:v>66</s:v>
       </s:c>
@@ -4634,16 +4894,36 @@
       <s:c r="E15" s="1" t="n">
         <s:v>402.64</s:v>
       </s:c>
-      <s:c r="F15" s="1"/>
-      <s:c r="G15" s="1"/>
-      <s:c r="H15" s="1"/>
-      <s:c r="I15" s="1"/>
-      <s:c r="J15" s="1"/>
-      <s:c r="K15" s="1"/>
-      <s:c r="L15" s="1"/>
-      <s:c r="M15" s="1"/>
-      <s:c r="N15" s="1"/>
-      <s:c r="O15" s="1"/>
+      <s:c r="F15" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="G15" s="1" t="n">
+        <s:v>2377.76</s:v>
+      </s:c>
+      <s:c r="H15" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="I15" s="1" t="n">
+        <s:v>3.7</s:v>
+      </s:c>
+      <s:c r="J15" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="K15" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="L15" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="M15" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="N15" s="1" t="n">
+        <s:v>17321.57</s:v>
+      </s:c>
+      <s:c r="O15" s="1" t="n">
+        <s:v>443.17</s:v>
+      </s:c>
       <s:c r="P15" s="1" t="n">
         <s:v>66</s:v>
       </s:c>
@@ -4664,16 +4944,36 @@
       <s:c r="E16" s="1" t="n">
         <s:v>395.85</s:v>
       </s:c>
-      <s:c r="F16" s="1"/>
-      <s:c r="G16" s="1"/>
-      <s:c r="H16" s="1"/>
-      <s:c r="I16" s="1"/>
-      <s:c r="J16" s="1"/>
-      <s:c r="K16" s="1"/>
-      <s:c r="L16" s="1"/>
-      <s:c r="M16" s="1"/>
-      <s:c r="N16" s="1"/>
-      <s:c r="O16" s="1"/>
+      <s:c r="F16" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="G16" s="1" t="n">
+        <s:v>2381.52</s:v>
+      </s:c>
+      <s:c r="H16" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="I16" s="1" t="n">
+        <s:v>3.7</s:v>
+      </s:c>
+      <s:c r="J16" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="K16" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="L16" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="M16" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="N16" s="1" t="n">
+        <s:v>17199.69</s:v>
+      </s:c>
+      <s:c r="O16" s="1" t="n">
+        <s:v>421.99</s:v>
+      </s:c>
       <s:c r="P16" s="1" t="n">
         <s:v>66</s:v>
       </s:c>
@@ -4694,16 +4994,36 @@
       <s:c r="E17" s="1" t="n">
         <s:v>395.45</s:v>
       </s:c>
-      <s:c r="F17" s="1"/>
-      <s:c r="G17" s="1"/>
-      <s:c r="H17" s="1"/>
-      <s:c r="I17" s="1"/>
-      <s:c r="J17" s="1"/>
-      <s:c r="K17" s="1"/>
-      <s:c r="L17" s="1"/>
-      <s:c r="M17" s="1"/>
-      <s:c r="N17" s="1"/>
-      <s:c r="O17" s="1"/>
+      <s:c r="F17" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="G17" s="1" t="n">
+        <s:v>2356.08</s:v>
+      </s:c>
+      <s:c r="H17" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="I17" s="1" t="n">
+        <s:v>3.7</s:v>
+      </s:c>
+      <s:c r="J17" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="K17" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="L17" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="M17" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="N17" s="1" t="n">
+        <s:v>17053.9</s:v>
+      </s:c>
+      <s:c r="O17" s="1" t="n">
+        <s:v>407.13</s:v>
+      </s:c>
       <s:c r="P17" s="1" t="n">
         <s:v>66</s:v>
       </s:c>
@@ -4724,16 +5044,36 @@
       <s:c r="E18" s="1" t="n">
         <s:v>395.7</s:v>
       </s:c>
-      <s:c r="F18" s="1"/>
-      <s:c r="G18" s="1"/>
-      <s:c r="H18" s="1"/>
-      <s:c r="I18" s="1"/>
-      <s:c r="J18" s="1"/>
-      <s:c r="K18" s="1"/>
-      <s:c r="L18" s="1"/>
-      <s:c r="M18" s="1"/>
-      <s:c r="N18" s="1"/>
-      <s:c r="O18" s="1"/>
+      <s:c r="F18" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="G18" s="1" t="n">
+        <s:v>2358.55</s:v>
+      </s:c>
+      <s:c r="H18" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="I18" s="1" t="n">
+        <s:v>3.7</s:v>
+      </s:c>
+      <s:c r="J18" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="K18" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="L18" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="M18" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="N18" s="1" t="n">
+        <s:v>17040</s:v>
+      </s:c>
+      <s:c r="O18" s="1" t="n">
+        <s:v>420.65</s:v>
+      </s:c>
       <s:c r="P18" s="1" t="n">
         <s:v>66</s:v>
       </s:c>
@@ -4754,16 +5094,36 @@
       <s:c r="E19" s="1" t="n">
         <s:v>394.6</s:v>
       </s:c>
-      <s:c r="F19" s="1"/>
-      <s:c r="G19" s="1"/>
-      <s:c r="H19" s="1"/>
-      <s:c r="I19" s="1"/>
-      <s:c r="J19" s="1"/>
-      <s:c r="K19" s="1"/>
-      <s:c r="L19" s="1"/>
-      <s:c r="M19" s="1"/>
-      <s:c r="N19" s="1"/>
-      <s:c r="O19" s="1"/>
+      <s:c r="F19" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="G19" s="1" t="n">
+        <s:v>2393.06</s:v>
+      </s:c>
+      <s:c r="H19" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="I19" s="1" t="n">
+        <s:v>3.7</s:v>
+      </s:c>
+      <s:c r="J19" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="K19" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="L19" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="M19" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="N19" s="1" t="n">
+        <s:v>16873.22</s:v>
+      </s:c>
+      <s:c r="O19" s="1" t="n">
+        <s:v>385.62</s:v>
+      </s:c>
       <s:c r="P19" s="1" t="n">
         <s:v>66</s:v>
       </s:c>
@@ -4784,16 +5144,36 @@
       <s:c r="E20" s="1" t="n">
         <s:v>394.61</s:v>
       </s:c>
-      <s:c r="F20" s="1"/>
-      <s:c r="G20" s="1"/>
-      <s:c r="H20" s="1"/>
-      <s:c r="I20" s="1"/>
-      <s:c r="J20" s="1"/>
-      <s:c r="K20" s="1"/>
-      <s:c r="L20" s="1"/>
-      <s:c r="M20" s="1"/>
-      <s:c r="N20" s="1"/>
-      <s:c r="O20" s="1"/>
+      <s:c r="F20" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="G20" s="1" t="n">
+        <s:v>2392.07</s:v>
+      </s:c>
+      <s:c r="H20" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="I20" s="1" t="n">
+        <s:v>3.7</s:v>
+      </s:c>
+      <s:c r="J20" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="K20" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="L20" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="M20" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="N20" s="1" t="n">
+        <s:v>16926.07</s:v>
+      </s:c>
+      <s:c r="O20" s="1" t="n">
+        <s:v>400.96</s:v>
+      </s:c>
       <s:c r="P20" s="1" t="n">
         <s:v>66</s:v>
       </s:c>
@@ -4814,16 +5194,36 @@
       <s:c r="E21" s="1" t="n">
         <s:v>395.45</s:v>
       </s:c>
-      <s:c r="F21" s="1"/>
-      <s:c r="G21" s="1"/>
-      <s:c r="H21" s="1"/>
-      <s:c r="I21" s="1"/>
-      <s:c r="J21" s="1"/>
-      <s:c r="K21" s="1"/>
-      <s:c r="L21" s="1"/>
-      <s:c r="M21" s="1"/>
-      <s:c r="N21" s="1"/>
-      <s:c r="O21" s="1"/>
+      <s:c r="F21" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="G21" s="1" t="n">
+        <s:v>2377.27</s:v>
+      </s:c>
+      <s:c r="H21" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="I21" s="1" t="n">
+        <s:v>3.7</s:v>
+      </s:c>
+      <s:c r="J21" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="K21" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="L21" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="M21" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="N21" s="1" t="n">
+        <s:v>16999.46</s:v>
+      </s:c>
+      <s:c r="O21" s="1" t="n">
+        <s:v>443.76</s:v>
+      </s:c>
       <s:c r="P21" s="1" t="n">
         <s:v>66</s:v>
       </s:c>
@@ -4844,16 +5244,36 @@
       <s:c r="E22" s="1" t="n">
         <s:v>395.85</s:v>
       </s:c>
-      <s:c r="F22" s="1"/>
-      <s:c r="G22" s="1"/>
-      <s:c r="H22" s="1"/>
-      <s:c r="I22" s="1"/>
-      <s:c r="J22" s="1"/>
-      <s:c r="K22" s="1"/>
-      <s:c r="L22" s="1"/>
-      <s:c r="M22" s="1"/>
-      <s:c r="N22" s="1"/>
-      <s:c r="O22" s="1"/>
+      <s:c r="F22" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="G22" s="1" t="n">
+        <s:v>2385.81</s:v>
+      </s:c>
+      <s:c r="H22" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="I22" s="1" t="n">
+        <s:v>3.7</s:v>
+      </s:c>
+      <s:c r="J22" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="K22" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="L22" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="M22" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="N22" s="1" t="n">
+        <s:v>17127.12</s:v>
+      </s:c>
+      <s:c r="O22" s="1" t="n">
+        <s:v>452.07</s:v>
+      </s:c>
       <s:c r="P22" s="1" t="n">
         <s:v>66</s:v>
       </s:c>
@@ -4874,16 +5294,36 @@
       <s:c r="E23" s="1" t="n">
         <s:v>403</s:v>
       </s:c>
-      <s:c r="F23" s="1"/>
-      <s:c r="G23" s="1"/>
-      <s:c r="H23" s="1"/>
-      <s:c r="I23" s="1"/>
-      <s:c r="J23" s="1"/>
-      <s:c r="K23" s="1"/>
-      <s:c r="L23" s="1"/>
-      <s:c r="M23" s="1"/>
-      <s:c r="N23" s="1"/>
-      <s:c r="O23" s="1"/>
+      <s:c r="F23" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="G23" s="1" t="n">
+        <s:v>2379.22</s:v>
+      </s:c>
+      <s:c r="H23" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="I23" s="1" t="n">
+        <s:v>3.73</s:v>
+      </s:c>
+      <s:c r="J23" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="K23" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="L23" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="M23" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="N23" s="1" t="n">
+        <s:v>17296.13</s:v>
+      </s:c>
+      <s:c r="O23" s="1" t="n">
+        <s:v>459.02</s:v>
+      </s:c>
       <s:c r="P23" s="1" t="n">
         <s:v>66</s:v>
       </s:c>
@@ -4904,16 +5344,36 @@
       <s:c r="E24" s="1" t="n">
         <s:v>404.32</s:v>
       </s:c>
-      <s:c r="F24" s="1"/>
-      <s:c r="G24" s="1"/>
-      <s:c r="H24" s="1"/>
-      <s:c r="I24" s="1"/>
-      <s:c r="J24" s="1"/>
-      <s:c r="K24" s="1"/>
-      <s:c r="L24" s="1"/>
-      <s:c r="M24" s="1"/>
-      <s:c r="N24" s="1"/>
-      <s:c r="O24" s="1"/>
+      <s:c r="F24" s="1" t="n">
+        <s:v>100</s:v>
+      </s:c>
+      <s:c r="G24" s="1" t="n">
+        <s:v>2383.38</s:v>
+      </s:c>
+      <s:c r="H24" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="I24" s="1" t="n">
+        <s:v>42</s:v>
+      </s:c>
+      <s:c r="J24" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="K24" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="L24" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="M24" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="N24" s="1" t="n">
+        <s:v>17492.57</s:v>
+      </s:c>
+      <s:c r="O24" s="1" t="n">
+        <s:v>417.25</s:v>
+      </s:c>
       <s:c r="P24" s="1" t="n">
         <s:v>66</s:v>
       </s:c>
@@ -4934,16 +5394,36 @@
       <s:c r="E25" s="1" t="n">
         <s:v>416.55</s:v>
       </s:c>
-      <s:c r="F25" s="1"/>
-      <s:c r="G25" s="1"/>
-      <s:c r="H25" s="1"/>
-      <s:c r="I25" s="1"/>
-      <s:c r="J25" s="1"/>
-      <s:c r="K25" s="1"/>
-      <s:c r="L25" s="1"/>
-      <s:c r="M25" s="1"/>
-      <s:c r="N25" s="1"/>
-      <s:c r="O25" s="1"/>
+      <s:c r="F25" s="1" t="n">
+        <s:v>130</s:v>
+      </s:c>
+      <s:c r="G25" s="1" t="n">
+        <s:v>2365.26</s:v>
+      </s:c>
+      <s:c r="H25" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="I25" s="1" t="n">
+        <s:v>139.05</s:v>
+      </s:c>
+      <s:c r="J25" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="K25" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="L25" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="M25" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="N25" s="1" t="n">
+        <s:v>17990</s:v>
+      </s:c>
+      <s:c r="O25" s="1" t="n">
+        <s:v>400</s:v>
+      </s:c>
       <s:c r="P25" s="1" t="n">
         <s:v>66</s:v>
       </s:c>
@@ -4964,16 +5444,36 @@
       <s:c r="E26" s="1" t="n">
         <s:v>423.39</s:v>
       </s:c>
-      <s:c r="F26" s="1"/>
-      <s:c r="G26" s="1"/>
-      <s:c r="H26" s="1"/>
-      <s:c r="I26" s="1"/>
-      <s:c r="J26" s="1"/>
-      <s:c r="K26" s="1"/>
-      <s:c r="L26" s="1"/>
-      <s:c r="M26" s="1"/>
-      <s:c r="N26" s="1"/>
-      <s:c r="O26" s="1"/>
+      <s:c r="F26" s="1" t="n">
+        <s:v>570</s:v>
+      </s:c>
+      <s:c r="G26" s="1" t="n">
+        <s:v>2373.38</s:v>
+      </s:c>
+      <s:c r="H26" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="I26" s="1" t="n">
+        <s:v>290.87</s:v>
+      </s:c>
+      <s:c r="J26" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="K26" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="L26" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="M26" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="N26" s="1" t="n">
+        <s:v>18259.25</s:v>
+      </s:c>
+      <s:c r="O26" s="1" t="n">
+        <s:v>387.51</s:v>
+      </s:c>
       <s:c r="P26" s="1" t="n">
         <s:v>66</s:v>
       </s:c>
@@ -4994,16 +5494,36 @@
       <s:c r="E27" s="1" t="n">
         <s:v>440.54</s:v>
       </s:c>
-      <s:c r="F27" s="1"/>
-      <s:c r="G27" s="1"/>
-      <s:c r="H27" s="1"/>
-      <s:c r="I27" s="1"/>
-      <s:c r="J27" s="1"/>
-      <s:c r="K27" s="1"/>
-      <s:c r="L27" s="1"/>
-      <s:c r="M27" s="1"/>
-      <s:c r="N27" s="1"/>
-      <s:c r="O27" s="1"/>
+      <s:c r="F27" s="1" t="n">
+        <s:v>630</s:v>
+      </s:c>
+      <s:c r="G27" s="1" t="n">
+        <s:v>2379.71</s:v>
+      </s:c>
+      <s:c r="H27" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="I27" s="1" t="n">
+        <s:v>577.93</s:v>
+      </s:c>
+      <s:c r="J27" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="K27" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="L27" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="M27" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="N27" s="1" t="n">
+        <s:v>18978.79</s:v>
+      </s:c>
+      <s:c r="O27" s="1" t="n">
+        <s:v>400.68</s:v>
+      </s:c>
       <s:c r="P27" s="1" t="n">
         <s:v>66</s:v>
       </s:c>
@@ -5024,16 +5544,36 @@
       <s:c r="E28" s="1" t="n">
         <s:v>453.6</s:v>
       </s:c>
-      <s:c r="F28" s="1"/>
-      <s:c r="G28" s="1"/>
-      <s:c r="H28" s="1"/>
-      <s:c r="I28" s="1"/>
-      <s:c r="J28" s="1"/>
-      <s:c r="K28" s="1"/>
-      <s:c r="L28" s="1"/>
-      <s:c r="M28" s="1"/>
-      <s:c r="N28" s="1"/>
-      <s:c r="O28" s="1"/>
+      <s:c r="F28" s="1" t="n">
+        <s:v>540</s:v>
+      </s:c>
+      <s:c r="G28" s="1" t="n">
+        <s:v>2367.53</s:v>
+      </s:c>
+      <s:c r="H28" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="I28" s="1" t="n">
+        <s:v>889.03</s:v>
+      </s:c>
+      <s:c r="J28" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="K28" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="L28" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="M28" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="N28" s="1" t="n">
+        <s:v>18921.34</s:v>
+      </s:c>
+      <s:c r="O28" s="1" t="n">
+        <s:v>410.9</s:v>
+      </s:c>
       <s:c r="P28" s="1" t="n">
         <s:v>66</s:v>
       </s:c>
@@ -5054,16 +5594,36 @@
       <s:c r="E29" s="1" t="n">
         <s:v>360</s:v>
       </s:c>
-      <s:c r="F29" s="1"/>
-      <s:c r="G29" s="1"/>
-      <s:c r="H29" s="1"/>
-      <s:c r="I29" s="1"/>
-      <s:c r="J29" s="1"/>
-      <s:c r="K29" s="1"/>
-      <s:c r="L29" s="1"/>
-      <s:c r="M29" s="1"/>
-      <s:c r="N29" s="1"/>
-      <s:c r="O29" s="1"/>
+      <s:c r="F29" s="1" t="n">
+        <s:v>330</s:v>
+      </s:c>
+      <s:c r="G29" s="1" t="n">
+        <s:v>2403.8</s:v>
+      </s:c>
+      <s:c r="H29" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="I29" s="1" t="n">
+        <s:v>1259.95</s:v>
+      </s:c>
+      <s:c r="J29" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="K29" s="1" t="n">
+        <s:v>150.9</s:v>
+      </s:c>
+      <s:c r="L29" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="M29" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="N29" s="1" t="n">
+        <s:v>18181.72</s:v>
+      </s:c>
+      <s:c r="O29" s="1" t="n">
+        <s:v>409.83</s:v>
+      </s:c>
       <s:c r="P29" s="1" t="n">
         <s:v>66</s:v>
       </s:c>
@@ -5084,16 +5644,36 @@
       <s:c r="E30" s="1" t="n">
         <s:v>431.69</s:v>
       </s:c>
-      <s:c r="F30" s="1"/>
-      <s:c r="G30" s="1"/>
-      <s:c r="H30" s="1"/>
-      <s:c r="I30" s="1"/>
-      <s:c r="J30" s="1"/>
-      <s:c r="K30" s="1"/>
-      <s:c r="L30" s="1"/>
-      <s:c r="M30" s="1"/>
-      <s:c r="N30" s="1"/>
-      <s:c r="O30" s="1"/>
+      <s:c r="F30" s="1" t="n">
+        <s:v>70</s:v>
+      </s:c>
+      <s:c r="G30" s="1" t="n">
+        <s:v>2414.45</s:v>
+      </s:c>
+      <s:c r="H30" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="I30" s="1" t="n">
+        <s:v>1633.95</s:v>
+      </s:c>
+      <s:c r="J30" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="K30" s="1" t="n">
+        <s:v>151.1</s:v>
+      </s:c>
+      <s:c r="L30" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="M30" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="N30" s="1" t="n">
+        <s:v>18386.03</s:v>
+      </s:c>
+      <s:c r="O30" s="1" t="n">
+        <s:v>372.58</s:v>
+      </s:c>
       <s:c r="P30" s="1" t="n">
         <s:v>66</s:v>
       </s:c>
@@ -5114,16 +5694,36 @@
       <s:c r="E31" s="1" t="n">
         <s:v>428.2</s:v>
       </s:c>
-      <s:c r="F31" s="1"/>
-      <s:c r="G31" s="1"/>
-      <s:c r="H31" s="1"/>
-      <s:c r="I31" s="1"/>
-      <s:c r="J31" s="1"/>
-      <s:c r="K31" s="1"/>
-      <s:c r="L31" s="1"/>
-      <s:c r="M31" s="1"/>
-      <s:c r="N31" s="1"/>
-      <s:c r="O31" s="1"/>
+      <s:c r="F31" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="G31" s="1" t="n">
+        <s:v>2453.35</s:v>
+      </s:c>
+      <s:c r="H31" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="I31" s="1" t="n">
+        <s:v>2189.83</s:v>
+      </s:c>
+      <s:c r="J31" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="K31" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="L31" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="M31" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="N31" s="1" t="n">
+        <s:v>17910.92</s:v>
+      </s:c>
+      <s:c r="O31" s="1" t="n">
+        <s:v>330.2</s:v>
+      </s:c>
       <s:c r="P31" s="1" t="n">
         <s:v>66</s:v>
       </s:c>
@@ -5144,16 +5744,36 @@
       <s:c r="E32" s="1" t="n">
         <s:v>404.58</s:v>
       </s:c>
-      <s:c r="F32" s="1"/>
-      <s:c r="G32" s="1"/>
-      <s:c r="H32" s="1"/>
-      <s:c r="I32" s="1"/>
-      <s:c r="J32" s="1"/>
-      <s:c r="K32" s="1"/>
-      <s:c r="L32" s="1"/>
-      <s:c r="M32" s="1"/>
-      <s:c r="N32" s="1"/>
-      <s:c r="O32" s="1"/>
+      <s:c r="F32" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="G32" s="1" t="n">
+        <s:v>2467.07</s:v>
+      </s:c>
+      <s:c r="H32" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="I32" s="1" t="n">
+        <s:v>2676.07</s:v>
+      </s:c>
+      <s:c r="J32" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="K32" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="L32" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="M32" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="N32" s="1" t="n">
+        <s:v>16900.62</s:v>
+      </s:c>
+      <s:c r="O32" s="1" t="n">
+        <s:v>312.44</s:v>
+      </s:c>
       <s:c r="P32" s="1" t="n">
         <s:v>66</s:v>
       </s:c>
@@ -5174,16 +5794,36 @@
       <s:c r="E33" s="1" t="n">
         <s:v>394.75</s:v>
       </s:c>
-      <s:c r="F33" s="1"/>
-      <s:c r="G33" s="1"/>
-      <s:c r="H33" s="1"/>
-      <s:c r="I33" s="1"/>
-      <s:c r="J33" s="1"/>
-      <s:c r="K33" s="1"/>
-      <s:c r="L33" s="1"/>
-      <s:c r="M33" s="1"/>
-      <s:c r="N33" s="1"/>
-      <s:c r="O33" s="1"/>
+      <s:c r="F33" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="G33" s="1" t="n">
+        <s:v>2537.84</s:v>
+      </s:c>
+      <s:c r="H33" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="I33" s="1" t="n">
+        <s:v>3130.42</s:v>
+      </s:c>
+      <s:c r="J33" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="K33" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="L33" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="M33" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="N33" s="1" t="n">
+        <s:v>15855.94</s:v>
+      </s:c>
+      <s:c r="O33" s="1" t="n">
+        <s:v>295.9</s:v>
+      </s:c>
       <s:c r="P33" s="1" t="n">
         <s:v>66</s:v>
       </s:c>
@@ -5204,16 +5844,36 @@
       <s:c r="E34" s="1" t="n">
         <s:v>404.42</s:v>
       </s:c>
-      <s:c r="F34" s="1"/>
-      <s:c r="G34" s="1"/>
-      <s:c r="H34" s="1"/>
-      <s:c r="I34" s="1"/>
-      <s:c r="J34" s="1"/>
-      <s:c r="K34" s="1"/>
-      <s:c r="L34" s="1"/>
-      <s:c r="M34" s="1"/>
-      <s:c r="N34" s="1"/>
-      <s:c r="O34" s="1"/>
+      <s:c r="F34" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="G34" s="1" t="n">
+        <s:v>2582.29</s:v>
+      </s:c>
+      <s:c r="H34" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="I34" s="1" t="n">
+        <s:v>3611.5</s:v>
+      </s:c>
+      <s:c r="J34" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="K34" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="L34" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="M34" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="N34" s="1" t="n">
+        <s:v>15884.8</s:v>
+      </s:c>
+      <s:c r="O34" s="1" t="n">
+        <s:v>263.31</s:v>
+      </s:c>
       <s:c r="P34" s="1" t="n">
         <s:v>66</s:v>
       </s:c>
@@ -5234,16 +5894,36 @@
       <s:c r="E35" s="1" t="n">
         <s:v>404.95</s:v>
       </s:c>
-      <s:c r="F35" s="1"/>
-      <s:c r="G35" s="1"/>
-      <s:c r="H35" s="1"/>
-      <s:c r="I35" s="1"/>
-      <s:c r="J35" s="1"/>
-      <s:c r="K35" s="1"/>
-      <s:c r="L35" s="1"/>
-      <s:c r="M35" s="1"/>
-      <s:c r="N35" s="1"/>
-      <s:c r="O35" s="1"/>
+      <s:c r="F35" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="G35" s="1" t="n">
+        <s:v>2593.45</s:v>
+      </s:c>
+      <s:c r="H35" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="I35" s="1" t="n">
+        <s:v>4017.15</s:v>
+      </s:c>
+      <s:c r="J35" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="K35" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="L35" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="M35" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="N35" s="1" t="n">
+        <s:v>15201.67</s:v>
+      </s:c>
+      <s:c r="O35" s="1" t="n">
+        <s:v>227.43</s:v>
+      </s:c>
       <s:c r="P35" s="1" t="n">
         <s:v>66</s:v>
       </s:c>
@@ -5264,16 +5944,36 @@
       <s:c r="E36" s="1" t="n">
         <s:v>431.76</s:v>
       </s:c>
-      <s:c r="F36" s="1"/>
-      <s:c r="G36" s="1"/>
-      <s:c r="H36" s="1"/>
-      <s:c r="I36" s="1"/>
-      <s:c r="J36" s="1"/>
-      <s:c r="K36" s="1"/>
-      <s:c r="L36" s="1"/>
-      <s:c r="M36" s="1"/>
-      <s:c r="N36" s="1"/>
-      <s:c r="O36" s="1"/>
+      <s:c r="F36" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="G36" s="1" t="n">
+        <s:v>2633.98</s:v>
+      </s:c>
+      <s:c r="H36" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="I36" s="1" t="n">
+        <s:v>4496.22</s:v>
+      </s:c>
+      <s:c r="J36" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="K36" s="1" t="n">
+        <s:v>-3.3</s:v>
+      </s:c>
+      <s:c r="L36" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="M36" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="N36" s="1" t="n">
+        <s:v>14250.37</s:v>
+      </s:c>
+      <s:c r="O36" s="1" t="n">
+        <s:v>210.42</s:v>
+      </s:c>
       <s:c r="P36" s="1" t="n">
         <s:v>66</s:v>
       </s:c>
@@ -5294,16 +5994,36 @@
       <s:c r="E37" s="1" t="n">
         <s:v>381.54</s:v>
       </s:c>
-      <s:c r="F37" s="1"/>
-      <s:c r="G37" s="1"/>
-      <s:c r="H37" s="1"/>
-      <s:c r="I37" s="1"/>
-      <s:c r="J37" s="1"/>
-      <s:c r="K37" s="1"/>
-      <s:c r="L37" s="1"/>
-      <s:c r="M37" s="1"/>
-      <s:c r="N37" s="1"/>
-      <s:c r="O37" s="1"/>
+      <s:c r="F37" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="G37" s="1" t="n">
+        <s:v>2665.43</s:v>
+      </s:c>
+      <s:c r="H37" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="I37" s="1" t="n">
+        <s:v>5187.09</s:v>
+      </s:c>
+      <s:c r="J37" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="K37" s="1" t="n">
+        <s:v>-6.6</s:v>
+      </s:c>
+      <s:c r="L37" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="M37" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="N37" s="1" t="n">
+        <s:v>12493.81</s:v>
+      </s:c>
+      <s:c r="O37" s="1" t="n">
+        <s:v>224.47</s:v>
+      </s:c>
       <s:c r="P37" s="1" t="n">
         <s:v>66</s:v>
       </s:c>
@@ -5324,16 +6044,36 @@
       <s:c r="E38" s="1" t="n">
         <s:v>372.17</s:v>
       </s:c>
-      <s:c r="F38" s="1"/>
-      <s:c r="G38" s="1"/>
-      <s:c r="H38" s="1"/>
-      <s:c r="I38" s="1"/>
-      <s:c r="J38" s="1"/>
-      <s:c r="K38" s="1"/>
-      <s:c r="L38" s="1"/>
-      <s:c r="M38" s="1"/>
-      <s:c r="N38" s="1"/>
-      <s:c r="O38" s="1"/>
+      <s:c r="F38" s="1" t="n">
+        <s:v>-300</s:v>
+      </s:c>
+      <s:c r="G38" s="1" t="n">
+        <s:v>2730</s:v>
+      </s:c>
+      <s:c r="H38" s="1" t="n">
+        <s:v>1</s:v>
+      </s:c>
+      <s:c r="I38" s="1" t="n">
+        <s:v>5790.02</s:v>
+      </s:c>
+      <s:c r="J38" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="K38" s="1" t="n">
+        <s:v>-258.5</s:v>
+      </s:c>
+      <s:c r="L38" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="M38" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="N38" s="1" t="n">
+        <s:v>11402.08</s:v>
+      </s:c>
+      <s:c r="O38" s="1" t="n">
+        <s:v>246.9</s:v>
+      </s:c>
       <s:c r="P38" s="1" t="n">
         <s:v>66</s:v>
       </s:c>
@@ -5354,16 +6094,36 @@
       <s:c r="E39" s="1" t="n">
         <s:v>429.45</s:v>
       </s:c>
-      <s:c r="F39" s="1"/>
-      <s:c r="G39" s="1"/>
-      <s:c r="H39" s="1"/>
-      <s:c r="I39" s="1"/>
-      <s:c r="J39" s="1"/>
-      <s:c r="K39" s="1"/>
-      <s:c r="L39" s="1"/>
-      <s:c r="M39" s="1"/>
-      <s:c r="N39" s="1"/>
-      <s:c r="O39" s="1"/>
+      <s:c r="F39" s="1" t="n">
+        <s:v>-840</s:v>
+      </s:c>
+      <s:c r="G39" s="1" t="n">
+        <s:v>2768.53</s:v>
+      </s:c>
+      <s:c r="H39" s="1" t="n">
+        <s:v>1</s:v>
+      </s:c>
+      <s:c r="I39" s="1" t="n">
+        <s:v>6323.04</s:v>
+      </s:c>
+      <s:c r="J39" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="K39" s="1" t="n">
+        <s:v>-260.2</s:v>
+      </s:c>
+      <s:c r="L39" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="M39" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="N39" s="1" t="n">
+        <s:v>11305.22</s:v>
+      </s:c>
+      <s:c r="O39" s="1" t="n">
+        <s:v>242.39</s:v>
+      </s:c>
       <s:c r="P39" s="1" t="n">
         <s:v>64</s:v>
       </s:c>
@@ -5384,16 +6144,36 @@
       <s:c r="E40" s="1" t="n">
         <s:v>381.73</s:v>
       </s:c>
-      <s:c r="F40" s="1"/>
-      <s:c r="G40" s="1"/>
-      <s:c r="H40" s="1"/>
-      <s:c r="I40" s="1"/>
-      <s:c r="J40" s="1"/>
-      <s:c r="K40" s="1"/>
-      <s:c r="L40" s="1"/>
-      <s:c r="M40" s="1"/>
-      <s:c r="N40" s="1"/>
-      <s:c r="O40" s="1"/>
+      <s:c r="F40" s="1" t="n">
+        <s:v>-1363</s:v>
+      </s:c>
+      <s:c r="G40" s="1" t="n">
+        <s:v>2829.6</s:v>
+      </s:c>
+      <s:c r="H40" s="1" t="n">
+        <s:v>1</s:v>
+      </s:c>
+      <s:c r="I40" s="1" t="n">
+        <s:v>6909.32</s:v>
+      </s:c>
+      <s:c r="J40" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="K40" s="1" t="n">
+        <s:v>-511</s:v>
+      </s:c>
+      <s:c r="L40" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="M40" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="N40" s="1" t="n">
+        <s:v>10356.39</s:v>
+      </s:c>
+      <s:c r="O40" s="1" t="n">
+        <s:v>243.87</s:v>
+      </s:c>
       <s:c r="P40" s="1" t="n">
         <s:v>64</s:v>
       </s:c>
@@ -5414,16 +6194,36 @@
       <s:c r="E41" s="1" t="n">
         <s:v>369.73</s:v>
       </s:c>
-      <s:c r="F41" s="1"/>
-      <s:c r="G41" s="1"/>
-      <s:c r="H41" s="1"/>
-      <s:c r="I41" s="1"/>
-      <s:c r="J41" s="1"/>
-      <s:c r="K41" s="1"/>
-      <s:c r="L41" s="1"/>
-      <s:c r="M41" s="1"/>
-      <s:c r="N41" s="1"/>
-      <s:c r="O41" s="1"/>
+      <s:c r="F41" s="1" t="n">
+        <s:v>-1568</s:v>
+      </s:c>
+      <s:c r="G41" s="1" t="n">
+        <s:v>2818.59</s:v>
+      </s:c>
+      <s:c r="H41" s="1" t="n">
+        <s:v>1</s:v>
+      </s:c>
+      <s:c r="I41" s="1" t="n">
+        <s:v>7472.56</s:v>
+      </s:c>
+      <s:c r="J41" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="K41" s="1" t="n">
+        <s:v>-508.9</s:v>
+      </s:c>
+      <s:c r="L41" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="M41" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="N41" s="1" t="n">
+        <s:v>9659.1</s:v>
+      </s:c>
+      <s:c r="O41" s="1" t="n">
+        <s:v>209.55</s:v>
+      </s:c>
       <s:c r="P41" s="1" t="n">
         <s:v>64</s:v>
       </s:c>
@@ -5444,16 +6244,36 @@
       <s:c r="E42" s="1" t="n">
         <s:v>395.79</s:v>
       </s:c>
-      <s:c r="F42" s="1"/>
-      <s:c r="G42" s="1"/>
-      <s:c r="H42" s="1"/>
-      <s:c r="I42" s="1"/>
-      <s:c r="J42" s="1"/>
-      <s:c r="K42" s="1"/>
-      <s:c r="L42" s="1"/>
-      <s:c r="M42" s="1"/>
-      <s:c r="N42" s="1"/>
-      <s:c r="O42" s="1"/>
+      <s:c r="F42" s="1" t="n">
+        <s:v>-2773</s:v>
+      </s:c>
+      <s:c r="G42" s="1" t="n">
+        <s:v>2899.08</s:v>
+      </s:c>
+      <s:c r="H42" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="I42" s="1" t="n">
+        <s:v>7969.69</s:v>
+      </s:c>
+      <s:c r="J42" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="K42" s="1" t="n">
+        <s:v>-509.2</s:v>
+      </s:c>
+      <s:c r="L42" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="M42" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="N42" s="1" t="n">
+        <s:v>10399.05</s:v>
+      </s:c>
+      <s:c r="O42" s="1" t="n">
+        <s:v>198.08</s:v>
+      </s:c>
       <s:c r="P42" s="1" t="n">
         <s:v>64</s:v>
       </s:c>
@@ -5474,16 +6294,36 @@
       <s:c r="E43" s="1" t="n">
         <s:v>383.52</s:v>
       </s:c>
-      <s:c r="F43" s="1"/>
-      <s:c r="G43" s="1"/>
-      <s:c r="H43" s="1"/>
-      <s:c r="I43" s="1"/>
-      <s:c r="J43" s="1"/>
-      <s:c r="K43" s="1"/>
-      <s:c r="L43" s="1"/>
-      <s:c r="M43" s="1"/>
-      <s:c r="N43" s="1"/>
-      <s:c r="O43" s="1"/>
+      <s:c r="F43" s="1" t="n">
+        <s:v>-3233</s:v>
+      </s:c>
+      <s:c r="G43" s="1" t="n">
+        <s:v>2950.79</s:v>
+      </s:c>
+      <s:c r="H43" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="I43" s="1" t="n">
+        <s:v>8409.68</s:v>
+      </s:c>
+      <s:c r="J43" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="K43" s="1" t="n">
+        <s:v>-513.3</s:v>
+      </s:c>
+      <s:c r="L43" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="M43" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="N43" s="1" t="n">
+        <s:v>9883.95</s:v>
+      </s:c>
+      <s:c r="O43" s="1" t="n">
+        <s:v>186.68</s:v>
+      </s:c>
       <s:c r="P43" s="1" t="n">
         <s:v>64</s:v>
       </s:c>
@@ -5504,16 +6344,36 @@
       <s:c r="E44" s="1" t="n">
         <s:v>380.98</s:v>
       </s:c>
-      <s:c r="F44" s="1"/>
-      <s:c r="G44" s="1"/>
-      <s:c r="H44" s="1"/>
-      <s:c r="I44" s="1"/>
-      <s:c r="J44" s="1"/>
-      <s:c r="K44" s="1"/>
-      <s:c r="L44" s="1"/>
-      <s:c r="M44" s="1"/>
-      <s:c r="N44" s="1"/>
-      <s:c r="O44" s="1"/>
+      <s:c r="F44" s="1" t="n">
+        <s:v>-3483</s:v>
+      </s:c>
+      <s:c r="G44" s="1" t="n">
+        <s:v>2964.38</s:v>
+      </s:c>
+      <s:c r="H44" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="I44" s="1" t="n">
+        <s:v>8705.24</s:v>
+      </s:c>
+      <s:c r="J44" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="K44" s="1" t="n">
+        <s:v>-512.2</s:v>
+      </s:c>
+      <s:c r="L44" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="M44" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="N44" s="1" t="n">
+        <s:v>9600.61</s:v>
+      </s:c>
+      <s:c r="O44" s="1" t="n">
+        <s:v>194.28</s:v>
+      </s:c>
       <s:c r="P44" s="1" t="n">
         <s:v>62</s:v>
       </s:c>
@@ -5534,16 +6394,36 @@
       <s:c r="E45" s="1" t="n">
         <s:v>393.23</s:v>
       </s:c>
-      <s:c r="F45" s="1"/>
-      <s:c r="G45" s="1"/>
-      <s:c r="H45" s="1"/>
-      <s:c r="I45" s="1"/>
-      <s:c r="J45" s="1"/>
-      <s:c r="K45" s="1"/>
-      <s:c r="L45" s="1"/>
-      <s:c r="M45" s="1"/>
-      <s:c r="N45" s="1"/>
-      <s:c r="O45" s="1"/>
+      <s:c r="F45" s="1" t="n">
+        <s:v>-3493</s:v>
+      </s:c>
+      <s:c r="G45" s="1" t="n">
+        <s:v>2945.22</s:v>
+      </s:c>
+      <s:c r="H45" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="I45" s="1" t="n">
+        <s:v>8997.76</s:v>
+      </s:c>
+      <s:c r="J45" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="K45" s="1" t="n">
+        <s:v>-807.6</s:v>
+      </s:c>
+      <s:c r="L45" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="M45" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="N45" s="1" t="n">
+        <s:v>9628.72</s:v>
+      </s:c>
+      <s:c r="O45" s="1" t="n">
+        <s:v>183.89</s:v>
+      </s:c>
       <s:c r="P45" s="1" t="n">
         <s:v>62</s:v>
       </s:c>
@@ -5564,16 +6444,36 @@
       <s:c r="E46" s="1" t="n">
         <s:v>430</s:v>
       </s:c>
-      <s:c r="F46" s="1"/>
-      <s:c r="G46" s="1"/>
-      <s:c r="H46" s="1"/>
-      <s:c r="I46" s="1"/>
-      <s:c r="J46" s="1"/>
-      <s:c r="K46" s="1"/>
-      <s:c r="L46" s="1"/>
-      <s:c r="M46" s="1"/>
-      <s:c r="N46" s="1"/>
-      <s:c r="O46" s="1"/>
+      <s:c r="F46" s="1" t="n">
+        <s:v>-3563</s:v>
+      </s:c>
+      <s:c r="G46" s="1" t="n">
+        <s:v>2895.92</s:v>
+      </s:c>
+      <s:c r="H46" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="I46" s="1" t="n">
+        <s:v>9258.08</s:v>
+      </s:c>
+      <s:c r="J46" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="K46" s="1" t="n">
+        <s:v>-806.3</s:v>
+      </s:c>
+      <s:c r="L46" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="M46" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="N46" s="1" t="n">
+        <s:v>9921.75</s:v>
+      </s:c>
+      <s:c r="O46" s="1" t="n">
+        <s:v>190.65</s:v>
+      </s:c>
       <s:c r="P46" s="1" t="n">
         <s:v>62</s:v>
       </s:c>
@@ -5594,16 +6494,36 @@
       <s:c r="E47" s="1" t="n">
         <s:v>430</s:v>
       </s:c>
-      <s:c r="F47" s="1"/>
-      <s:c r="G47" s="1"/>
-      <s:c r="H47" s="1"/>
-      <s:c r="I47" s="1"/>
-      <s:c r="J47" s="1"/>
-      <s:c r="K47" s="1"/>
-      <s:c r="L47" s="1"/>
-      <s:c r="M47" s="1"/>
-      <s:c r="N47" s="1"/>
-      <s:c r="O47" s="1"/>
+      <s:c r="F47" s="1" t="n">
+        <s:v>-3658</s:v>
+      </s:c>
+      <s:c r="G47" s="1" t="n">
+        <s:v>2930.96</s:v>
+      </s:c>
+      <s:c r="H47" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="I47" s="1" t="n">
+        <s:v>9183.39</s:v>
+      </s:c>
+      <s:c r="J47" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="K47" s="1" t="n">
+        <s:v>-810.8</s:v>
+      </s:c>
+      <s:c r="L47" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="M47" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="N47" s="1" t="n">
+        <s:v>10451.44</s:v>
+      </s:c>
+      <s:c r="O47" s="1" t="n">
+        <s:v>212.04</s:v>
+      </s:c>
       <s:c r="P47" s="1" t="n">
         <s:v>62</s:v>
       </s:c>
@@ -5624,16 +6544,36 @@
       <s:c r="E48" s="1" t="n">
         <s:v>403.79</s:v>
       </s:c>
-      <s:c r="F48" s="1"/>
-      <s:c r="G48" s="1"/>
-      <s:c r="H48" s="1"/>
-      <s:c r="I48" s="1"/>
-      <s:c r="J48" s="1"/>
-      <s:c r="K48" s="1"/>
-      <s:c r="L48" s="1"/>
-      <s:c r="M48" s="1"/>
-      <s:c r="N48" s="1"/>
-      <s:c r="O48" s="1"/>
+      <s:c r="F48" s="1" t="n">
+        <s:v>-3703</s:v>
+      </s:c>
+      <s:c r="G48" s="1" t="n">
+        <s:v>2955.26</s:v>
+      </s:c>
+      <s:c r="H48" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="I48" s="1" t="n">
+        <s:v>9470.81</s:v>
+      </s:c>
+      <s:c r="J48" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="K48" s="1" t="n">
+        <s:v>-809.2</s:v>
+      </s:c>
+      <s:c r="L48" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="M48" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="N48" s="1" t="n">
+        <s:v>10026.45</s:v>
+      </s:c>
+      <s:c r="O48" s="1" t="n">
+        <s:v>215.28</s:v>
+      </s:c>
       <s:c r="P48" s="1" t="n">
         <s:v>62</s:v>
       </s:c>
@@ -5654,16 +6594,36 @@
       <s:c r="E49" s="1" t="n">
         <s:v>393.23</s:v>
       </s:c>
-      <s:c r="F49" s="1"/>
-      <s:c r="G49" s="1"/>
-      <s:c r="H49" s="1"/>
-      <s:c r="I49" s="1"/>
-      <s:c r="J49" s="1"/>
-      <s:c r="K49" s="1"/>
-      <s:c r="L49" s="1"/>
-      <s:c r="M49" s="1"/>
-      <s:c r="N49" s="1"/>
-      <s:c r="O49" s="1"/>
+      <s:c r="F49" s="1" t="n">
+        <s:v>-3713</s:v>
+      </s:c>
+      <s:c r="G49" s="1" t="n">
+        <s:v>2931.47</s:v>
+      </s:c>
+      <s:c r="H49" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="I49" s="1" t="n">
+        <s:v>9415.12</s:v>
+      </s:c>
+      <s:c r="J49" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="K49" s="1" t="n">
+        <s:v>-807.9</s:v>
+      </s:c>
+      <s:c r="L49" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="M49" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="N49" s="1" t="n">
+        <s:v>9714.9</s:v>
+      </s:c>
+      <s:c r="O49" s="1" t="n">
+        <s:v>223.32</s:v>
+      </s:c>
       <s:c r="P49" s="1" t="n">
         <s:v>62</s:v>
       </s:c>
@@ -5684,16 +6644,36 @@
       <s:c r="E50" s="1" t="n">
         <s:v>440.04</s:v>
       </s:c>
-      <s:c r="F50" s="1"/>
-      <s:c r="G50" s="1"/>
-      <s:c r="H50" s="1"/>
-      <s:c r="I50" s="1"/>
-      <s:c r="J50" s="1"/>
-      <s:c r="K50" s="1"/>
-      <s:c r="L50" s="1"/>
-      <s:c r="M50" s="1"/>
-      <s:c r="N50" s="1"/>
-      <s:c r="O50" s="1"/>
+      <s:c r="F50" s="1" t="n">
+        <s:v>-2933</s:v>
+      </s:c>
+      <s:c r="G50" s="1" t="n">
+        <s:v>2935.42</s:v>
+      </s:c>
+      <s:c r="H50" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="I50" s="1" t="n">
+        <s:v>9470.55</s:v>
+      </s:c>
+      <s:c r="J50" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="K50" s="1" t="n">
+        <s:v>-803.2</s:v>
+      </s:c>
+      <s:c r="L50" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="M50" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="N50" s="1" t="n">
+        <s:v>10678.21</s:v>
+      </s:c>
+      <s:c r="O50" s="1" t="n">
+        <s:v>232.85</s:v>
+      </s:c>
       <s:c r="P50" s="1" t="n">
         <s:v>62</s:v>
       </s:c>
@@ -5714,16 +6694,36 @@
       <s:c r="E51" s="1" t="n">
         <s:v>416.95</s:v>
       </s:c>
-      <s:c r="F51" s="1"/>
-      <s:c r="G51" s="1"/>
-      <s:c r="H51" s="1"/>
-      <s:c r="I51" s="1"/>
-      <s:c r="J51" s="1"/>
-      <s:c r="K51" s="1"/>
-      <s:c r="L51" s="1"/>
-      <s:c r="M51" s="1"/>
-      <s:c r="N51" s="1"/>
-      <s:c r="O51" s="1"/>
+      <s:c r="F51" s="1" t="n">
+        <s:v>-2813</s:v>
+      </s:c>
+      <s:c r="G51" s="1" t="n">
+        <s:v>2926.48</s:v>
+      </s:c>
+      <s:c r="H51" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="I51" s="1" t="n">
+        <s:v>9344.62</s:v>
+      </s:c>
+      <s:c r="J51" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="K51" s="1" t="n">
+        <s:v>-560.3</s:v>
+      </s:c>
+      <s:c r="L51" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="M51" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="N51" s="1" t="n">
+        <s:v>11064.17</s:v>
+      </s:c>
+      <s:c r="O51" s="1" t="n">
+        <s:v>235.53</s:v>
+      </s:c>
       <s:c r="P51" s="1" t="n">
         <s:v>62</s:v>
       </s:c>
@@ -5744,16 +6744,36 @@
       <s:c r="E52" s="1" t="n">
         <s:v>430</s:v>
       </s:c>
-      <s:c r="F52" s="1"/>
-      <s:c r="G52" s="1"/>
-      <s:c r="H52" s="1"/>
-      <s:c r="I52" s="1"/>
-      <s:c r="J52" s="1"/>
-      <s:c r="K52" s="1"/>
-      <s:c r="L52" s="1"/>
-      <s:c r="M52" s="1"/>
-      <s:c r="N52" s="1"/>
-      <s:c r="O52" s="1"/>
+      <s:c r="F52" s="1" t="n">
+        <s:v>-2653</s:v>
+      </s:c>
+      <s:c r="G52" s="1" t="n">
+        <s:v>2902.34</s:v>
+      </s:c>
+      <s:c r="H52" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="I52" s="1" t="n">
+        <s:v>9231.21</s:v>
+      </s:c>
+      <s:c r="J52" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="K52" s="1" t="n">
+        <s:v>-802.2</s:v>
+      </s:c>
+      <s:c r="L52" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="M52" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="N52" s="1" t="n">
+        <s:v>10754.79</s:v>
+      </s:c>
+      <s:c r="O52" s="1" t="n">
+        <s:v>245.25</s:v>
+      </s:c>
       <s:c r="P52" s="1" t="n">
         <s:v>62</s:v>
       </s:c>
@@ -5774,16 +6794,36 @@
       <s:c r="E53" s="1" t="n">
         <s:v>370.89</s:v>
       </s:c>
-      <s:c r="F53" s="1"/>
-      <s:c r="G53" s="1"/>
-      <s:c r="H53" s="1"/>
-      <s:c r="I53" s="1"/>
-      <s:c r="J53" s="1"/>
-      <s:c r="K53" s="1"/>
-      <s:c r="L53" s="1"/>
-      <s:c r="M53" s="1"/>
-      <s:c r="N53" s="1"/>
-      <s:c r="O53" s="1"/>
+      <s:c r="F53" s="1" t="n">
+        <s:v>-2593</s:v>
+      </s:c>
+      <s:c r="G53" s="1" t="n">
+        <s:v>2934.98</s:v>
+      </s:c>
+      <s:c r="H53" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="I53" s="1" t="n">
+        <s:v>9289.34</s:v>
+      </s:c>
+      <s:c r="J53" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="K53" s="1" t="n">
+        <s:v>-802.4</s:v>
+      </s:c>
+      <s:c r="L53" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="M53" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="N53" s="1" t="n">
+        <s:v>10156.72</s:v>
+      </s:c>
+      <s:c r="O53" s="1" t="n">
+        <s:v>247.56</s:v>
+      </s:c>
       <s:c r="P53" s="1" t="n">
         <s:v>62</s:v>
       </s:c>
@@ -5804,16 +6844,36 @@
       <s:c r="E54" s="1" t="n">
         <s:v>370.14</s:v>
       </s:c>
-      <s:c r="F54" s="1"/>
-      <s:c r="G54" s="1"/>
-      <s:c r="H54" s="1"/>
-      <s:c r="I54" s="1"/>
-      <s:c r="J54" s="1"/>
-      <s:c r="K54" s="1"/>
-      <s:c r="L54" s="1"/>
-      <s:c r="M54" s="1"/>
-      <s:c r="N54" s="1"/>
-      <s:c r="O54" s="1"/>
+      <s:c r="F54" s="1" t="n">
+        <s:v>-2383</s:v>
+      </s:c>
+      <s:c r="G54" s="1" t="n">
+        <s:v>2930.35</s:v>
+      </s:c>
+      <s:c r="H54" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="I54" s="1" t="n">
+        <s:v>9189.69</s:v>
+      </s:c>
+      <s:c r="J54" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="K54" s="1" t="n">
+        <s:v>-799.2</s:v>
+      </s:c>
+      <s:c r="L54" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="M54" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="N54" s="1" t="n">
+        <s:v>10510.39</s:v>
+      </s:c>
+      <s:c r="O54" s="1" t="n">
+        <s:v>260.87</s:v>
+      </s:c>
       <s:c r="P54" s="1" t="n">
         <s:v>62</s:v>
       </s:c>
@@ -5834,16 +6894,36 @@
       <s:c r="E55" s="1" t="n">
         <s:v>372.17</s:v>
       </s:c>
-      <s:c r="F55" s="1"/>
-      <s:c r="G55" s="1"/>
-      <s:c r="H55" s="1"/>
-      <s:c r="I55" s="1"/>
-      <s:c r="J55" s="1"/>
-      <s:c r="K55" s="1"/>
-      <s:c r="L55" s="1"/>
-      <s:c r="M55" s="1"/>
-      <s:c r="N55" s="1"/>
-      <s:c r="O55" s="1"/>
+      <s:c r="F55" s="1" t="n">
+        <s:v>-2273</s:v>
+      </s:c>
+      <s:c r="G55" s="1" t="n">
+        <s:v>2959.54</s:v>
+      </s:c>
+      <s:c r="H55" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="I55" s="1" t="n">
+        <s:v>8884.4</s:v>
+      </s:c>
+      <s:c r="J55" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="K55" s="1" t="n">
+        <s:v>-800</s:v>
+      </s:c>
+      <s:c r="L55" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="M55" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="N55" s="1" t="n">
+        <s:v>10850.04</s:v>
+      </s:c>
+      <s:c r="O55" s="1" t="n">
+        <s:v>278.61</s:v>
+      </s:c>
       <s:c r="P55" s="1" t="n">
         <s:v>62</s:v>
       </s:c>
@@ -5864,16 +6944,36 @@
       <s:c r="E56" s="1" t="n">
         <s:v>358.92</s:v>
       </s:c>
-      <s:c r="F56" s="1"/>
-      <s:c r="G56" s="1"/>
-      <s:c r="H56" s="1"/>
-      <s:c r="I56" s="1"/>
-      <s:c r="J56" s="1"/>
-      <s:c r="K56" s="1"/>
-      <s:c r="L56" s="1"/>
-      <s:c r="M56" s="1"/>
-      <s:c r="N56" s="1"/>
-      <s:c r="O56" s="1"/>
+      <s:c r="F56" s="1" t="n">
+        <s:v>-1760</s:v>
+      </s:c>
+      <s:c r="G56" s="1" t="n">
+        <s:v>2911.97</s:v>
+      </s:c>
+      <s:c r="H56" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="I56" s="1" t="n">
+        <s:v>8869.84</s:v>
+      </s:c>
+      <s:c r="J56" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="K56" s="1" t="n">
+        <s:v>-799.6</s:v>
+      </s:c>
+      <s:c r="L56" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="M56" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="N56" s="1" t="n">
+        <s:v>10592.87</s:v>
+      </s:c>
+      <s:c r="O56" s="1" t="n">
+        <s:v>293.01</s:v>
+      </s:c>
       <s:c r="P56" s="1" t="n">
         <s:v>62</s:v>
       </s:c>
@@ -5894,16 +6994,36 @@
       <s:c r="E57" s="1" t="n">
         <s:v>354.26</s:v>
       </s:c>
-      <s:c r="F57" s="1"/>
-      <s:c r="G57" s="1"/>
-      <s:c r="H57" s="1"/>
-      <s:c r="I57" s="1"/>
-      <s:c r="J57" s="1"/>
-      <s:c r="K57" s="1"/>
-      <s:c r="L57" s="1"/>
-      <s:c r="M57" s="1"/>
-      <s:c r="N57" s="1"/>
-      <s:c r="O57" s="1"/>
+      <s:c r="F57" s="1" t="n">
+        <s:v>-1250</s:v>
+      </s:c>
+      <s:c r="G57" s="1" t="n">
+        <s:v>2887.73</s:v>
+      </s:c>
+      <s:c r="H57" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="I57" s="1" t="n">
+        <s:v>8940.36</s:v>
+      </s:c>
+      <s:c r="J57" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="K57" s="1" t="n">
+        <s:v>-551.1</s:v>
+      </s:c>
+      <s:c r="L57" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="M57" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="N57" s="1" t="n">
+        <s:v>11171.27</s:v>
+      </s:c>
+      <s:c r="O57" s="1" t="n">
+        <s:v>276.11</s:v>
+      </s:c>
       <s:c r="P57" s="1" t="n">
         <s:v>65</s:v>
       </s:c>
@@ -5924,16 +7044,36 @@
       <s:c r="E58" s="1" t="n">
         <s:v>204.63</s:v>
       </s:c>
-      <s:c r="F58" s="1"/>
-      <s:c r="G58" s="1"/>
-      <s:c r="H58" s="1"/>
-      <s:c r="I58" s="1"/>
-      <s:c r="J58" s="1"/>
-      <s:c r="K58" s="1"/>
-      <s:c r="L58" s="1"/>
-      <s:c r="M58" s="1"/>
-      <s:c r="N58" s="1"/>
-      <s:c r="O58" s="1"/>
+      <s:c r="F58" s="1" t="n">
+        <s:v>-670</s:v>
+      </s:c>
+      <s:c r="G58" s="1" t="n">
+        <s:v>2823.84</s:v>
+      </s:c>
+      <s:c r="H58" s="1" t="n">
+        <s:v>1</s:v>
+      </s:c>
+      <s:c r="I58" s="1" t="n">
+        <s:v>8341.16</s:v>
+      </s:c>
+      <s:c r="J58" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="K58" s="1" t="n">
+        <s:v>-795.8</s:v>
+      </s:c>
+      <s:c r="L58" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="M58" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="N58" s="1" t="n">
+        <s:v>10776.12</s:v>
+      </s:c>
+      <s:c r="O58" s="1" t="n">
+        <s:v>294.68</s:v>
+      </s:c>
       <s:c r="P58" s="1" t="n">
         <s:v>65</s:v>
       </s:c>
@@ -5954,16 +7094,36 @@
       <s:c r="E59" s="1" t="n">
         <s:v>204.63</s:v>
       </s:c>
-      <s:c r="F59" s="1"/>
-      <s:c r="G59" s="1"/>
-      <s:c r="H59" s="1"/>
-      <s:c r="I59" s="1"/>
-      <s:c r="J59" s="1"/>
-      <s:c r="K59" s="1"/>
-      <s:c r="L59" s="1"/>
-      <s:c r="M59" s="1"/>
-      <s:c r="N59" s="1"/>
-      <s:c r="O59" s="1"/>
+      <s:c r="F59" s="1" t="n">
+        <s:v>-410</s:v>
+      </s:c>
+      <s:c r="G59" s="1" t="n">
+        <s:v>2837.68</s:v>
+      </s:c>
+      <s:c r="H59" s="1" t="n">
+        <s:v>1</s:v>
+      </s:c>
+      <s:c r="I59" s="1" t="n">
+        <s:v>7765.35</s:v>
+      </s:c>
+      <s:c r="J59" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="K59" s="1" t="n">
+        <s:v>-795</s:v>
+      </s:c>
+      <s:c r="L59" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="M59" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="N59" s="1" t="n">
+        <s:v>11849.75</s:v>
+      </s:c>
+      <s:c r="O59" s="1" t="n">
+        <s:v>309.89</s:v>
+      </s:c>
       <s:c r="P59" s="1" t="n">
         <s:v>65</s:v>
       </s:c>
@@ -5984,16 +7144,36 @@
       <s:c r="E60" s="1" t="n">
         <s:v>204.63</s:v>
       </s:c>
-      <s:c r="F60" s="1"/>
-      <s:c r="G60" s="1"/>
-      <s:c r="H60" s="1"/>
-      <s:c r="I60" s="1"/>
-      <s:c r="J60" s="1"/>
-      <s:c r="K60" s="1"/>
-      <s:c r="L60" s="1"/>
-      <s:c r="M60" s="1"/>
-      <s:c r="N60" s="1"/>
-      <s:c r="O60" s="1"/>
+      <s:c r="F60" s="1" t="n">
+        <s:v>-90</s:v>
+      </s:c>
+      <s:c r="G60" s="1" t="n">
+        <s:v>2909.23</s:v>
+      </s:c>
+      <s:c r="H60" s="1" t="n">
+        <s:v>1</s:v>
+      </s:c>
+      <s:c r="I60" s="1" t="n">
+        <s:v>7548.34</s:v>
+      </s:c>
+      <s:c r="J60" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="K60" s="1" t="n">
+        <s:v>-549.9</s:v>
+      </s:c>
+      <s:c r="L60" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="M60" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="N60" s="1" t="n">
+        <s:v>13354.3</s:v>
+      </s:c>
+      <s:c r="O60" s="1" t="n">
+        <s:v>315.64</s:v>
+      </s:c>
       <s:c r="P60" s="1" t="n">
         <s:v>65</s:v>
       </s:c>
@@ -6014,16 +7194,36 @@
       <s:c r="E61" s="1" t="n">
         <s:v>271.14</s:v>
       </s:c>
-      <s:c r="F61" s="1"/>
-      <s:c r="G61" s="1"/>
-      <s:c r="H61" s="1"/>
-      <s:c r="I61" s="1"/>
-      <s:c r="J61" s="1"/>
-      <s:c r="K61" s="1"/>
-      <s:c r="L61" s="1"/>
-      <s:c r="M61" s="1"/>
-      <s:c r="N61" s="1"/>
-      <s:c r="O61" s="1"/>
+      <s:c r="F61" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="G61" s="1" t="n">
+        <s:v>2886.08</s:v>
+      </s:c>
+      <s:c r="H61" s="1" t="n">
+        <s:v>1</s:v>
+      </s:c>
+      <s:c r="I61" s="1" t="n">
+        <s:v>7042.14</s:v>
+      </s:c>
+      <s:c r="J61" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="K61" s="1" t="n">
+        <s:v>-549.8</s:v>
+      </s:c>
+      <s:c r="L61" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="M61" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="N61" s="1" t="n">
+        <s:v>14322.14</s:v>
+      </s:c>
+      <s:c r="O61" s="1" t="n">
+        <s:v>326.87</s:v>
+      </s:c>
       <s:c r="P61" s="1" t="n">
         <s:v>64</s:v>
       </s:c>
@@ -6044,16 +7244,36 @@
       <s:c r="E62" s="1" t="n">
         <s:v>206</s:v>
       </s:c>
-      <s:c r="F62" s="1"/>
-      <s:c r="G62" s="1"/>
-      <s:c r="H62" s="1"/>
-      <s:c r="I62" s="1"/>
-      <s:c r="J62" s="1"/>
-      <s:c r="K62" s="1"/>
-      <s:c r="L62" s="1"/>
-      <s:c r="M62" s="1"/>
-      <s:c r="N62" s="1"/>
-      <s:c r="O62" s="1"/>
+      <s:c r="F62" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="G62" s="1" t="n">
+        <s:v>2839.1</s:v>
+      </s:c>
+      <s:c r="H62" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="I62" s="1" t="n">
+        <s:v>6380.59</s:v>
+      </s:c>
+      <s:c r="J62" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="K62" s="1" t="n">
+        <s:v>-796.7</s:v>
+      </s:c>
+      <s:c r="L62" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="M62" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="N62" s="1" t="n">
+        <s:v>15911.19</s:v>
+      </s:c>
+      <s:c r="O62" s="1" t="n">
+        <s:v>315.95</s:v>
+      </s:c>
       <s:c r="P62" s="1" t="n">
         <s:v>64</s:v>
       </s:c>
@@ -6074,16 +7294,36 @@
       <s:c r="E63" s="1" t="n">
         <s:v>204.63</s:v>
       </s:c>
-      <s:c r="F63" s="1"/>
-      <s:c r="G63" s="1"/>
-      <s:c r="H63" s="1"/>
-      <s:c r="I63" s="1"/>
-      <s:c r="J63" s="1"/>
-      <s:c r="K63" s="1"/>
-      <s:c r="L63" s="1"/>
-      <s:c r="M63" s="1"/>
-      <s:c r="N63" s="1"/>
-      <s:c r="O63" s="1"/>
+      <s:c r="F63" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="G63" s="1" t="n">
+        <s:v>2820.43</s:v>
+      </s:c>
+      <s:c r="H63" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="I63" s="1" t="n">
+        <s:v>5926.63</s:v>
+      </s:c>
+      <s:c r="J63" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="K63" s="1" t="n">
+        <s:v>-792.1</s:v>
+      </s:c>
+      <s:c r="L63" s="1" t="n">
+        <s:v>200</s:v>
+      </s:c>
+      <s:c r="M63" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="N63" s="1" t="n">
+        <s:v>15536.48</s:v>
+      </s:c>
+      <s:c r="O63" s="1" t="n">
+        <s:v>315.04</s:v>
+      </s:c>
       <s:c r="P63" s="1" t="n">
         <s:v>64</s:v>
       </s:c>
@@ -6104,16 +7344,36 @@
       <s:c r="E64" s="1" t="n">
         <s:v>417.64</s:v>
       </s:c>
-      <s:c r="F64" s="1"/>
-      <s:c r="G64" s="1"/>
-      <s:c r="H64" s="1"/>
-      <s:c r="I64" s="1"/>
-      <s:c r="J64" s="1"/>
-      <s:c r="K64" s="1"/>
-      <s:c r="L64" s="1"/>
-      <s:c r="M64" s="1"/>
-      <s:c r="N64" s="1"/>
-      <s:c r="O64" s="1"/>
+      <s:c r="F64" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="G64" s="1" t="n">
+        <s:v>2776.44</s:v>
+      </s:c>
+      <s:c r="H64" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="I64" s="1" t="n">
+        <s:v>5272.75</s:v>
+      </s:c>
+      <s:c r="J64" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="K64" s="1" t="n">
+        <s:v>-791.5</s:v>
+      </s:c>
+      <s:c r="L64" s="1" t="n">
+        <s:v>12.66</s:v>
+      </s:c>
+      <s:c r="M64" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="N64" s="1" t="n">
+        <s:v>15838.69</s:v>
+      </s:c>
+      <s:c r="O64" s="1" t="n">
+        <s:v>298.35</s:v>
+      </s:c>
       <s:c r="P64" s="1" t="n">
         <s:v>64</s:v>
       </s:c>
@@ -6134,16 +7394,36 @@
       <s:c r="E65" s="1" t="n">
         <s:v>418.94</s:v>
       </s:c>
-      <s:c r="F65" s="1"/>
-      <s:c r="G65" s="1"/>
-      <s:c r="H65" s="1"/>
-      <s:c r="I65" s="1"/>
-      <s:c r="J65" s="1"/>
-      <s:c r="K65" s="1"/>
-      <s:c r="L65" s="1"/>
-      <s:c r="M65" s="1"/>
-      <s:c r="N65" s="1"/>
-      <s:c r="O65" s="1"/>
+      <s:c r="F65" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="G65" s="1" t="n">
+        <s:v>2761.16</s:v>
+      </s:c>
+      <s:c r="H65" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="I65" s="1" t="n">
+        <s:v>4682.03</s:v>
+      </s:c>
+      <s:c r="J65" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="K65" s="1" t="n">
+        <s:v>-789.8</s:v>
+      </s:c>
+      <s:c r="L65" s="1" t="n">
+        <s:v>60.15</s:v>
+      </s:c>
+      <s:c r="M65" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="N65" s="1" t="n">
+        <s:v>16311.64</s:v>
+      </s:c>
+      <s:c r="O65" s="1" t="n">
+        <s:v>321.03</s:v>
+      </s:c>
       <s:c r="P65" s="1" t="n">
         <s:v>64</s:v>
       </s:c>
@@ -6164,16 +7444,36 @@
       <s:c r="E66" s="1" t="n">
         <s:v>429.66</s:v>
       </s:c>
-      <s:c r="F66" s="1"/>
-      <s:c r="G66" s="1"/>
-      <s:c r="H66" s="1"/>
-      <s:c r="I66" s="1"/>
-      <s:c r="J66" s="1"/>
-      <s:c r="K66" s="1"/>
-      <s:c r="L66" s="1"/>
-      <s:c r="M66" s="1"/>
-      <s:c r="N66" s="1"/>
-      <s:c r="O66" s="1"/>
+      <s:c r="F66" s="1" t="n">
+        <s:v>220</s:v>
+      </s:c>
+      <s:c r="G66" s="1" t="n">
+        <s:v>2722.58</s:v>
+      </s:c>
+      <s:c r="H66" s="1" t="n">
+        <s:v>1</s:v>
+      </s:c>
+      <s:c r="I66" s="1" t="n">
+        <s:v>4157.06</s:v>
+      </s:c>
+      <s:c r="J66" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="K66" s="1" t="n">
+        <s:v>-493.5</s:v>
+      </s:c>
+      <s:c r="L66" s="1" t="n">
+        <s:v>74.72</s:v>
+      </s:c>
+      <s:c r="M66" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="N66" s="1" t="n">
+        <s:v>16295.43</s:v>
+      </s:c>
+      <s:c r="O66" s="1" t="n">
+        <s:v>338.01</s:v>
+      </s:c>
       <s:c r="P66" s="1" t="n">
         <s:v>64</s:v>
       </s:c>
@@ -6194,16 +7494,36 @@
       <s:c r="E67" s="1" t="n">
         <s:v>415.73</s:v>
       </s:c>
-      <s:c r="F67" s="1"/>
-      <s:c r="G67" s="1"/>
-      <s:c r="H67" s="1"/>
-      <s:c r="I67" s="1"/>
-      <s:c r="J67" s="1"/>
-      <s:c r="K67" s="1"/>
-      <s:c r="L67" s="1"/>
-      <s:c r="M67" s="1"/>
-      <s:c r="N67" s="1"/>
-      <s:c r="O67" s="1"/>
+      <s:c r="F67" s="1" t="n">
+        <s:v>520</s:v>
+      </s:c>
+      <s:c r="G67" s="1" t="n">
+        <s:v>2693.21</s:v>
+      </s:c>
+      <s:c r="H67" s="1" t="n">
+        <s:v>1</s:v>
+      </s:c>
+      <s:c r="I67" s="1" t="n">
+        <s:v>3745.87</s:v>
+      </s:c>
+      <s:c r="J67" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="K67" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="L67" s="1" t="n">
+        <s:v>74.72</s:v>
+      </s:c>
+      <s:c r="M67" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="N67" s="1" t="n">
+        <s:v>16125.94</s:v>
+      </s:c>
+      <s:c r="O67" s="1" t="n">
+        <s:v>358.56</s:v>
+      </s:c>
       <s:c r="P67" s="1" t="n">
         <s:v>64</s:v>
       </s:c>
@@ -6224,16 +7544,36 @@
       <s:c r="E68" s="1" t="n">
         <s:v>414.98</s:v>
       </s:c>
-      <s:c r="F68" s="1"/>
-      <s:c r="G68" s="1"/>
-      <s:c r="H68" s="1"/>
-      <s:c r="I68" s="1"/>
-      <s:c r="J68" s="1"/>
-      <s:c r="K68" s="1"/>
-      <s:c r="L68" s="1"/>
-      <s:c r="M68" s="1"/>
-      <s:c r="N68" s="1"/>
-      <s:c r="O68" s="1"/>
+      <s:c r="F68" s="1" t="n">
+        <s:v>970</s:v>
+      </s:c>
+      <s:c r="G68" s="1" t="n">
+        <s:v>2724.11</s:v>
+      </s:c>
+      <s:c r="H68" s="1" t="n">
+        <s:v>1</s:v>
+      </s:c>
+      <s:c r="I68" s="1" t="n">
+        <s:v>3160.46</s:v>
+      </s:c>
+      <s:c r="J68" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="K68" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="L68" s="1" t="n">
+        <s:v>145.71</s:v>
+      </s:c>
+      <s:c r="M68" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="N68" s="1" t="n">
+        <s:v>16511.17</s:v>
+      </s:c>
+      <s:c r="O68" s="1" t="n">
+        <s:v>350.35</s:v>
+      </s:c>
       <s:c r="P68" s="1" t="n">
         <s:v>64</s:v>
       </s:c>
@@ -6254,16 +7594,36 @@
       <s:c r="E69" s="1" t="n">
         <s:v>416.01</s:v>
       </s:c>
-      <s:c r="F69" s="1"/>
-      <s:c r="G69" s="1"/>
-      <s:c r="H69" s="1"/>
-      <s:c r="I69" s="1"/>
-      <s:c r="J69" s="1"/>
-      <s:c r="K69" s="1"/>
-      <s:c r="L69" s="1"/>
-      <s:c r="M69" s="1"/>
-      <s:c r="N69" s="1"/>
-      <s:c r="O69" s="1"/>
+      <s:c r="F69" s="1" t="n">
+        <s:v>1355</s:v>
+      </s:c>
+      <s:c r="G69" s="1" t="n">
+        <s:v>2695.86</s:v>
+      </s:c>
+      <s:c r="H69" s="1" t="n">
+        <s:v>1</s:v>
+      </s:c>
+      <s:c r="I69" s="1" t="n">
+        <s:v>2754.07</s:v>
+      </s:c>
+      <s:c r="J69" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="K69" s="1" t="n">
+        <s:v>151.9</s:v>
+      </s:c>
+      <s:c r="L69" s="1" t="n">
+        <s:v>393.76</s:v>
+      </s:c>
+      <s:c r="M69" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="N69" s="1" t="n">
+        <s:v>16264.62</s:v>
+      </s:c>
+      <s:c r="O69" s="1" t="n">
+        <s:v>431.5</s:v>
+      </s:c>
       <s:c r="P69" s="1" t="n">
         <s:v>64</s:v>
       </s:c>
@@ -6284,16 +7644,36 @@
       <s:c r="E70" s="1" t="n">
         <s:v>404.58</s:v>
       </s:c>
-      <s:c r="F70" s="1"/>
-      <s:c r="G70" s="1"/>
-      <s:c r="H70" s="1"/>
-      <s:c r="I70" s="1"/>
-      <s:c r="J70" s="1"/>
-      <s:c r="K70" s="1"/>
-      <s:c r="L70" s="1"/>
-      <s:c r="M70" s="1"/>
-      <s:c r="N70" s="1"/>
-      <s:c r="O70" s="1"/>
+      <s:c r="F70" s="1" t="n">
+        <s:v>2735</s:v>
+      </s:c>
+      <s:c r="G70" s="1" t="n">
+        <s:v>2705.4</s:v>
+      </s:c>
+      <s:c r="H70" s="1" t="n">
+        <s:v>1</s:v>
+      </s:c>
+      <s:c r="I70" s="1" t="n">
+        <s:v>2167.91</s:v>
+      </s:c>
+      <s:c r="J70" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="K70" s="1" t="n">
+        <s:v>251.9</s:v>
+      </s:c>
+      <s:c r="L70" s="1" t="n">
+        <s:v>400</s:v>
+      </s:c>
+      <s:c r="M70" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="N70" s="1" t="n">
+        <s:v>16041.65</s:v>
+      </s:c>
+      <s:c r="O70" s="1" t="n">
+        <s:v>453.04</s:v>
+      </s:c>
       <s:c r="P70" s="1" t="n">
         <s:v>64</s:v>
       </s:c>
@@ -6314,16 +7694,36 @@
       <s:c r="E71" s="1" t="n">
         <s:v>372.17</s:v>
       </s:c>
-      <s:c r="F71" s="1"/>
-      <s:c r="G71" s="1"/>
-      <s:c r="H71" s="1"/>
-      <s:c r="I71" s="1"/>
-      <s:c r="J71" s="1"/>
-      <s:c r="K71" s="1"/>
-      <s:c r="L71" s="1"/>
-      <s:c r="M71" s="1"/>
-      <s:c r="N71" s="1"/>
-      <s:c r="O71" s="1"/>
+      <s:c r="F71" s="1" t="n">
+        <s:v>3130</s:v>
+      </s:c>
+      <s:c r="G71" s="1" t="n">
+        <s:v>2695.81</s:v>
+      </s:c>
+      <s:c r="H71" s="1" t="n">
+        <s:v>1</s:v>
+      </s:c>
+      <s:c r="I71" s="1" t="n">
+        <s:v>1715.82</s:v>
+      </s:c>
+      <s:c r="J71" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="K71" s="1" t="n">
+        <s:v>301.5</s:v>
+      </s:c>
+      <s:c r="L71" s="1" t="n">
+        <s:v>400</s:v>
+      </s:c>
+      <s:c r="M71" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="N71" s="1" t="n">
+        <s:v>15101.28</s:v>
+      </s:c>
+      <s:c r="O71" s="1" t="n">
+        <s:v>457.2</s:v>
+      </s:c>
       <s:c r="P71" s="1" t="n">
         <s:v>65</s:v>
       </s:c>
@@ -6344,16 +7744,36 @@
       <s:c r="E72" s="1" t="n">
         <s:v>369.69</s:v>
       </s:c>
-      <s:c r="F72" s="1"/>
-      <s:c r="G72" s="1"/>
-      <s:c r="H72" s="1"/>
-      <s:c r="I72" s="1"/>
-      <s:c r="J72" s="1"/>
-      <s:c r="K72" s="1"/>
-      <s:c r="L72" s="1"/>
-      <s:c r="M72" s="1"/>
-      <s:c r="N72" s="1"/>
-      <s:c r="O72" s="1"/>
+      <s:c r="F72" s="1" t="n">
+        <s:v>3230</s:v>
+      </s:c>
+      <s:c r="G72" s="1" t="n">
+        <s:v>2658.07</s:v>
+      </s:c>
+      <s:c r="H72" s="1" t="n">
+        <s:v>1</s:v>
+      </s:c>
+      <s:c r="I72" s="1" t="n">
+        <s:v>1282.09</s:v>
+      </s:c>
+      <s:c r="J72" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="K72" s="1" t="n">
+        <s:v>448.5</s:v>
+      </s:c>
+      <s:c r="L72" s="1" t="n">
+        <s:v>400</s:v>
+      </s:c>
+      <s:c r="M72" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="N72" s="1" t="n">
+        <s:v>14955.92</s:v>
+      </s:c>
+      <s:c r="O72" s="1" t="n">
+        <s:v>413.62</s:v>
+      </s:c>
       <s:c r="P72" s="1" t="n">
         <s:v>65</s:v>
       </s:c>
@@ -6374,16 +7794,36 @@
       <s:c r="E73" s="1" t="n">
         <s:v>271.14</s:v>
       </s:c>
-      <s:c r="F73" s="1"/>
-      <s:c r="G73" s="1"/>
-      <s:c r="H73" s="1"/>
-      <s:c r="I73" s="1"/>
-      <s:c r="J73" s="1"/>
-      <s:c r="K73" s="1"/>
-      <s:c r="L73" s="1"/>
-      <s:c r="M73" s="1"/>
-      <s:c r="N73" s="1"/>
-      <s:c r="O73" s="1"/>
+      <s:c r="F73" s="1" t="n">
+        <s:v>3167.3</s:v>
+      </s:c>
+      <s:c r="G73" s="1" t="n">
+        <s:v>2661.85</s:v>
+      </s:c>
+      <s:c r="H73" s="1" t="n">
+        <s:v>1</s:v>
+      </s:c>
+      <s:c r="I73" s="1" t="n">
+        <s:v>1044.34</s:v>
+      </s:c>
+      <s:c r="J73" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="K73" s="1" t="n">
+        <s:v>449.5</s:v>
+      </s:c>
+      <s:c r="L73" s="1" t="n">
+        <s:v>400</s:v>
+      </s:c>
+      <s:c r="M73" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="N73" s="1" t="n">
+        <s:v>14478.35</s:v>
+      </s:c>
+      <s:c r="O73" s="1" t="n">
+        <s:v>401.76</s:v>
+      </s:c>
       <s:c r="P73" s="1" t="n">
         <s:v>66</s:v>
       </s:c>
@@ -6404,16 +7844,36 @@
       <s:c r="E74" s="1" t="n">
         <s:v>371.92</s:v>
       </s:c>
-      <s:c r="F74" s="1"/>
-      <s:c r="G74" s="1"/>
-      <s:c r="H74" s="1"/>
-      <s:c r="I74" s="1"/>
-      <s:c r="J74" s="1"/>
-      <s:c r="K74" s="1"/>
-      <s:c r="L74" s="1"/>
-      <s:c r="M74" s="1"/>
-      <s:c r="N74" s="1"/>
-      <s:c r="O74" s="1"/>
+      <s:c r="F74" s="1" t="n">
+        <s:v>2972.3</s:v>
+      </s:c>
+      <s:c r="G74" s="1" t="n">
+        <s:v>2624.84</s:v>
+      </s:c>
+      <s:c r="H74" s="1" t="n">
+        <s:v>1</s:v>
+      </s:c>
+      <s:c r="I74" s="1" t="n">
+        <s:v>775.43</s:v>
+      </s:c>
+      <s:c r="J74" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="K74" s="1" t="n">
+        <s:v>550.2</s:v>
+      </s:c>
+      <s:c r="L74" s="1" t="n">
+        <s:v>400</s:v>
+      </s:c>
+      <s:c r="M74" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="N74" s="1" t="n">
+        <s:v>14337.69</s:v>
+      </s:c>
+      <s:c r="O74" s="1" t="n">
+        <s:v>403.04</s:v>
+      </s:c>
       <s:c r="P74" s="1" t="n">
         <s:v>64</s:v>
       </s:c>
@@ -6434,16 +7894,36 @@
       <s:c r="E75" s="1" t="n">
         <s:v>370.58</s:v>
       </s:c>
-      <s:c r="F75" s="1"/>
-      <s:c r="G75" s="1"/>
-      <s:c r="H75" s="1"/>
-      <s:c r="I75" s="1"/>
-      <s:c r="J75" s="1"/>
-      <s:c r="K75" s="1"/>
-      <s:c r="L75" s="1"/>
-      <s:c r="M75" s="1"/>
-      <s:c r="N75" s="1"/>
-      <s:c r="O75" s="1"/>
+      <s:c r="F75" s="1" t="n">
+        <s:v>2860</s:v>
+      </s:c>
+      <s:c r="G75" s="1" t="n">
+        <s:v>2605.5</s:v>
+      </s:c>
+      <s:c r="H75" s="1" t="n">
+        <s:v>1</s:v>
+      </s:c>
+      <s:c r="I75" s="1" t="n">
+        <s:v>585.28</s:v>
+      </s:c>
+      <s:c r="J75" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="K75" s="1" t="n">
+        <s:v>551.2</s:v>
+      </s:c>
+      <s:c r="L75" s="1" t="n">
+        <s:v>400</s:v>
+      </s:c>
+      <s:c r="M75" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="N75" s="1" t="n">
+        <s:v>14855.52</s:v>
+      </s:c>
+      <s:c r="O75" s="1" t="n">
+        <s:v>393.6</s:v>
+      </s:c>
       <s:c r="P75" s="1" t="n">
         <s:v>64</s:v>
       </s:c>
@@ -6464,16 +7944,36 @@
       <s:c r="E76" s="1" t="n">
         <s:v>371.45</s:v>
       </s:c>
-      <s:c r="F76" s="1"/>
-      <s:c r="G76" s="1"/>
-      <s:c r="H76" s="1"/>
-      <s:c r="I76" s="1"/>
-      <s:c r="J76" s="1"/>
-      <s:c r="K76" s="1"/>
-      <s:c r="L76" s="1"/>
-      <s:c r="M76" s="1"/>
-      <s:c r="N76" s="1"/>
-      <s:c r="O76" s="1"/>
+      <s:c r="F76" s="1" t="n">
+        <s:v>2680</s:v>
+      </s:c>
+      <s:c r="G76" s="1" t="n">
+        <s:v>2594.86</s:v>
+      </s:c>
+      <s:c r="H76" s="1" t="n">
+        <s:v>1</s:v>
+      </s:c>
+      <s:c r="I76" s="1" t="n">
+        <s:v>378.99</s:v>
+      </s:c>
+      <s:c r="J76" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="K76" s="1" t="n">
+        <s:v>448.1</s:v>
+      </s:c>
+      <s:c r="L76" s="1" t="n">
+        <s:v>400</s:v>
+      </s:c>
+      <s:c r="M76" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="N76" s="1" t="n">
+        <s:v>15543.19</s:v>
+      </s:c>
+      <s:c r="O76" s="1" t="n">
+        <s:v>389.37</s:v>
+      </s:c>
       <s:c r="P76" s="1" t="n">
         <s:v>64</s:v>
       </s:c>
@@ -6494,16 +7994,36 @@
       <s:c r="E77" s="1" t="n">
         <s:v>394.08</s:v>
       </s:c>
-      <s:c r="F77" s="1"/>
-      <s:c r="G77" s="1"/>
-      <s:c r="H77" s="1"/>
-      <s:c r="I77" s="1"/>
-      <s:c r="J77" s="1"/>
-      <s:c r="K77" s="1"/>
-      <s:c r="L77" s="1"/>
-      <s:c r="M77" s="1"/>
-      <s:c r="N77" s="1"/>
-      <s:c r="O77" s="1"/>
+      <s:c r="F77" s="1" t="n">
+        <s:v>2145</s:v>
+      </s:c>
+      <s:c r="G77" s="1" t="n">
+        <s:v>2621.39</s:v>
+      </s:c>
+      <s:c r="H77" s="1" t="n">
+        <s:v>1</s:v>
+      </s:c>
+      <s:c r="I77" s="1" t="n">
+        <s:v>213.75</s:v>
+      </s:c>
+      <s:c r="J77" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="K77" s="1" t="n">
+        <s:v>302.9</s:v>
+      </s:c>
+      <s:c r="L77" s="1" t="n">
+        <s:v>400</s:v>
+      </s:c>
+      <s:c r="M77" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="N77" s="1" t="n">
+        <s:v>15753.2</s:v>
+      </s:c>
+      <s:c r="O77" s="1" t="n">
+        <s:v>374.86</s:v>
+      </s:c>
       <s:c r="P77" s="1" t="n">
         <s:v>64</s:v>
       </s:c>
@@ -6524,16 +8044,36 @@
       <s:c r="E78" s="1" t="n">
         <s:v>393.85</s:v>
       </s:c>
-      <s:c r="F78" s="1"/>
-      <s:c r="G78" s="1"/>
-      <s:c r="H78" s="1"/>
-      <s:c r="I78" s="1"/>
-      <s:c r="J78" s="1"/>
-      <s:c r="K78" s="1"/>
-      <s:c r="L78" s="1"/>
-      <s:c r="M78" s="1"/>
-      <s:c r="N78" s="1"/>
-      <s:c r="O78" s="1"/>
+      <s:c r="F78" s="1" t="n">
+        <s:v>1270</s:v>
+      </s:c>
+      <s:c r="G78" s="1" t="n">
+        <s:v>2619.89</s:v>
+      </s:c>
+      <s:c r="H78" s="1" t="n">
+        <s:v>1</s:v>
+      </s:c>
+      <s:c r="I78" s="1" t="n">
+        <s:v>202.95</s:v>
+      </s:c>
+      <s:c r="J78" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="K78" s="1" t="n">
+        <s:v>300.5</s:v>
+      </s:c>
+      <s:c r="L78" s="1" t="n">
+        <s:v>400</s:v>
+      </s:c>
+      <s:c r="M78" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="N78" s="1" t="n">
+        <s:v>16263.8</s:v>
+      </s:c>
+      <s:c r="O78" s="1" t="n">
+        <s:v>377.47</s:v>
+      </s:c>
       <s:c r="P78" s="1" t="n">
         <s:v>64</s:v>
       </s:c>
@@ -6554,16 +8094,36 @@
       <s:c r="E79" s="1" t="n">
         <s:v>394.6</s:v>
       </s:c>
-      <s:c r="F79" s="1"/>
-      <s:c r="G79" s="1"/>
-      <s:c r="H79" s="1"/>
-      <s:c r="I79" s="1"/>
-      <s:c r="J79" s="1"/>
-      <s:c r="K79" s="1"/>
-      <s:c r="L79" s="1"/>
-      <s:c r="M79" s="1"/>
-      <s:c r="N79" s="1"/>
-      <s:c r="O79" s="1"/>
+      <s:c r="F79" s="1" t="n">
+        <s:v>850</s:v>
+      </s:c>
+      <s:c r="G79" s="1" t="n">
+        <s:v>2599.87</s:v>
+      </s:c>
+      <s:c r="H79" s="1" t="n">
+        <s:v>1</s:v>
+      </s:c>
+      <s:c r="I79" s="1" t="n">
+        <s:v>216.75</s:v>
+      </s:c>
+      <s:c r="J79" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="K79" s="1" t="n">
+        <s:v>300.2</s:v>
+      </s:c>
+      <s:c r="L79" s="1" t="n">
+        <s:v>400</s:v>
+      </s:c>
+      <s:c r="M79" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="N79" s="1" t="n">
+        <s:v>16625.82</s:v>
+      </s:c>
+      <s:c r="O79" s="1" t="n">
+        <s:v>381.25</s:v>
+      </s:c>
       <s:c r="P79" s="1" t="n">
         <s:v>64</s:v>
       </s:c>
@@ -6584,16 +8144,36 @@
       <s:c r="E80" s="1" t="n">
         <s:v>389.54</s:v>
       </s:c>
-      <s:c r="F80" s="1"/>
-      <s:c r="G80" s="1"/>
-      <s:c r="H80" s="1"/>
-      <s:c r="I80" s="1"/>
-      <s:c r="J80" s="1"/>
-      <s:c r="K80" s="1"/>
-      <s:c r="L80" s="1"/>
-      <s:c r="M80" s="1"/>
-      <s:c r="N80" s="1"/>
-      <s:c r="O80" s="1"/>
+      <s:c r="F80" s="1" t="n">
+        <s:v>330</s:v>
+      </s:c>
+      <s:c r="G80" s="1" t="n">
+        <s:v>2589.37</s:v>
+      </s:c>
+      <s:c r="H80" s="1" t="n">
+        <s:v>1</s:v>
+      </s:c>
+      <s:c r="I80" s="1" t="n">
+        <s:v>148.2</s:v>
+      </s:c>
+      <s:c r="J80" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="K80" s="1" t="n">
+        <s:v>300.4</s:v>
+      </s:c>
+      <s:c r="L80" s="1" t="n">
+        <s:v>400</s:v>
+      </s:c>
+      <s:c r="M80" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="N80" s="1" t="n">
+        <s:v>17090.55</s:v>
+      </s:c>
+      <s:c r="O80" s="1" t="n">
+        <s:v>370.47</s:v>
+      </s:c>
       <s:c r="P80" s="1" t="n">
         <s:v>64</s:v>
       </s:c>
@@ -6614,16 +8194,36 @@
       <s:c r="E81" s="1" t="n">
         <s:v>385</s:v>
       </s:c>
-      <s:c r="F81" s="1"/>
-      <s:c r="G81" s="1"/>
-      <s:c r="H81" s="1"/>
-      <s:c r="I81" s="1"/>
-      <s:c r="J81" s="1"/>
-      <s:c r="K81" s="1"/>
-      <s:c r="L81" s="1"/>
-      <s:c r="M81" s="1"/>
-      <s:c r="N81" s="1"/>
-      <s:c r="O81" s="1"/>
+      <s:c r="F81" s="1" t="n">
+        <s:v>130</s:v>
+      </s:c>
+      <s:c r="G81" s="1" t="n">
+        <s:v>2610.16</s:v>
+      </s:c>
+      <s:c r="H81" s="1" t="n">
+        <s:v>1</s:v>
+      </s:c>
+      <s:c r="I81" s="1" t="n">
+        <s:v>142.2</s:v>
+      </s:c>
+      <s:c r="J81" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="K81" s="1" t="n">
+        <s:v>150</s:v>
+      </s:c>
+      <s:c r="L81" s="1" t="n">
+        <s:v>400</s:v>
+      </s:c>
+      <s:c r="M81" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="N81" s="1" t="n">
+        <s:v>16739.58</s:v>
+      </s:c>
+      <s:c r="O81" s="1" t="n">
+        <s:v>406.66</s:v>
+      </s:c>
       <s:c r="P81" s="1" t="n">
         <s:v>64</s:v>
       </s:c>
@@ -6644,16 +8244,36 @@
       <s:c r="E82" s="1" t="n">
         <s:v>395.75</s:v>
       </s:c>
-      <s:c r="F82" s="1"/>
-      <s:c r="G82" s="1"/>
-      <s:c r="H82" s="1"/>
-      <s:c r="I82" s="1"/>
-      <s:c r="J82" s="1"/>
-      <s:c r="K82" s="1"/>
-      <s:c r="L82" s="1"/>
-      <s:c r="M82" s="1"/>
-      <s:c r="N82" s="1"/>
-      <s:c r="O82" s="1"/>
+      <s:c r="F82" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="G82" s="1" t="n">
+        <s:v>2614.64</s:v>
+      </s:c>
+      <s:c r="H82" s="1" t="n">
+        <s:v>1</s:v>
+      </s:c>
+      <s:c r="I82" s="1" t="n">
+        <s:v>126.5</s:v>
+      </s:c>
+      <s:c r="J82" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="K82" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="L82" s="1" t="n">
+        <s:v>400</s:v>
+      </s:c>
+      <s:c r="M82" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="N82" s="1" t="n">
+        <s:v>16683</s:v>
+      </s:c>
+      <s:c r="O82" s="1" t="n">
+        <s:v>430.97</s:v>
+      </s:c>
       <s:c r="P82" s="1" t="n">
         <s:v>64</s:v>
       </s:c>
@@ -6674,16 +8294,36 @@
       <s:c r="E83" s="1" t="n">
         <s:v>383.1</s:v>
       </s:c>
-      <s:c r="F83" s="1"/>
-      <s:c r="G83" s="1"/>
-      <s:c r="H83" s="1"/>
-      <s:c r="I83" s="1"/>
-      <s:c r="J83" s="1"/>
-      <s:c r="K83" s="1"/>
-      <s:c r="L83" s="1"/>
-      <s:c r="M83" s="1"/>
-      <s:c r="N83" s="1"/>
-      <s:c r="O83" s="1"/>
+      <s:c r="F83" s="1" t="n">
+        <s:v>90</s:v>
+      </s:c>
+      <s:c r="G83" s="1" t="n">
+        <s:v>2654.09</s:v>
+      </s:c>
+      <s:c r="H83" s="1" t="n">
+        <s:v>1</s:v>
+      </s:c>
+      <s:c r="I83" s="1" t="n">
+        <s:v>123.5</s:v>
+      </s:c>
+      <s:c r="J83" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="K83" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="L83" s="1" t="n">
+        <s:v>400</s:v>
+      </s:c>
+      <s:c r="M83" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="N83" s="1" t="n">
+        <s:v>16460.45</s:v>
+      </s:c>
+      <s:c r="O83" s="1" t="n">
+        <s:v>437.75</s:v>
+      </s:c>
       <s:c r="P83" s="1" t="n">
         <s:v>64</s:v>
       </s:c>
@@ -6704,16 +8344,36 @@
       <s:c r="E84" s="1" t="n">
         <s:v>380.98</s:v>
       </s:c>
-      <s:c r="F84" s="1"/>
-      <s:c r="G84" s="1"/>
-      <s:c r="H84" s="1"/>
-      <s:c r="I84" s="1"/>
-      <s:c r="J84" s="1"/>
-      <s:c r="K84" s="1"/>
-      <s:c r="L84" s="1"/>
-      <s:c r="M84" s="1"/>
-      <s:c r="N84" s="1"/>
-      <s:c r="O84" s="1"/>
+      <s:c r="F84" s="1" t="n">
+        <s:v>90</s:v>
+      </s:c>
+      <s:c r="G84" s="1" t="n">
+        <s:v>2658.15</s:v>
+      </s:c>
+      <s:c r="H84" s="1" t="n">
+        <s:v>1</s:v>
+      </s:c>
+      <s:c r="I84" s="1" t="n">
+        <s:v>109.9</s:v>
+      </s:c>
+      <s:c r="J84" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="K84" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="L84" s="1" t="n">
+        <s:v>400</s:v>
+      </s:c>
+      <s:c r="M84" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="N84" s="1" t="n">
+        <s:v>15932.29</s:v>
+      </s:c>
+      <s:c r="O84" s="1" t="n">
+        <s:v>435.86</s:v>
+      </s:c>
       <s:c r="P84" s="1" t="n">
         <s:v>64</s:v>
       </s:c>
@@ -6734,16 +8394,36 @@
       <s:c r="E85" s="1" t="n">
         <s:v>393.23</s:v>
       </s:c>
-      <s:c r="F85" s="1"/>
-      <s:c r="G85" s="1"/>
-      <s:c r="H85" s="1"/>
-      <s:c r="I85" s="1"/>
-      <s:c r="J85" s="1"/>
-      <s:c r="K85" s="1"/>
-      <s:c r="L85" s="1"/>
-      <s:c r="M85" s="1"/>
-      <s:c r="N85" s="1"/>
-      <s:c r="O85" s="1"/>
+      <s:c r="F85" s="1" t="n">
+        <s:v>90</s:v>
+      </s:c>
+      <s:c r="G85" s="1" t="n">
+        <s:v>2674.89</s:v>
+      </s:c>
+      <s:c r="H85" s="1" t="n">
+        <s:v>1</s:v>
+      </s:c>
+      <s:c r="I85" s="1" t="n">
+        <s:v>100.45</s:v>
+      </s:c>
+      <s:c r="J85" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="K85" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="L85" s="1" t="n">
+        <s:v>400</s:v>
+      </s:c>
+      <s:c r="M85" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="N85" s="1" t="n">
+        <s:v>16051.82</s:v>
+      </s:c>
+      <s:c r="O85" s="1" t="n">
+        <s:v>427.64</s:v>
+      </s:c>
       <s:c r="P85" s="1" t="n">
         <s:v>64</s:v>
       </s:c>
@@ -6764,16 +8444,36 @@
       <s:c r="E86" s="1" t="n">
         <s:v>392.7</s:v>
       </s:c>
-      <s:c r="F86" s="1"/>
-      <s:c r="G86" s="1"/>
-      <s:c r="H86" s="1"/>
-      <s:c r="I86" s="1"/>
-      <s:c r="J86" s="1"/>
-      <s:c r="K86" s="1"/>
-      <s:c r="L86" s="1"/>
-      <s:c r="M86" s="1"/>
-      <s:c r="N86" s="1"/>
-      <s:c r="O86" s="1"/>
+      <s:c r="F86" s="1" t="n">
+        <s:v>90</s:v>
+      </s:c>
+      <s:c r="G86" s="1" t="n">
+        <s:v>2677.38</s:v>
+      </s:c>
+      <s:c r="H86" s="1" t="n">
+        <s:v>1</s:v>
+      </s:c>
+      <s:c r="I86" s="1" t="n">
+        <s:v>42.6</s:v>
+      </s:c>
+      <s:c r="J86" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="K86" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="L86" s="1" t="n">
+        <s:v>400</s:v>
+      </s:c>
+      <s:c r="M86" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="N86" s="1" t="n">
+        <s:v>15960.45</s:v>
+      </s:c>
+      <s:c r="O86" s="1" t="n">
+        <s:v>460.48</s:v>
+      </s:c>
       <s:c r="P86" s="1" t="n">
         <s:v>64</s:v>
       </s:c>
@@ -6794,16 +8494,36 @@
       <s:c r="E87" s="1" t="n">
         <s:v>394.51</s:v>
       </s:c>
-      <s:c r="F87" s="1"/>
-      <s:c r="G87" s="1"/>
-      <s:c r="H87" s="1"/>
-      <s:c r="I87" s="1"/>
-      <s:c r="J87" s="1"/>
-      <s:c r="K87" s="1"/>
-      <s:c r="L87" s="1"/>
-      <s:c r="M87" s="1"/>
-      <s:c r="N87" s="1"/>
-      <s:c r="O87" s="1"/>
+      <s:c r="F87" s="1" t="n">
+        <s:v>190</s:v>
+      </s:c>
+      <s:c r="G87" s="1" t="n">
+        <s:v>2672.98</s:v>
+      </s:c>
+      <s:c r="H87" s="1" t="n">
+        <s:v>1</s:v>
+      </s:c>
+      <s:c r="I87" s="1" t="n">
+        <s:v>41.7</s:v>
+      </s:c>
+      <s:c r="J87" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="K87" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="L87" s="1" t="n">
+        <s:v>400</s:v>
+      </s:c>
+      <s:c r="M87" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="N87" s="1" t="n">
+        <s:v>16115.6</s:v>
+      </s:c>
+      <s:c r="O87" s="1" t="n">
+        <s:v>505.52</s:v>
+      </s:c>
       <s:c r="P87" s="1" t="n">
         <s:v>64</s:v>
       </s:c>
@@ -6824,16 +8544,36 @@
       <s:c r="E88" s="1" t="n">
         <s:v>400.54</s:v>
       </s:c>
-      <s:c r="F88" s="1"/>
-      <s:c r="G88" s="1"/>
-      <s:c r="H88" s="1"/>
-      <s:c r="I88" s="1"/>
-      <s:c r="J88" s="1"/>
-      <s:c r="K88" s="1"/>
-      <s:c r="L88" s="1"/>
-      <s:c r="M88" s="1"/>
-      <s:c r="N88" s="1"/>
-      <s:c r="O88" s="1"/>
+      <s:c r="F88" s="1" t="n">
+        <s:v>190</s:v>
+      </s:c>
+      <s:c r="G88" s="1" t="n">
+        <s:v>2664.79</s:v>
+      </s:c>
+      <s:c r="H88" s="1" t="n">
+        <s:v>1</s:v>
+      </s:c>
+      <s:c r="I88" s="1" t="n">
+        <s:v>41.7</s:v>
+      </s:c>
+      <s:c r="J88" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="K88" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="L88" s="1" t="n">
+        <s:v>400</s:v>
+      </s:c>
+      <s:c r="M88" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="N88" s="1" t="n">
+        <s:v>16405.43</s:v>
+      </s:c>
+      <s:c r="O88" s="1" t="n">
+        <s:v>550.17</s:v>
+      </s:c>
       <s:c r="P88" s="1" t="n">
         <s:v>64</s:v>
       </s:c>
@@ -6854,16 +8594,36 @@
       <s:c r="E89" s="1" t="n">
         <s:v>395.79</s:v>
       </s:c>
-      <s:c r="F89" s="1"/>
-      <s:c r="G89" s="1"/>
-      <s:c r="H89" s="1"/>
-      <s:c r="I89" s="1"/>
-      <s:c r="J89" s="1"/>
-      <s:c r="K89" s="1"/>
-      <s:c r="L89" s="1"/>
-      <s:c r="M89" s="1"/>
-      <s:c r="N89" s="1"/>
-      <s:c r="O89" s="1"/>
+      <s:c r="F89" s="1" t="n">
+        <s:v>420</s:v>
+      </s:c>
+      <s:c r="G89" s="1" t="n">
+        <s:v>2646.7</s:v>
+      </s:c>
+      <s:c r="H89" s="1" t="n">
+        <s:v>1</s:v>
+      </s:c>
+      <s:c r="I89" s="1" t="n">
+        <s:v>41.7</s:v>
+      </s:c>
+      <s:c r="J89" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="K89" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="L89" s="1" t="n">
+        <s:v>400</s:v>
+      </s:c>
+      <s:c r="M89" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="N89" s="1" t="n">
+        <s:v>16360.23</s:v>
+      </s:c>
+      <s:c r="O89" s="1" t="n">
+        <s:v>566.57</s:v>
+      </s:c>
       <s:c r="P89" s="1" t="n">
         <s:v>64</s:v>
       </s:c>
@@ -6884,16 +8644,36 @@
       <s:c r="E90" s="1" t="n">
         <s:v>395.45</s:v>
       </s:c>
-      <s:c r="F90" s="1"/>
-      <s:c r="G90" s="1"/>
-      <s:c r="H90" s="1"/>
-      <s:c r="I90" s="1"/>
-      <s:c r="J90" s="1"/>
-      <s:c r="K90" s="1"/>
-      <s:c r="L90" s="1"/>
-      <s:c r="M90" s="1"/>
-      <s:c r="N90" s="1"/>
-      <s:c r="O90" s="1"/>
+      <s:c r="F90" s="1" t="n">
+        <s:v>950</s:v>
+      </s:c>
+      <s:c r="G90" s="1" t="n">
+        <s:v>2635.56</s:v>
+      </s:c>
+      <s:c r="H90" s="1" t="n">
+        <s:v>1</s:v>
+      </s:c>
+      <s:c r="I90" s="1" t="n">
+        <s:v>41.7</s:v>
+      </s:c>
+      <s:c r="J90" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="K90" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="L90" s="1" t="n">
+        <s:v>400</s:v>
+      </s:c>
+      <s:c r="M90" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="N90" s="1" t="n">
+        <s:v>16187.6</s:v>
+      </s:c>
+      <s:c r="O90" s="1" t="n">
+        <s:v>598.04</s:v>
+      </s:c>
       <s:c r="P90" s="1" t="n">
         <s:v>64</s:v>
       </s:c>
@@ -6914,16 +8694,36 @@
       <s:c r="E91" s="1" t="n">
         <s:v>395.75</s:v>
       </s:c>
-      <s:c r="F91" s="1"/>
-      <s:c r="G91" s="1"/>
-      <s:c r="H91" s="1"/>
-      <s:c r="I91" s="1"/>
-      <s:c r="J91" s="1"/>
-      <s:c r="K91" s="1"/>
-      <s:c r="L91" s="1"/>
-      <s:c r="M91" s="1"/>
-      <s:c r="N91" s="1"/>
-      <s:c r="O91" s="1"/>
+      <s:c r="F91" s="1" t="n">
+        <s:v>1220</s:v>
+      </s:c>
+      <s:c r="G91" s="1" t="n">
+        <s:v>2635.16</s:v>
+      </s:c>
+      <s:c r="H91" s="1" t="n">
+        <s:v>1</s:v>
+      </s:c>
+      <s:c r="I91" s="1" t="n">
+        <s:v>23.7</s:v>
+      </s:c>
+      <s:c r="J91" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="K91" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="L91" s="1" t="n">
+        <s:v>400</s:v>
+      </s:c>
+      <s:c r="M91" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="N91" s="1" t="n">
+        <s:v>16180.16</s:v>
+      </s:c>
+      <s:c r="O91" s="1" t="n">
+        <s:v>607.98</s:v>
+      </s:c>
       <s:c r="P91" s="1" t="n">
         <s:v>64</s:v>
       </s:c>
@@ -6944,16 +8744,36 @@
       <s:c r="E92" s="1" t="n">
         <s:v>395.35</s:v>
       </s:c>
-      <s:c r="F92" s="1"/>
-      <s:c r="G92" s="1"/>
-      <s:c r="H92" s="1"/>
-      <s:c r="I92" s="1"/>
-      <s:c r="J92" s="1"/>
-      <s:c r="K92" s="1"/>
-      <s:c r="L92" s="1"/>
-      <s:c r="M92" s="1"/>
-      <s:c r="N92" s="1"/>
-      <s:c r="O92" s="1"/>
+      <s:c r="F92" s="1" t="n">
+        <s:v>1520</s:v>
+      </s:c>
+      <s:c r="G92" s="1" t="n">
+        <s:v>2600.98</s:v>
+      </s:c>
+      <s:c r="H92" s="1" t="n">
+        <s:v>1</s:v>
+      </s:c>
+      <s:c r="I92" s="1" t="n">
+        <s:v>23.7</s:v>
+      </s:c>
+      <s:c r="J92" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="K92" s="1" t="n">
+        <s:v>150.4</s:v>
+      </s:c>
+      <s:c r="L92" s="1" t="n">
+        <s:v>400</s:v>
+      </s:c>
+      <s:c r="M92" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="N92" s="1" t="n">
+        <s:v>15947.11</s:v>
+      </s:c>
+      <s:c r="O92" s="1" t="n">
+        <s:v>622.11</s:v>
+      </s:c>
       <s:c r="P92" s="1" t="n">
         <s:v>64</s:v>
       </s:c>
@@ -6974,16 +8794,36 @@
       <s:c r="E93" s="1" t="n">
         <s:v>403.98</s:v>
       </s:c>
-      <s:c r="F93" s="1"/>
-      <s:c r="G93" s="1"/>
-      <s:c r="H93" s="1"/>
-      <s:c r="I93" s="1"/>
-      <s:c r="J93" s="1"/>
-      <s:c r="K93" s="1"/>
-      <s:c r="L93" s="1"/>
-      <s:c r="M93" s="1"/>
-      <s:c r="N93" s="1"/>
-      <s:c r="O93" s="1"/>
+      <s:c r="F93" s="1" t="n">
+        <s:v>1620</s:v>
+      </s:c>
+      <s:c r="G93" s="1" t="n">
+        <s:v>2579.25</s:v>
+      </s:c>
+      <s:c r="H93" s="1" t="n">
+        <s:v>1</s:v>
+      </s:c>
+      <s:c r="I93" s="1" t="n">
+        <s:v>23.7</s:v>
+      </s:c>
+      <s:c r="J93" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="K93" s="1" t="n">
+        <s:v>151.6</s:v>
+      </s:c>
+      <s:c r="L93" s="1" t="n">
+        <s:v>400</s:v>
+      </s:c>
+      <s:c r="M93" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="N93" s="1" t="n">
+        <s:v>16370.05</s:v>
+      </s:c>
+      <s:c r="O93" s="1" t="n">
+        <s:v>635.7</s:v>
+      </s:c>
       <s:c r="P93" s="1" t="n">
         <s:v>64</s:v>
       </s:c>
@@ -7004,16 +8844,36 @@
       <s:c r="E94" s="1" t="n">
         <s:v>402.3</s:v>
       </s:c>
-      <s:c r="F94" s="1"/>
-      <s:c r="G94" s="1"/>
-      <s:c r="H94" s="1"/>
-      <s:c r="I94" s="1"/>
-      <s:c r="J94" s="1"/>
-      <s:c r="K94" s="1"/>
-      <s:c r="L94" s="1"/>
-      <s:c r="M94" s="1"/>
-      <s:c r="N94" s="1"/>
-      <s:c r="O94" s="1"/>
+      <s:c r="F94" s="1" t="n">
+        <s:v>2260</s:v>
+      </s:c>
+      <s:c r="G94" s="1" t="n">
+        <s:v>2537.73</s:v>
+      </s:c>
+      <s:c r="H94" s="1" t="n">
+        <s:v>1</s:v>
+      </s:c>
+      <s:c r="I94" s="1" t="n">
+        <s:v>23.7</s:v>
+      </s:c>
+      <s:c r="J94" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="K94" s="1" t="n">
+        <s:v>251.3</s:v>
+      </s:c>
+      <s:c r="L94" s="1" t="n">
+        <s:v>400</s:v>
+      </s:c>
+      <s:c r="M94" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="N94" s="1" t="n">
+        <s:v>16263.43</s:v>
+      </s:c>
+      <s:c r="O94" s="1" t="n">
+        <s:v>667.94</s:v>
+      </s:c>
       <s:c r="P94" s="1" t="n">
         <s:v>64</s:v>
       </s:c>
@@ -7034,16 +8894,36 @@
       <s:c r="E95" s="1" t="n">
         <s:v>383.97</s:v>
       </s:c>
-      <s:c r="F95" s="1"/>
-      <s:c r="G95" s="1"/>
-      <s:c r="H95" s="1"/>
-      <s:c r="I95" s="1"/>
-      <s:c r="J95" s="1"/>
-      <s:c r="K95" s="1"/>
-      <s:c r="L95" s="1"/>
-      <s:c r="M95" s="1"/>
-      <s:c r="N95" s="1"/>
-      <s:c r="O95" s="1"/>
+      <s:c r="F95" s="1" t="n">
+        <s:v>2390</s:v>
+      </s:c>
+      <s:c r="G95" s="1" t="n">
+        <s:v>2535.8</s:v>
+      </s:c>
+      <s:c r="H95" s="1" t="n">
+        <s:v>1</s:v>
+      </s:c>
+      <s:c r="I95" s="1" t="n">
+        <s:v>15.7</s:v>
+      </s:c>
+      <s:c r="J95" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="K95" s="1" t="n">
+        <s:v>250.2</s:v>
+      </s:c>
+      <s:c r="L95" s="1" t="n">
+        <s:v>400</s:v>
+      </s:c>
+      <s:c r="M95" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="N95" s="1" t="n">
+        <s:v>15641.33</s:v>
+      </s:c>
+      <s:c r="O95" s="1" t="n">
+        <s:v>686.76</s:v>
+      </s:c>
       <s:c r="P95" s="1" t="n">
         <s:v>64</s:v>
       </s:c>
@@ -7064,16 +8944,36 @@
       <s:c r="E96" s="1" t="n">
         <s:v>403.57</s:v>
       </s:c>
-      <s:c r="F96" s="1"/>
-      <s:c r="G96" s="1"/>
-      <s:c r="H96" s="1"/>
-      <s:c r="I96" s="1"/>
-      <s:c r="J96" s="1"/>
-      <s:c r="K96" s="1"/>
-      <s:c r="L96" s="1"/>
-      <s:c r="M96" s="1"/>
-      <s:c r="N96" s="1"/>
-      <s:c r="O96" s="1"/>
+      <s:c r="F96" s="1" t="n">
+        <s:v>1960</s:v>
+      </s:c>
+      <s:c r="G96" s="1" t="n">
+        <s:v>2537.52</s:v>
+      </s:c>
+      <s:c r="H96" s="1" t="n">
+        <s:v>1</s:v>
+      </s:c>
+      <s:c r="I96" s="1" t="n">
+        <s:v>9.7</s:v>
+      </s:c>
+      <s:c r="J96" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="K96" s="1" t="n">
+        <s:v>151.1</s:v>
+      </s:c>
+      <s:c r="L96" s="1" t="n">
+        <s:v>400</s:v>
+      </s:c>
+      <s:c r="M96" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="N96" s="1" t="n">
+        <s:v>15913.32</s:v>
+      </s:c>
+      <s:c r="O96" s="1" t="n">
+        <s:v>696.56</s:v>
+      </s:c>
       <s:c r="P96" s="1" t="n">
         <s:v>64</s:v>
       </s:c>
@@ -7096,16 +8996,36 @@
       <s:c r="E97" s="1" t="n">
         <s:v>429.66</s:v>
       </s:c>
-      <s:c r="F97" s="1"/>
-      <s:c r="G97" s="1"/>
-      <s:c r="H97" s="1"/>
-      <s:c r="I97" s="1"/>
-      <s:c r="J97" s="1"/>
-      <s:c r="K97" s="1"/>
-      <s:c r="L97" s="1"/>
-      <s:c r="M97" s="1"/>
-      <s:c r="N97" s="1"/>
-      <s:c r="O97" s="1"/>
+      <s:c r="F97" s="1" t="n">
+        <s:v>1060</s:v>
+      </s:c>
+      <s:c r="G97" s="1" t="n">
+        <s:v>2544.86</s:v>
+      </s:c>
+      <s:c r="H97" s="1" t="n">
+        <s:v>1</s:v>
+      </s:c>
+      <s:c r="I97" s="1" t="n">
+        <s:v>3.7</s:v>
+      </s:c>
+      <s:c r="J97" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="K97" s="1" t="n">
+        <s:v>150.7</s:v>
+      </s:c>
+      <s:c r="L97" s="1" t="n">
+        <s:v>400</s:v>
+      </s:c>
+      <s:c r="M97" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="N97" s="1" t="n">
+        <s:v>16646.15</s:v>
+      </s:c>
+      <s:c r="O97" s="1" t="n">
+        <s:v>715.49</s:v>
+      </s:c>
       <s:c r="P97" s="1" t="n">
         <s:v>64</s:v>
       </s:c>
